--- a/Excel_practice/practice_excel.xlsx
+++ b/Excel_practice/practice_excel.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fiiit\Excel_practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3DBA816-B69D-4BCC-AD0C-93DBED509AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC96A86-9705-4FD8-8B7F-DF66EA050E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9582A52E-1B81-4984-BBE7-A03F4D74D0D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Task 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId3"/>
+    <sheet name="Task 3" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="106">
   <si>
     <t>S.No</t>
   </si>
@@ -168,13 +169,203 @@
   </si>
   <si>
     <t xml:space="preserve">mixed </t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Region</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>UnitPrice</t>
+  </si>
+  <si>
+    <t>StoreLocation</t>
+  </si>
+  <si>
+    <t>CustomerType</t>
+  </si>
+  <si>
+    <t>Discount</t>
+  </si>
+  <si>
+    <t>Salesperson</t>
+  </si>
+  <si>
+    <t>PaymentMethod</t>
+  </si>
+  <si>
+    <t>Returned</t>
+  </si>
+  <si>
+    <t>OrderDate</t>
+  </si>
+  <si>
+    <t>DeliveryDate</t>
+  </si>
+  <si>
+    <t>RegionManager</t>
+  </si>
+  <si>
+    <t>East</t>
+  </si>
+  <si>
+    <t>Laptop</t>
+  </si>
+  <si>
+    <t>Store B</t>
+  </si>
+  <si>
+    <t>Wholesale</t>
+  </si>
+  <si>
+    <t>Eva</t>
+  </si>
+  <si>
+    <t>Online</t>
+  </si>
+  <si>
+    <t>Eric</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>Phone</t>
+  </si>
+  <si>
+    <t>Store A</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Alice</t>
+  </si>
+  <si>
+    <t>Gift Card</t>
+  </si>
+  <si>
+    <t>Sophie</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>Desk</t>
+  </si>
+  <si>
+    <t>Ryan</t>
+  </si>
+  <si>
+    <t>Central</t>
+  </si>
+  <si>
+    <t>Chair</t>
+  </si>
+  <si>
+    <t>Frank</t>
+  </si>
+  <si>
+    <t>Cameron</t>
+  </si>
+  <si>
+    <t>Store C</t>
+  </si>
+  <si>
+    <t>Carlos</t>
+  </si>
+  <si>
+    <t>Monitor</t>
+  </si>
+  <si>
+    <t>Store D</t>
+  </si>
+  <si>
+    <t>Diana</t>
+  </si>
+  <si>
+    <t>Credit Card</t>
+  </si>
+  <si>
+    <t>Debit Card</t>
+  </si>
+  <si>
+    <t>Cash</t>
+  </si>
+  <si>
+    <t>Bob</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>Wendy</t>
+  </si>
+  <si>
+    <t>Tablet</t>
+  </si>
+  <si>
+    <t>Printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Year </t>
+  </si>
+  <si>
+    <t>Total sales</t>
+  </si>
+  <si>
+    <t>Total Sale</t>
+  </si>
+  <si>
+    <t>Product Sales in 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laptop   </t>
+  </si>
+  <si>
+    <t>Total sales by Year</t>
+  </si>
+  <si>
+    <t>Average  (2023)</t>
+  </si>
+  <si>
+    <t>Average  (2024)</t>
+  </si>
+  <si>
+    <t>Average  (2025)</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>Sale count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Percentage of sale </t>
+  </si>
+  <si>
+    <t>Total sale price</t>
+  </si>
+  <si>
+    <t>Average</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="2">
+    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0.00"/>
+  </numFmts>
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -189,8 +380,46 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="23">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -221,8 +450,110 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF002060"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -245,11 +576,23 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -264,6 +607,7 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -273,13 +617,431 @@
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="1" fillId="14" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="172" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{838E1F74-091B-422A-8F25-11DC4903382E}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="35">
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="9" tint="-0.25098422193060094"/>
+          </stop>
+          <stop position="1">
+            <color theme="8" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="9" tint="-0.25098422193060094"/>
+          </stop>
+          <stop position="1">
+            <color theme="9" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FF10A872"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFFF00"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="5" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="5" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="9" tint="-0.25098422193060094"/>
+          </stop>
+          <stop position="1">
+            <color theme="8" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="9" tint="-0.25098422193060094"/>
+          </stop>
+          <stop position="1">
+            <color theme="9" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FF10A872"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFFFF00"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="270">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="9" tint="-0.25098422193060094"/>
+          </stop>
+          <stop position="1">
+            <color theme="8" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="9" tint="-0.25098422193060094"/>
+          </stop>
+          <stop position="1">
+            <color theme="9" tint="-0.49803155613879818"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="270">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF7030A0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="5" tint="0.59999389629810485"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FF4472C4"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FF10A872"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -2696,54 +3458,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="35.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="8"/>
-      <c r="C1" s="8"/>
-      <c r="D1" s="8"/>
-      <c r="E1" s="8"/>
-      <c r="F1" s="8"/>
-      <c r="G1" s="8"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="8"/>
-      <c r="L1" s="8"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
+      <c r="L1" s="9"/>
     </row>
     <row r="2" spans="1:12" ht="28.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="C2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="7" t="s">
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="J2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="K2" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7"/>
-      <c r="B3" s="7"/>
+      <c r="A3" s="8"/>
+      <c r="B3" s="8"/>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
@@ -2759,11 +3521,11 @@
       <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-      <c r="J3" s="7"/>
-      <c r="K3" s="7"/>
-      <c r="L3" s="7"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8"/>
+      <c r="L3" s="8"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
@@ -2998,6 +3760,3141 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BD969E-335E-4BAE-AA07-B8473F045CD1}">
+  <dimension ref="A1:O92"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="3" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" customWidth="1"/>
+    <col min="5" max="5" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="13.4140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.75" customWidth="1"/>
+    <col min="11" max="11" width="18.9140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A1" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="O1" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A2" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D2" s="10">
+        <v>14</v>
+      </c>
+      <c r="E2" s="10">
+        <v>2000</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H2" s="10">
+        <v>0</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" s="10">
+        <v>0</v>
+      </c>
+      <c r="L2" s="12">
+        <v>44980</v>
+      </c>
+      <c r="M2" s="12">
+        <v>44984</v>
+      </c>
+      <c r="N2" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2">
+        <f>PRODUCT(D2,E2)</f>
+        <v>28000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A3" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B3" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="10">
+        <v>1</v>
+      </c>
+      <c r="E3" s="10">
+        <v>544.01</v>
+      </c>
+      <c r="F3" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H3" s="10">
+        <v>0</v>
+      </c>
+      <c r="I3" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K3" s="10">
+        <v>0</v>
+      </c>
+      <c r="L3" s="12">
+        <v>45645</v>
+      </c>
+      <c r="M3" s="12">
+        <v>45654</v>
+      </c>
+      <c r="N3" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O3">
+        <f t="shared" ref="O3:O50" si="0">PRODUCT(D3,E3)</f>
+        <v>544.01</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A4" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="10">
+        <v>14</v>
+      </c>
+      <c r="E4" s="10">
+        <v>346.18</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J4" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="10">
+        <v>0</v>
+      </c>
+      <c r="L4" s="12">
+        <v>45056</v>
+      </c>
+      <c r="M4" s="12">
+        <v>45065</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O4">
+        <f t="shared" si="0"/>
+        <v>4846.5200000000004</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A5" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="10">
+        <v>18</v>
+      </c>
+      <c r="E5" s="10">
+        <v>384.82</v>
+      </c>
+      <c r="F5" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J5" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K5" s="10">
+        <v>0</v>
+      </c>
+      <c r="L5" s="12">
+        <v>45714</v>
+      </c>
+      <c r="M5" s="12">
+        <v>45718</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O5">
+        <f t="shared" si="0"/>
+        <v>6926.76</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A6" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="10">
+        <v>18</v>
+      </c>
+      <c r="E6" s="10">
+        <v>237.76</v>
+      </c>
+      <c r="F6" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H6" s="10">
+        <v>0</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K6" s="10">
+        <v>0</v>
+      </c>
+      <c r="L6" s="12">
+        <v>45101</v>
+      </c>
+      <c r="M6" s="12">
+        <v>45104</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6">
+        <f t="shared" si="0"/>
+        <v>4279.68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A7" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="10">
+        <v>2</v>
+      </c>
+      <c r="E7" s="10">
+        <v>385.09</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H7" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J7" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K7" s="10">
+        <v>0</v>
+      </c>
+      <c r="L7" s="12">
+        <v>45342</v>
+      </c>
+      <c r="M7" s="12">
+        <v>45352</v>
+      </c>
+      <c r="N7" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O7">
+        <f t="shared" si="0"/>
+        <v>770.18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A8" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="10">
+        <v>7</v>
+      </c>
+      <c r="E8" s="10">
+        <v>17.5</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H8" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J8" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K8" s="10">
+        <v>0</v>
+      </c>
+      <c r="L8" s="12">
+        <v>44937</v>
+      </c>
+      <c r="M8" s="12">
+        <v>44940</v>
+      </c>
+      <c r="N8" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O8">
+        <f t="shared" si="0"/>
+        <v>122.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A9" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D9" s="10">
+        <v>3</v>
+      </c>
+      <c r="E9" s="10">
+        <v>330.22</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H9" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K9" s="10">
+        <v>0</v>
+      </c>
+      <c r="L9" s="12">
+        <v>44935</v>
+      </c>
+      <c r="M9" s="12">
+        <v>44937</v>
+      </c>
+      <c r="N9" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O9">
+        <f t="shared" si="0"/>
+        <v>990.66000000000008</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A10" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D10" s="10">
+        <v>3</v>
+      </c>
+      <c r="E10" s="10">
+        <v>432.04</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J10" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K10" s="10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="12">
+        <v>45581</v>
+      </c>
+      <c r="M10" s="12">
+        <v>45583</v>
+      </c>
+      <c r="N10" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O10">
+        <f t="shared" si="0"/>
+        <v>1296.1200000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A11" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D11" s="10">
+        <v>5</v>
+      </c>
+      <c r="E11" s="10">
+        <v>323.27999999999997</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H11" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="10">
+        <v>0</v>
+      </c>
+      <c r="L11" s="12">
+        <v>45721</v>
+      </c>
+      <c r="M11" s="12">
+        <v>45729</v>
+      </c>
+      <c r="N11" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O11">
+        <f t="shared" si="0"/>
+        <v>1616.3999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A12" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B12" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="10">
+        <v>15</v>
+      </c>
+      <c r="E12" s="10">
+        <v>523.29</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J12" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K12" s="10">
+        <v>0</v>
+      </c>
+      <c r="L12" s="12">
+        <v>45392</v>
+      </c>
+      <c r="M12" s="12">
+        <v>45399</v>
+      </c>
+      <c r="N12" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O12">
+        <f t="shared" si="0"/>
+        <v>7849.3499999999995</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A13" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B13" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C13" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="10">
+        <v>19</v>
+      </c>
+      <c r="E13" s="10">
+        <v>207.35</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H13" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="10">
+        <v>1</v>
+      </c>
+      <c r="L13" s="12">
+        <v>45485</v>
+      </c>
+      <c r="M13" s="12">
+        <v>45491</v>
+      </c>
+      <c r="N13" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O13">
+        <f t="shared" si="0"/>
+        <v>3939.65</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A14" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B14" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C14" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="10">
+        <v>1</v>
+      </c>
+      <c r="E14" s="10">
+        <v>120.53</v>
+      </c>
+      <c r="F14" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H14" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I14" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J14" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K14" s="10">
+        <v>0</v>
+      </c>
+      <c r="L14" s="12">
+        <v>45128</v>
+      </c>
+      <c r="M14" s="12">
+        <v>45138</v>
+      </c>
+      <c r="N14" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O14">
+        <f t="shared" si="0"/>
+        <v>120.53</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A15" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B15" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="10">
+        <v>1</v>
+      </c>
+      <c r="E15" s="10">
+        <v>157.83000000000001</v>
+      </c>
+      <c r="F15" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H15" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I15" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K15" s="10">
+        <v>0</v>
+      </c>
+      <c r="L15" s="12">
+        <v>45675</v>
+      </c>
+      <c r="M15" s="12">
+        <v>45679</v>
+      </c>
+      <c r="N15" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O15">
+        <f t="shared" si="0"/>
+        <v>157.83000000000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A16" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="10">
+        <v>15</v>
+      </c>
+      <c r="E16" s="10">
+        <v>220.3</v>
+      </c>
+      <c r="F16" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I16" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J16" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K16" s="10">
+        <v>0</v>
+      </c>
+      <c r="L16" s="12">
+        <v>45634</v>
+      </c>
+      <c r="M16" s="12">
+        <v>45641</v>
+      </c>
+      <c r="N16" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O16">
+        <f t="shared" si="0"/>
+        <v>3304.5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A17" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D17" s="10">
+        <v>17</v>
+      </c>
+      <c r="E17" s="10">
+        <v>162.96</v>
+      </c>
+      <c r="F17" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K17" s="10">
+        <v>0</v>
+      </c>
+      <c r="L17" s="12">
+        <v>45788</v>
+      </c>
+      <c r="M17" s="12">
+        <v>45794</v>
+      </c>
+      <c r="N17" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O17">
+        <f t="shared" si="0"/>
+        <v>2770.32</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A18" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B18" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="10">
+        <v>19</v>
+      </c>
+      <c r="E18" s="10">
+        <v>236.11</v>
+      </c>
+      <c r="F18" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H18" s="10">
+        <v>0</v>
+      </c>
+      <c r="I18" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J18" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K18" s="10">
+        <v>0</v>
+      </c>
+      <c r="L18" s="12">
+        <v>44983</v>
+      </c>
+      <c r="M18" s="12">
+        <v>44989</v>
+      </c>
+      <c r="N18" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O18">
+        <f t="shared" si="0"/>
+        <v>4486.09</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A19" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B19" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C19" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="10">
+        <v>11</v>
+      </c>
+      <c r="E19" s="10">
+        <v>573.14</v>
+      </c>
+      <c r="F19" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H19" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J19" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K19" s="10">
+        <v>0</v>
+      </c>
+      <c r="L19" s="12">
+        <v>45440</v>
+      </c>
+      <c r="M19" s="12">
+        <v>45444</v>
+      </c>
+      <c r="N19" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O19">
+        <f t="shared" si="0"/>
+        <v>6304.54</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A20" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B20" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D20" s="10">
+        <v>20</v>
+      </c>
+      <c r="E20" s="10">
+        <v>519.04</v>
+      </c>
+      <c r="F20" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I20" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J20" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K20" s="10">
+        <v>0</v>
+      </c>
+      <c r="L20" s="12">
+        <v>45260</v>
+      </c>
+      <c r="M20" s="12">
+        <v>45268</v>
+      </c>
+      <c r="N20" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O20">
+        <f t="shared" si="0"/>
+        <v>10380.799999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A21" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D21" s="10">
+        <v>14</v>
+      </c>
+      <c r="E21" s="10">
+        <v>30.83</v>
+      </c>
+      <c r="F21" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H21" s="10">
+        <v>0</v>
+      </c>
+      <c r="I21" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K21" s="10">
+        <v>1</v>
+      </c>
+      <c r="L21" s="12">
+        <v>45099</v>
+      </c>
+      <c r="M21" s="12">
+        <v>45109</v>
+      </c>
+      <c r="N21" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O21">
+        <f t="shared" si="0"/>
+        <v>431.62</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A22" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B22" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D22" s="10">
+        <v>10</v>
+      </c>
+      <c r="E22" s="10">
+        <v>319.05</v>
+      </c>
+      <c r="F22" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H22" s="10">
+        <v>0</v>
+      </c>
+      <c r="I22" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K22" s="10">
+        <v>0</v>
+      </c>
+      <c r="L22" s="12">
+        <v>45813</v>
+      </c>
+      <c r="M22" s="12">
+        <v>45816</v>
+      </c>
+      <c r="N22" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="0"/>
+        <v>3190.5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A23" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D23" s="10">
+        <v>14</v>
+      </c>
+      <c r="E23" s="10">
+        <v>312.79000000000002</v>
+      </c>
+      <c r="F23" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H23" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I23" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J23" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K23" s="10">
+        <v>1</v>
+      </c>
+      <c r="L23" s="12">
+        <v>44988</v>
+      </c>
+      <c r="M23" s="12">
+        <v>44993</v>
+      </c>
+      <c r="N23" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O23">
+        <f t="shared" si="0"/>
+        <v>4379.0600000000004</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A24" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D24" s="10">
+        <v>14</v>
+      </c>
+      <c r="E24" s="10">
+        <v>395.45</v>
+      </c>
+      <c r="F24" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="10">
+        <v>0</v>
+      </c>
+      <c r="I24" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J24" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K24" s="10">
+        <v>1</v>
+      </c>
+      <c r="L24" s="12">
+        <v>45340</v>
+      </c>
+      <c r="M24" s="12">
+        <v>45344</v>
+      </c>
+      <c r="N24" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O24">
+        <f t="shared" si="0"/>
+        <v>5536.3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A25" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="10">
+        <v>12</v>
+      </c>
+      <c r="E25" s="10">
+        <v>472.72</v>
+      </c>
+      <c r="F25" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H25" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I25" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J25" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K25" s="10">
+        <v>0</v>
+      </c>
+      <c r="L25" s="12">
+        <v>45144</v>
+      </c>
+      <c r="M25" s="12">
+        <v>45152</v>
+      </c>
+      <c r="N25" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O25">
+        <f t="shared" si="0"/>
+        <v>5672.64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A26" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B26" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D26" s="10">
+        <v>5</v>
+      </c>
+      <c r="E26" s="10">
+        <v>288.01</v>
+      </c>
+      <c r="F26" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H26" s="10">
+        <v>0</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J26" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K26" s="10">
+        <v>0</v>
+      </c>
+      <c r="L26" s="12">
+        <v>45435</v>
+      </c>
+      <c r="M26" s="12">
+        <v>45442</v>
+      </c>
+      <c r="N26" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O26">
+        <f t="shared" si="0"/>
+        <v>1440.05</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A27" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B27" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D27" s="10">
+        <v>13</v>
+      </c>
+      <c r="E27" s="10">
+        <v>562.29</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H27" s="10">
+        <v>0</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J27" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K27" s="10">
+        <v>0</v>
+      </c>
+      <c r="L27" s="12">
+        <v>45222</v>
+      </c>
+      <c r="M27" s="12">
+        <v>45227</v>
+      </c>
+      <c r="N27" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O27">
+        <f t="shared" si="0"/>
+        <v>7309.7699999999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A28" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B28" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D28" s="10">
+        <v>1</v>
+      </c>
+      <c r="E28" s="10">
+        <v>101.73</v>
+      </c>
+      <c r="F28" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="10">
+        <v>0</v>
+      </c>
+      <c r="I28" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J28" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K28" s="10">
+        <v>0</v>
+      </c>
+      <c r="L28" s="12">
+        <v>45824</v>
+      </c>
+      <c r="M28" s="12">
+        <v>45833</v>
+      </c>
+      <c r="N28" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O28">
+        <f t="shared" si="0"/>
+        <v>101.73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A29" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B29" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C29" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="10">
+        <v>4</v>
+      </c>
+      <c r="E29" s="10">
+        <v>279.49</v>
+      </c>
+      <c r="F29" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H29" s="10">
+        <v>0</v>
+      </c>
+      <c r="I29" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J29" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K29" s="10">
+        <v>0</v>
+      </c>
+      <c r="L29" s="12">
+        <v>44988</v>
+      </c>
+      <c r="M29" s="12">
+        <v>44993</v>
+      </c>
+      <c r="N29" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O29">
+        <f t="shared" si="0"/>
+        <v>1117.96</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A30" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B30" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C30" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D30" s="10">
+        <v>1</v>
+      </c>
+      <c r="E30" s="10">
+        <v>178.55</v>
+      </c>
+      <c r="F30" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H30" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I30" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J30" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K30" s="10">
+        <v>1</v>
+      </c>
+      <c r="L30" s="12">
+        <v>45614</v>
+      </c>
+      <c r="M30" s="12">
+        <v>45617</v>
+      </c>
+      <c r="N30" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O30">
+        <f t="shared" si="0"/>
+        <v>178.55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A31" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B31" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C31" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="10">
+        <v>1</v>
+      </c>
+      <c r="E31" s="10">
+        <v>472.07</v>
+      </c>
+      <c r="F31" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H31" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I31" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J31" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K31" s="10">
+        <v>0</v>
+      </c>
+      <c r="L31" s="12">
+        <v>45055</v>
+      </c>
+      <c r="M31" s="12">
+        <v>45063</v>
+      </c>
+      <c r="N31" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O31">
+        <f t="shared" si="0"/>
+        <v>472.07</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A32" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="10">
+        <v>12</v>
+      </c>
+      <c r="E32" s="10">
+        <v>306.29000000000002</v>
+      </c>
+      <c r="F32" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H32" s="10">
+        <v>0</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J32" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K32" s="10">
+        <v>0</v>
+      </c>
+      <c r="L32" s="12">
+        <v>45633</v>
+      </c>
+      <c r="M32" s="12">
+        <v>45640</v>
+      </c>
+      <c r="N32" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O32">
+        <f t="shared" si="0"/>
+        <v>3675.4800000000005</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A33" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B33" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="D33" s="10">
+        <v>7</v>
+      </c>
+      <c r="E33" s="10">
+        <v>434.77</v>
+      </c>
+      <c r="F33" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I33" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J33" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K33" s="10">
+        <v>0</v>
+      </c>
+      <c r="L33" s="12">
+        <v>45335</v>
+      </c>
+      <c r="M33" s="12">
+        <v>45337</v>
+      </c>
+      <c r="N33" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O33">
+        <f t="shared" si="0"/>
+        <v>3043.39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A34" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B34" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C34" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="10">
+        <v>6</v>
+      </c>
+      <c r="E34" s="10">
+        <v>64.98</v>
+      </c>
+      <c r="F34" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H34" s="10">
+        <v>0</v>
+      </c>
+      <c r="I34" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J34" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K34" s="10">
+        <v>0</v>
+      </c>
+      <c r="L34" s="12">
+        <v>45725</v>
+      </c>
+      <c r="M34" s="12">
+        <v>45731</v>
+      </c>
+      <c r="N34" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O34">
+        <f t="shared" si="0"/>
+        <v>389.88</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A35" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B35" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C35" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="10">
+        <v>17</v>
+      </c>
+      <c r="E35" s="10">
+        <v>476.49</v>
+      </c>
+      <c r="F35" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H35" s="10">
+        <v>0</v>
+      </c>
+      <c r="I35" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J35" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K35" s="10">
+        <v>0</v>
+      </c>
+      <c r="L35" s="12">
+        <v>45021</v>
+      </c>
+      <c r="M35" s="12">
+        <v>45027</v>
+      </c>
+      <c r="N35" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O35">
+        <f t="shared" si="0"/>
+        <v>8100.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A36" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B36" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D36" s="10">
+        <v>4</v>
+      </c>
+      <c r="E36" s="10">
+        <v>559.72</v>
+      </c>
+      <c r="F36" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I36" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J36" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K36" s="10">
+        <v>0</v>
+      </c>
+      <c r="L36" s="12">
+        <v>45785</v>
+      </c>
+      <c r="M36" s="12">
+        <v>45789</v>
+      </c>
+      <c r="N36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O36">
+        <f t="shared" si="0"/>
+        <v>2238.88</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A37" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="10">
+        <v>14</v>
+      </c>
+      <c r="E37" s="10">
+        <v>82.14</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H37" s="10">
+        <v>0</v>
+      </c>
+      <c r="I37" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J37" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="K37" s="10">
+        <v>0</v>
+      </c>
+      <c r="L37" s="12">
+        <v>45172</v>
+      </c>
+      <c r="M37" s="12">
+        <v>45180</v>
+      </c>
+      <c r="N37" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O37">
+        <f t="shared" si="0"/>
+        <v>1149.96</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A38" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B38" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D38" s="10">
+        <v>9</v>
+      </c>
+      <c r="E38" s="10">
+        <v>343.21</v>
+      </c>
+      <c r="F38" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H38" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I38" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J38" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K38" s="10">
+        <v>0</v>
+      </c>
+      <c r="L38" s="12">
+        <v>45737</v>
+      </c>
+      <c r="M38" s="12">
+        <v>45744</v>
+      </c>
+      <c r="N38" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O38">
+        <f t="shared" si="0"/>
+        <v>3088.89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A39" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B39" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D39" s="10">
+        <v>7</v>
+      </c>
+      <c r="E39" s="10">
+        <v>301.01</v>
+      </c>
+      <c r="F39" s="10" t="s">
+        <v>60</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H39" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I39" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="J39" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K39" s="10">
+        <v>1</v>
+      </c>
+      <c r="L39" s="12">
+        <v>45828</v>
+      </c>
+      <c r="M39" s="12">
+        <v>45838</v>
+      </c>
+      <c r="N39" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O39">
+        <f t="shared" si="0"/>
+        <v>2107.0699999999997</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A40" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B40" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="10">
+        <v>14</v>
+      </c>
+      <c r="E40" s="10">
+        <v>428.13</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H40" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I40" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="J40" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="K40" s="10">
+        <v>1</v>
+      </c>
+      <c r="L40" s="12">
+        <v>45337</v>
+      </c>
+      <c r="M40" s="12">
+        <v>45347</v>
+      </c>
+      <c r="N40" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O40">
+        <f t="shared" si="0"/>
+        <v>5993.82</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A41" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B41" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D41" s="10">
+        <v>2</v>
+      </c>
+      <c r="E41" s="10">
+        <v>503.28</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H41" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I41" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J41" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K41" s="10">
+        <v>0</v>
+      </c>
+      <c r="L41" s="12">
+        <v>45086</v>
+      </c>
+      <c r="M41" s="12">
+        <v>45094</v>
+      </c>
+      <c r="N41" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O41">
+        <f t="shared" si="0"/>
+        <v>1006.56</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A42" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B42" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="10">
+        <v>5</v>
+      </c>
+      <c r="E42" s="10">
+        <v>470.32</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H42" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J42" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K42" s="10">
+        <v>0</v>
+      </c>
+      <c r="L42" s="12">
+        <v>45148</v>
+      </c>
+      <c r="M42" s="12">
+        <v>45152</v>
+      </c>
+      <c r="N42" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O42">
+        <f t="shared" si="0"/>
+        <v>2351.6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A43" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B43" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="10">
+        <v>20</v>
+      </c>
+      <c r="E43" s="10">
+        <v>65.17</v>
+      </c>
+      <c r="F43" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H43" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I43" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J43" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K43" s="10">
+        <v>0</v>
+      </c>
+      <c r="L43" s="12">
+        <v>45459</v>
+      </c>
+      <c r="M43" s="12">
+        <v>45468</v>
+      </c>
+      <c r="N43" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O43">
+        <f t="shared" si="0"/>
+        <v>1303.4000000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A44" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B44" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C44" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="10">
+        <v>12</v>
+      </c>
+      <c r="E44" s="10">
+        <v>36.17</v>
+      </c>
+      <c r="F44" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H44" s="10">
+        <v>0</v>
+      </c>
+      <c r="I44" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J44" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K44" s="10">
+        <v>0</v>
+      </c>
+      <c r="L44" s="12">
+        <v>45130</v>
+      </c>
+      <c r="M44" s="12">
+        <v>45133</v>
+      </c>
+      <c r="N44" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O44">
+        <f t="shared" si="0"/>
+        <v>434.04</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A45" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B45" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="C45" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D45" s="10">
+        <v>4</v>
+      </c>
+      <c r="E45" s="10">
+        <v>459.31</v>
+      </c>
+      <c r="F45" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>61</v>
+      </c>
+      <c r="H45" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I45" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="J45" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K45" s="10">
+        <v>1</v>
+      </c>
+      <c r="L45" s="12">
+        <v>45066</v>
+      </c>
+      <c r="M45" s="12">
+        <v>45073</v>
+      </c>
+      <c r="N45" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="O45">
+        <f t="shared" si="0"/>
+        <v>1837.24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A46" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B46" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C46" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="D46" s="10">
+        <v>2</v>
+      </c>
+      <c r="E46" s="10">
+        <v>416.06</v>
+      </c>
+      <c r="F46" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H46" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="I46" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J46" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="K46" s="10">
+        <v>0</v>
+      </c>
+      <c r="L46" s="12">
+        <v>45107</v>
+      </c>
+      <c r="M46" s="12">
+        <v>45111</v>
+      </c>
+      <c r="N46" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O46">
+        <f t="shared" si="0"/>
+        <v>832.12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A47" s="14">
+        <v>2023</v>
+      </c>
+      <c r="B47" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="C47" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D47" s="10">
+        <v>16</v>
+      </c>
+      <c r="E47" s="10">
+        <v>302.58</v>
+      </c>
+      <c r="F47" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H47" s="10">
+        <v>0</v>
+      </c>
+      <c r="I47" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="J47" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K47" s="10">
+        <v>1</v>
+      </c>
+      <c r="L47" s="12">
+        <v>45447</v>
+      </c>
+      <c r="M47" s="12">
+        <v>45457</v>
+      </c>
+      <c r="N47" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="O47">
+        <f t="shared" si="0"/>
+        <v>4841.28</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A48" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B48" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D48" s="10">
+        <v>11</v>
+      </c>
+      <c r="E48" s="10">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="F48" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H48" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I48" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J48" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="K48" s="10">
+        <v>0</v>
+      </c>
+      <c r="L48" s="12">
+        <v>45691</v>
+      </c>
+      <c r="M48" s="12">
+        <v>45693</v>
+      </c>
+      <c r="N48" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="O48">
+        <f t="shared" si="0"/>
+        <v>364.43</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A49" s="14">
+        <v>2025</v>
+      </c>
+      <c r="B49" s="10" t="s">
+        <v>58</v>
+      </c>
+      <c r="C49" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" s="10">
+        <v>8</v>
+      </c>
+      <c r="E49" s="10">
+        <v>582.52</v>
+      </c>
+      <c r="F49" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H49" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="I49" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="J49" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K49" s="10">
+        <v>0</v>
+      </c>
+      <c r="L49" s="12">
+        <v>45300</v>
+      </c>
+      <c r="M49" s="12">
+        <v>45304</v>
+      </c>
+      <c r="N49" s="10" t="s">
+        <v>64</v>
+      </c>
+      <c r="O49">
+        <f t="shared" si="0"/>
+        <v>4660.16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A50" s="14">
+        <v>2024</v>
+      </c>
+      <c r="B50" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="D50" s="10">
+        <v>5</v>
+      </c>
+      <c r="E50" s="10">
+        <v>165.15</v>
+      </c>
+      <c r="F50" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="H50" s="10">
+        <v>0.1</v>
+      </c>
+      <c r="I50" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="J50" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="K50" s="10">
+        <v>0</v>
+      </c>
+      <c r="L50" s="12">
+        <v>45365</v>
+      </c>
+      <c r="M50" s="12">
+        <v>45367</v>
+      </c>
+      <c r="N50" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="O50">
+        <f t="shared" si="0"/>
+        <v>825.75</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>92</v>
+      </c>
+      <c r="B54" s="15">
+        <v>2024</v>
+      </c>
+      <c r="C54" s="15"/>
+    </row>
+    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>30</v>
+      </c>
+      <c r="B55">
+        <f>SUMIF(A2:A50,B54,O2:O50)</f>
+        <v>56788.600000000006</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>92</v>
+      </c>
+      <c r="B57">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>45</v>
+      </c>
+      <c r="B58" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>94</v>
+      </c>
+      <c r="B59">
+        <f>SUMIFS(O2:O50,A2:A50,B57,B2:B50,B58)</f>
+        <v>21630.219999999998</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A61" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="B61" s="16"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61">
+        <v>2023</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>96</v>
+      </c>
+      <c r="B62">
+        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM(A62),$A$2:$A$50,$E$61)</f>
+        <v>1838.6799999999998</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>91</v>
+      </c>
+      <c r="B63">
+        <f t="shared" ref="B63:B66" si="1">SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM(A63),$A$2:$A$50,$E$61)</f>
+        <v>2351.6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>76</v>
+      </c>
+      <c r="B64">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65">
+        <f t="shared" si="1"/>
+        <v>12591.11</v>
+      </c>
+    </row>
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A66" t="s">
+        <v>90</v>
+      </c>
+      <c r="B66">
+        <f t="shared" si="1"/>
+        <v>4841.28</v>
+      </c>
+    </row>
+    <row r="69" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="17" t="s">
+        <v>97</v>
+      </c>
+      <c r="B69" s="17"/>
+      <c r="C69" s="17"/>
+      <c r="D69" s="17"/>
+      <c r="E69" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="F69" s="20"/>
+      <c r="G69" s="20"/>
+      <c r="H69" s="28" t="s">
+        <v>103</v>
+      </c>
+      <c r="I69" s="28"/>
+      <c r="J69" s="28"/>
+    </row>
+    <row r="70" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="18">
+        <v>2023</v>
+      </c>
+      <c r="C70" s="18">
+        <v>2024</v>
+      </c>
+      <c r="D70" s="18">
+        <v>2025</v>
+      </c>
+      <c r="E70" s="21">
+        <v>2023</v>
+      </c>
+      <c r="F70" s="21">
+        <v>2024</v>
+      </c>
+      <c r="G70" s="21">
+        <v>2025</v>
+      </c>
+      <c r="H70" s="21">
+        <v>2023</v>
+      </c>
+      <c r="I70" s="21">
+        <v>2024</v>
+      </c>
+      <c r="J70" s="21">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="24" t="s">
+        <v>59</v>
+      </c>
+      <c r="B71" s="31">
+        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
+        <v>1838.6799999999998</v>
+      </c>
+      <c r="C71" s="31">
+        <f t="shared" ref="C71:D75" si="2">SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,C$70)</f>
+        <v>33536.300000000003</v>
+      </c>
+      <c r="D71" s="31">
+        <f t="shared" si="2"/>
+        <v>10771.32</v>
+      </c>
+      <c r="E71" s="27">
+        <f>COUNTIFS($C$2:$C$50,TRIM($A71),$A$2:$A$50,E$70)</f>
+        <v>2</v>
+      </c>
+      <c r="F71" s="27">
+        <f t="shared" ref="F71:G71" si="3">COUNTIFS($C$2:$C$50,TRIM($A71),$A$2:$A$50,F$70)</f>
+        <v>2</v>
+      </c>
+      <c r="G71" s="27">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="H71" s="29">
+        <f>E71/SUM(E$71:E$75)</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I71" s="29">
+        <f t="shared" ref="I71:J75" si="4">F71/SUM(F$71:F$75)</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="J71" s="29">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="24" t="s">
+        <v>91</v>
+      </c>
+      <c r="B72" s="31">
+        <f t="shared" ref="B72:B75" si="5">SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,B$70)</f>
+        <v>2351.6</v>
+      </c>
+      <c r="C72" s="31">
+        <f t="shared" si="2"/>
+        <v>1303.4000000000001</v>
+      </c>
+      <c r="D72" s="31">
+        <f t="shared" si="2"/>
+        <v>7831.0599999999995</v>
+      </c>
+      <c r="E72" s="27">
+        <f t="shared" ref="D72:G75" si="6">COUNTIFS($C$2:$C$50,TRIM($A72),$A$2:$A$50,E$70)</f>
+        <v>1</v>
+      </c>
+      <c r="F72" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="G72" s="27">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="H72" s="29">
+        <f t="shared" ref="H72:H75" si="7">E72/SUM(E$71:E$75)</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I72" s="29">
+        <f t="shared" si="4"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="J72" s="29">
+        <f t="shared" si="4"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="24" t="s">
+        <v>76</v>
+      </c>
+      <c r="B73" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="C73" s="31">
+        <f t="shared" si="2"/>
+        <v>7149.380000000001</v>
+      </c>
+      <c r="D73" s="31">
+        <f t="shared" si="2"/>
+        <v>14896.43</v>
+      </c>
+      <c r="E73" s="27">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="27">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G73" s="27">
+        <f t="shared" si="6"/>
+        <v>7</v>
+      </c>
+      <c r="H73" s="29">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="29">
+        <f t="shared" si="4"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="J73" s="29">
+        <f t="shared" si="4"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="24" t="s">
+        <v>73</v>
+      </c>
+      <c r="B74" s="31">
+        <f t="shared" si="5"/>
+        <v>12591.11</v>
+      </c>
+      <c r="C74" s="31">
+        <f t="shared" si="2"/>
+        <v>12411.22</v>
+      </c>
+      <c r="D74" s="31">
+        <f t="shared" si="2"/>
+        <v>14386.29</v>
+      </c>
+      <c r="E74" s="27">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="F74" s="27">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="G74" s="27">
+        <f t="shared" si="6"/>
+        <v>4</v>
+      </c>
+      <c r="H74" s="29">
+        <f t="shared" si="7"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="I74" s="29">
+        <f t="shared" si="4"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="J74" s="29">
+        <f t="shared" si="4"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="24" t="s">
+        <v>90</v>
+      </c>
+      <c r="B75" s="31">
+        <f t="shared" si="5"/>
+        <v>4841.28</v>
+      </c>
+      <c r="C75" s="31">
+        <f t="shared" si="2"/>
+        <v>1622.03</v>
+      </c>
+      <c r="D75" s="31">
+        <f t="shared" si="2"/>
+        <v>8493.4700000000012</v>
+      </c>
+      <c r="E75" s="27">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="F75" s="27">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="G75" s="27">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="H75" s="29">
+        <f t="shared" si="7"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I75" s="29">
+        <f t="shared" si="4"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="J75" s="29">
+        <f t="shared" si="4"/>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
+    </row>
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="D77" s="30" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="25">
+        <f>SUM(E71:E75)</f>
+        <v>7</v>
+      </c>
+      <c r="F77" s="25">
+        <f>SUM(F71:F75)</f>
+        <v>11</v>
+      </c>
+      <c r="G77" s="25">
+        <f>SUM(G71:G75)</f>
+        <v>20</v>
+      </c>
+      <c r="H77" s="26">
+        <f>SUM(H71:H75)</f>
+        <v>1</v>
+      </c>
+      <c r="I77" s="26">
+        <f t="shared" ref="I77:J77" si="8">SUM(I71:I75)</f>
+        <v>1</v>
+      </c>
+      <c r="J77" s="26">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A80" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="B80" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="C80" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E80" s="23" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A81" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
+        <v>919.33999999999992</v>
+      </c>
+      <c r="B81" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,C$70)</f>
+        <v>16768.150000000001</v>
+      </c>
+      <c r="C81" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,D$70)</f>
+        <v>2692.83</v>
+      </c>
+      <c r="E81" s="22">
+        <f>IFERROR(A81,"Something went wrong")</f>
+        <v>919.33999999999992</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A82" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,B$70)</f>
+        <v>2351.6</v>
+      </c>
+      <c r="B82" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,C$70)</f>
+        <v>1303.4000000000001</v>
+      </c>
+      <c r="C82" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,D$70)</f>
+        <v>3915.5299999999997</v>
+      </c>
+      <c r="E82" s="22">
+        <f>IFERROR(A82,"Something went wrong")</f>
+        <v>2351.6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A83" s="22" t="e">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A73),$A$2:$A$50,B$70)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="B83" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A73),$A$2:$A$50,C$70)</f>
+        <v>3574.6900000000005</v>
+      </c>
+      <c r="C83" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A73),$A$2:$A$50,D$70)</f>
+        <v>2128.0614285714287</v>
+      </c>
+      <c r="E83" s="22" t="str">
+        <f>IFERROR(A83,"Something went wrong")</f>
+        <v>Something went wrong</v>
+      </c>
+    </row>
+    <row r="84" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A84" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A74),$A$2:$A$50,B$70)</f>
+        <v>4197.0366666666669</v>
+      </c>
+      <c r="B84" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A74),$A$2:$A$50,C$70)</f>
+        <v>3102.8049999999998</v>
+      </c>
+      <c r="C84" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A74),$A$2:$A$50,D$70)</f>
+        <v>3596.5725000000002</v>
+      </c>
+      <c r="E84" s="22">
+        <f>IFERROR(A84,"Something went wrong")</f>
+        <v>4197.0366666666669</v>
+      </c>
+    </row>
+    <row r="85" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A85" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A75),$A$2:$A$50,B$70)</f>
+        <v>4841.28</v>
+      </c>
+      <c r="B85" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A75),$A$2:$A$50,C$70)</f>
+        <v>811.01499999999999</v>
+      </c>
+      <c r="C85" s="22">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A75),$A$2:$A$50,D$70)</f>
+        <v>2831.1566666666672</v>
+      </c>
+      <c r="E85" s="22">
+        <f>IFERROR(A85,"Something went wrong")</f>
+        <v>4841.28</v>
+      </c>
+    </row>
+    <row r="87" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
+    </row>
+    <row r="88" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A88" s="1"/>
+      <c r="B88" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C88" s="35"/>
+      <c r="D88" s="35"/>
+      <c r="E88" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="F88" s="36"/>
+      <c r="G88" s="36"/>
+      <c r="H88" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="I88" s="37"/>
+      <c r="J88" s="37"/>
+    </row>
+    <row r="89" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A89" s="1"/>
+      <c r="B89" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C89" s="38" t="s">
+        <v>104</v>
+      </c>
+      <c r="D89" s="38" t="s">
+        <v>105</v>
+      </c>
+      <c r="E89" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="F89" s="33" t="s">
+        <v>104</v>
+      </c>
+      <c r="G89" s="33" t="s">
+        <v>105</v>
+      </c>
+      <c r="H89" s="39" t="s">
+        <v>102</v>
+      </c>
+      <c r="I89" s="39" t="s">
+        <v>104</v>
+      </c>
+      <c r="J89" s="39" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="90" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A90" s="32">
+        <v>2023</v>
+      </c>
+      <c r="B90" s="34">
+        <f>COUNTIFS($C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A90)</f>
+        <v>2</v>
+      </c>
+      <c r="C90" s="34">
+        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,B$88,$A$2:$A$50,$A90)</f>
+        <v>1838.6799999999998</v>
+      </c>
+      <c r="D90" s="34">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A90)</f>
+        <v>919.33999999999992</v>
+      </c>
+      <c r="E90" s="34">
+        <f>COUNTIFS($C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A90)</f>
+        <v>0</v>
+      </c>
+      <c r="F90" s="34">
+        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,E$88,$A$2:$A$50,$A90)</f>
+        <v>0</v>
+      </c>
+      <c r="G90" s="34" t="e">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A90)</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H90" s="34">
+        <f>COUNTIFS($C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A90)</f>
+        <v>1</v>
+      </c>
+      <c r="I90" s="34">
+        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,H$88,$A$2:$A$50,$A90)</f>
+        <v>2351.6</v>
+      </c>
+      <c r="J90" s="34">
+        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A90)</f>
+        <v>2351.6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A91" s="32">
+        <v>2024</v>
+      </c>
+      <c r="B91" s="34">
+        <f t="shared" ref="B91:B92" si="9">COUNTIFS($C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A91)</f>
+        <v>2</v>
+      </c>
+      <c r="C91" s="34">
+        <f t="shared" ref="C91:C92" si="10">SUMIFS($O$2:$O$50,$C$2:$C$50,B$88,$A$2:$A$50,$A91)</f>
+        <v>33536.300000000003</v>
+      </c>
+      <c r="D91" s="34">
+        <f t="shared" ref="D91:D92" si="11">AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A91)</f>
+        <v>16768.150000000001</v>
+      </c>
+      <c r="E91" s="34">
+        <f t="shared" ref="E91:E92" si="12">COUNTIFS($C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A91)</f>
+        <v>2</v>
+      </c>
+      <c r="F91" s="34">
+        <f t="shared" ref="F91:F92" si="13">SUMIFS($O$2:$O$50,$C$2:$C$50,E$88,$A$2:$A$50,$A91)</f>
+        <v>7149.380000000001</v>
+      </c>
+      <c r="G91" s="34">
+        <f t="shared" ref="G91:G92" si="14">AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A91)</f>
+        <v>3574.6900000000005</v>
+      </c>
+      <c r="H91" s="34">
+        <f t="shared" ref="H91:H92" si="15">COUNTIFS($C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A91)</f>
+        <v>1</v>
+      </c>
+      <c r="I91" s="34">
+        <f t="shared" ref="I91:I92" si="16">SUMIFS($O$2:$O$50,$C$2:$C$50,H$88,$A$2:$A$50,$A91)</f>
+        <v>1303.4000000000001</v>
+      </c>
+      <c r="J91" s="34">
+        <f t="shared" ref="J91:J92" si="17">AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A91)</f>
+        <v>1303.4000000000001</v>
+      </c>
+    </row>
+    <row r="92" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A92" s="32">
+        <v>2025</v>
+      </c>
+      <c r="B92" s="34">
+        <f t="shared" si="9"/>
+        <v>4</v>
+      </c>
+      <c r="C92" s="34">
+        <f t="shared" si="10"/>
+        <v>10771.32</v>
+      </c>
+      <c r="D92" s="34">
+        <f t="shared" si="11"/>
+        <v>2692.83</v>
+      </c>
+      <c r="E92" s="34">
+        <f t="shared" si="12"/>
+        <v>7</v>
+      </c>
+      <c r="F92" s="34">
+        <f t="shared" si="13"/>
+        <v>14896.43</v>
+      </c>
+      <c r="G92" s="34">
+        <f t="shared" si="14"/>
+        <v>2128.0614285714287</v>
+      </c>
+      <c r="H92" s="34">
+        <f t="shared" si="15"/>
+        <v>2</v>
+      </c>
+      <c r="I92" s="34">
+        <f t="shared" si="16"/>
+        <v>7831.0599999999995</v>
+      </c>
+      <c r="J92" s="34">
+        <f t="shared" si="17"/>
+        <v>3915.5299999999997</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A69:D69"/>
+    <mergeCell ref="E69:G69"/>
+    <mergeCell ref="H69:J69"/>
+    <mergeCell ref="B88:D88"/>
+    <mergeCell ref="E88:G88"/>
+    <mergeCell ref="H88:J88"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E81:E85">
+    <cfRule type="expression" dxfId="5" priority="11">
+      <formula>ISERROR(A81)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H71:J75">
+    <cfRule type="expression" dxfId="4" priority="5">
+      <formula>H71=MAX(H$71:H$75)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E71:G75">
+    <cfRule type="expression" dxfId="3" priority="4">
+      <formula>E71=MAX(E$71:E$75)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B71:D75">
+    <cfRule type="expression" dxfId="2" priority="3">
+      <formula>B71=MAX(B$71:B$75)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A81:A85">
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>A81=MAX(A$81:A$85)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B81:C85">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>B81=MAX(B$81:B$85)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC1EC01-3558-4CAF-8FA5-3C02BC76403B}">
   <dimension ref="C1:L72"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -3007,17 +6904,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
     </row>
     <row r="2" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D2" t="s">
@@ -3495,7 +7392,7 @@
         <v>150000</v>
       </c>
       <c r="F61">
-        <f t="shared" ref="F60:F61" si="4">E61*($K$58/100)</f>
+        <f t="shared" ref="F61" si="4">E61*($K$58/100)</f>
         <v>15000</v>
       </c>
     </row>
@@ -3610,7 +7507,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08F756C-290F-404E-81ED-2B88E96B5E6A}">
   <dimension ref="B2:F7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -3626,7 +7523,7 @@
       </c>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="F4" s="9">
+      <c r="F4" s="6">
         <v>46288.717997337961</v>
       </c>
     </row>
@@ -3634,7 +7531,7 @@
       <c r="B5" t="s">
         <v>32</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="6">
         <v>46289</v>
       </c>
     </row>

--- a/Excel_practice/practice_excel.xlsx
+++ b/Excel_practice/practice_excel.xlsx
@@ -1,25 +1,51 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fiiit\Excel_practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC96A86-9705-4FD8-8B7F-DF66EA050E22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7148AC2B-C614-4BFC-9B4E-B61E5696B324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{9582A52E-1B81-4984-BBE7-A03F4D74D0D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{9582A52E-1B81-4984-BBE7-A03F4D74D0D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Task 1" sheetId="1" r:id="rId1"/>
-    <sheet name="Task 3" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Pivot table" sheetId="5" r:id="rId2"/>
+    <sheet name="pivot chart" sheetId="6" r:id="rId3"/>
+    <sheet name="Task 3" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId5"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId6"/>
   </sheets>
+  <definedNames>
+    <definedName name="Slicer_CustomerType">#N/A</definedName>
+    <definedName name="Slicer_PaymentMethod">#N/A</definedName>
+    <definedName name="Slicer_Product">#N/A</definedName>
+    <definedName name="Slicer_Region">#N/A</definedName>
+    <definedName name="Slicer_Salesperson">#N/A</definedName>
+    <definedName name="Slicer_StoreLocation">#N/A</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
+  <pivotCaches>
+    <pivotCache cacheId="0" r:id="rId7"/>
+  </pivotCaches>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
+      <x14:slicerCaches>
+        <x14:slicerCache r:id="rId8"/>
+        <x14:slicerCache r:id="rId9"/>
+        <x14:slicerCache r:id="rId10"/>
+        <x14:slicerCache r:id="rId11"/>
+        <x14:slicerCache r:id="rId12"/>
+        <x14:slicerCache r:id="rId13"/>
+      </x14:slicerCaches>
+    </ext>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
+      <x14:workbookPr/>
+    </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
@@ -36,8 +62,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="107">
   <si>
     <t>S.No</t>
   </si>
@@ -201,9 +249,6 @@
     <t>PaymentMethod</t>
   </si>
   <si>
-    <t>Returned</t>
-  </si>
-  <si>
     <t>OrderDate</t>
   </si>
   <si>
@@ -315,21 +360,9 @@
     <t>Printer</t>
   </si>
   <si>
-    <t xml:space="preserve">Year </t>
-  </si>
-  <si>
     <t>Total sales</t>
   </si>
   <si>
-    <t>Total Sale</t>
-  </si>
-  <si>
-    <t>Product Sales in 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Laptop   </t>
-  </si>
-  <si>
     <t>Total sales by Year</t>
   </si>
   <si>
@@ -355,6 +388,24 @@
   </si>
   <si>
     <t>Average</t>
+  </si>
+  <si>
+    <t>Row Labels</t>
+  </si>
+  <si>
+    <t>Grand Total</t>
+  </si>
+  <si>
+    <t>(All)</t>
+  </si>
+  <si>
+    <t>Sum of Total sales</t>
+  </si>
+  <si>
+    <t>Sum of Discount</t>
+  </si>
+  <si>
+    <t>Sum of UnitPrice</t>
   </si>
 </sst>
 </file>
@@ -362,8 +413,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
-    <numFmt numFmtId="168" formatCode="yyyy\-mm\-dd"/>
-    <numFmt numFmtId="172" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
@@ -608,38 +659,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="168" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -661,14 +692,11 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="17" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="172" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -680,6 +708,28 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -689,50 +739,29 @@
     <xf numFmtId="0" fontId="2" fillId="19" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{838E1F74-091B-422A-8F25-11DC4903382E}"/>
   </cellStyles>
-  <dxfs count="35">
+  <dxfs count="6">
     <dxf>
       <fill>
         <gradientFill degree="90">
           <stop position="0">
-            <color theme="9" tint="-0.25098422193060094"/>
+            <color theme="5" tint="0.40000610370189521"/>
           </stop>
           <stop position="1">
-            <color theme="8" tint="-0.49803155613879818"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="9" tint="-0.25098422193060094"/>
-          </stop>
-          <stop position="1">
-            <color theme="9" tint="-0.49803155613879818"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="7" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="7" tint="-0.25098422193060094"/>
+            <color theme="5" tint="-0.49803155613879818"/>
           </stop>
         </gradientFill>
       </fill>
@@ -751,21 +780,21 @@
     </dxf>
     <dxf>
       <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="5" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="5" tint="-0.49803155613879818"/>
-          </stop>
-        </gradientFill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
       </fill>
     </dxf>
     <dxf>
       <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color theme="7" tint="0.40000610370189521"/>
+          </stop>
+          <stop position="1">
+            <color theme="7" tint="-0.25098422193060094"/>
+          </stop>
+        </gradientFill>
       </fill>
     </dxf>
     <dxf>
@@ -790,249 +819,6 @@
             <color theme="9" tint="-0.49803155613879818"/>
           </stop>
         </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="7" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="7" tint="-0.25098422193060094"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color rgb="FF10A872"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FFFFFF00"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="270">
-          <stop position="0">
-            <color theme="7" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="7" tint="-0.25098422193060094"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="9" tint="-0.25098422193060094"/>
-          </stop>
-          <stop position="1">
-            <color theme="8" tint="-0.49803155613879818"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="9" tint="-0.25098422193060094"/>
-          </stop>
-          <stop position="1">
-            <color theme="9" tint="-0.49803155613879818"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="7" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="7" tint="-0.25098422193060094"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="7" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="7" tint="-0.25098422193060094"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="270">
-          <stop position="0">
-            <color theme="7" tint="0.40000610370189521"/>
-          </stop>
-          <stop position="1">
-            <color theme="7" tint="-0.25098422193060094"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF7030A0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <gradientFill degree="90">
-          <stop position="0">
-            <color theme="5" tint="0.59999389629810485"/>
-          </stop>
-          <stop position="1">
-            <color rgb="FF4472C4"/>
-          </stop>
-        </gradientFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
       </fill>
     </dxf>
   </dxfs>
@@ -2003,6 +1789,707 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:pivotSource>
+    <c:name>[practice_excel.xlsx]pivot chart!PivotTable3</c:name>
+    <c:fmtId val="0"/>
+  </c:pivotSource>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1800" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="all" spc="150" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="50000"/>
+                  <a:lumOff val="50000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:pivotFmts>
+      <c:pivotFmt>
+        <c:idx val="0"/>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:spPr>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="75000"/>
+                      <a:lumOff val="25000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="en-US"/>
+            </a:p>
+          </c:txPr>
+          <c:dLblPos val="outEnd"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:pattFill prst="narHorz">
+            <a:fgClr>
+              <a:schemeClr val="accent1"/>
+            </a:fgClr>
+            <a:bgClr>
+              <a:schemeClr val="accent1">
+                <a:lumMod val="20000"/>
+                <a:lumOff val="80000"/>
+              </a:schemeClr>
+            </a:bgClr>
+          </a:pattFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst>
+            <a:innerShdw blurRad="114300">
+              <a:schemeClr val="accent1"/>
+            </a:innerShdw>
+          </a:effectLst>
+        </c:spPr>
+      </c:pivotFmt>
+    </c:pivotFmts>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'pivot chart'!$B$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Total</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent1"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent1">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent1"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-C5D0-44A7-9677-E8E7DC6D652A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent2"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent2">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent2"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-C5D0-44A7-9677-E8E7DC6D652A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent3"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent3">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent3"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-C5D0-44A7-9677-E8E7DC6D652A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent4"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent4">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent4"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000007-C5D0-44A7-9677-E8E7DC6D652A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent5"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent5">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent5"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000009-C5D0-44A7-9677-E8E7DC6D652A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="5"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:pattFill prst="narHorz">
+                <a:fgClr>
+                  <a:schemeClr val="accent6"/>
+                </a:fgClr>
+                <a:bgClr>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="20000"/>
+                    <a:lumOff val="80000"/>
+                  </a:schemeClr>
+                </a:bgClr>
+              </a:pattFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst>
+                <a:innerShdw blurRad="114300">
+                  <a:schemeClr val="accent6"/>
+                </a:innerShdw>
+              </a:effectLst>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{0000000B-C5D0-44A7-9677-E8E7DC6D652A}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="en-US"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="outEnd"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>'pivot chart'!$A$4:$A$10</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Chair</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Desk</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Laptop</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Phone</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Printer</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Tablet</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'pivot chart'!$B$4:$B$10</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>3525.6899999999996</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>389.88</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1444.71</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>544.01</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2351.6</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>4841.28</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-D504-422E-BE0A-67BF5AFF9586}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="r"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+  <c:extLst>
+    <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
+      <c14:pivotOptions>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
+        <c14:dropZonesVisible val="1"/>
+      </c14:pivotOptions>
+    </c:ext>
+    <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
+      <c16:pivotOptions16>
+        <c16:showExpandCollapseFieldButtons val="1"/>
+      </c16:pivotOptions16>
+    </c:ext>
+  </c:extLst>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -2044,6 +2531,46 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -3075,6 +3602,525 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="203">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" b="1" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:effectRef>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:pattFill prst="narHorz">
+        <a:fgClr>
+          <a:schemeClr val="phClr"/>
+        </a:fgClr>
+        <a:bgClr>
+          <a:schemeClr val="phClr">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:bgClr>
+      </a:pattFill>
+      <a:effectLst>
+        <a:innerShdw blurRad="114300">
+          <a:schemeClr val="phClr"/>
+        </a:innerShdw>
+      </a:effectLst>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="6"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="50000"/>
+        <a:lumOff val="50000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1800" b="1" kern="1200" cap="all" spc="150" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -3150,6 +4196,1987 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>38101</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>876300</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>144781</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="2" name="Region">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9318628A-5D9A-A5BC-254F-8A435F7EFA60}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Region"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5509260" y="38101"/>
+              <a:ext cx="1828800" cy="2621280"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>960120</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>91440</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>944880</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>198120</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="3" name="Product">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B19EAF66-FC4A-FFE6-1F96-A0BF7E986968}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Product"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="7421880" y="91440"/>
+              <a:ext cx="1828800" cy="2849880"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1051560</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>53341</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1211580</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>129541</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="4" name="StoreLocation">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FB5022BA-2EC5-ABA4-8F9D-99F12455EE60}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="StoreLocation"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9357360" y="281941"/>
+              <a:ext cx="1828800" cy="2133600"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>335280</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>906780</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>150495</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="5" name="CustomerType">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC92EAFC-7CA4-1F97-5099-E90168B202F3}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="CustomerType"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="5539740" y="2781300"/>
+              <a:ext cx="1828800" cy="1941195"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>114300</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>22860</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>274320</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>89535</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="6" name="Salesperson">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3847C60B-4E6F-AF12-2D98-5DC7401C6F0F}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Salesperson"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="11879580" y="251460"/>
+              <a:ext cx="1828800" cy="3038475"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1188720</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>1348740</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>135255</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="PaymentMethod">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{434F858B-0357-7C1A-C2FD-8FFB2B8D5AA0}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="PaymentMethod"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="9494520" y="2552700"/>
+              <a:ext cx="1828800" cy="2383155"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="en-IN" sz="1100"/>
+                <a:t>This shape represents a slicer. Slicers are supported in Excel 2010 or later.
+If the shape was modified in an earlier version of Excel, or if the workbook was saved in Excel 2003 or earlier, the slicer cannot be used.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>129540</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>716280</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>213360</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4E752A7-957A-A67A-6049-743DFC9592A9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Raj kumar" refreshedDate="46290.967947569443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="49" xr:uid="{2FDE50FE-7957-47EE-B383-986769CD9CBB}">
+  <cacheSource type="worksheet">
+    <worksheetSource ref="A1:N50" sheet="Task 3"/>
+  </cacheSource>
+  <cacheFields count="14">
+    <cacheField name="Date" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="2023" maxValue="2025" count="3">
+        <n v="2024"/>
+        <n v="2023"/>
+        <n v="2025"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Region" numFmtId="0">
+      <sharedItems count="5">
+        <s v="East"/>
+        <s v="South"/>
+        <s v="North"/>
+        <s v="Central"/>
+        <s v="West"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Product" numFmtId="0">
+      <sharedItems count="7">
+        <s v="Laptop"/>
+        <s v="Phone"/>
+        <s v="Desk"/>
+        <s v="Chair"/>
+        <s v="Monitor"/>
+        <s v="Tablet"/>
+        <s v="Printer"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Quantity" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="1" maxValue="20" count="20">
+        <n v="14"/>
+        <n v="1"/>
+        <n v="18"/>
+        <n v="2"/>
+        <n v="7"/>
+        <n v="3"/>
+        <n v="5"/>
+        <n v="15"/>
+        <n v="19"/>
+        <n v="17"/>
+        <n v="11"/>
+        <n v="20"/>
+        <n v="10"/>
+        <n v="12"/>
+        <n v="13"/>
+        <n v="4"/>
+        <n v="6"/>
+        <n v="9"/>
+        <n v="16"/>
+        <n v="8"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="UnitPrice" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="17.5" maxValue="2000"/>
+    </cacheField>
+    <cacheField name="StoreLocation" numFmtId="0">
+      <sharedItems count="4">
+        <s v="Store B"/>
+        <s v="Store A"/>
+        <s v="Store C"/>
+        <s v="Store D"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="CustomerType" numFmtId="0">
+      <sharedItems count="2">
+        <s v="Wholesale"/>
+        <s v="Retail"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Discount" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="0" maxValue="0.15"/>
+    </cacheField>
+    <cacheField name="Salesperson" numFmtId="0">
+      <sharedItems count="6">
+        <s v="Eva"/>
+        <s v="Alice"/>
+        <s v="Frank"/>
+        <s v="Carlos"/>
+        <s v="Diana"/>
+        <s v="Bob"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="PaymentMethod" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Online"/>
+        <s v="Gift Card"/>
+        <s v="Credit Card"/>
+        <s v="Debit Card"/>
+        <s v="Cash"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="OrderDate" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-09T00:00:00" maxDate="2025-06-21T00:00:00"/>
+    </cacheField>
+    <cacheField name="DeliveryDate" numFmtId="164">
+      <sharedItems containsSemiMixedTypes="0" containsNonDate="0" containsDate="1" containsString="0" minDate="2023-01-11T00:00:00" maxDate="2025-07-01T00:00:00" count="47">
+        <d v="2023-02-27T00:00:00"/>
+        <d v="2024-12-28T00:00:00"/>
+        <d v="2023-05-19T00:00:00"/>
+        <d v="2025-03-02T00:00:00"/>
+        <d v="2023-06-27T00:00:00"/>
+        <d v="2024-03-01T00:00:00"/>
+        <d v="2023-01-14T00:00:00"/>
+        <d v="2023-01-11T00:00:00"/>
+        <d v="2024-10-18T00:00:00"/>
+        <d v="2025-03-13T00:00:00"/>
+        <d v="2024-04-17T00:00:00"/>
+        <d v="2024-07-18T00:00:00"/>
+        <d v="2023-07-31T00:00:00"/>
+        <d v="2025-01-22T00:00:00"/>
+        <d v="2024-12-15T00:00:00"/>
+        <d v="2025-05-17T00:00:00"/>
+        <d v="2023-03-04T00:00:00"/>
+        <d v="2024-06-01T00:00:00"/>
+        <d v="2023-12-08T00:00:00"/>
+        <d v="2023-07-02T00:00:00"/>
+        <d v="2025-06-08T00:00:00"/>
+        <d v="2023-03-08T00:00:00"/>
+        <d v="2024-02-22T00:00:00"/>
+        <d v="2023-08-14T00:00:00"/>
+        <d v="2024-05-30T00:00:00"/>
+        <d v="2023-10-28T00:00:00"/>
+        <d v="2025-06-25T00:00:00"/>
+        <d v="2024-11-21T00:00:00"/>
+        <d v="2023-05-17T00:00:00"/>
+        <d v="2024-12-14T00:00:00"/>
+        <d v="2024-02-15T00:00:00"/>
+        <d v="2025-03-15T00:00:00"/>
+        <d v="2023-04-11T00:00:00"/>
+        <d v="2025-05-12T00:00:00"/>
+        <d v="2023-09-11T00:00:00"/>
+        <d v="2025-03-28T00:00:00"/>
+        <d v="2025-06-30T00:00:00"/>
+        <d v="2024-02-25T00:00:00"/>
+        <d v="2023-06-17T00:00:00"/>
+        <d v="2024-06-25T00:00:00"/>
+        <d v="2023-07-26T00:00:00"/>
+        <d v="2023-05-27T00:00:00"/>
+        <d v="2023-07-04T00:00:00"/>
+        <d v="2024-06-14T00:00:00"/>
+        <d v="2025-02-05T00:00:00"/>
+        <d v="2024-01-13T00:00:00"/>
+        <d v="2024-03-16T00:00:00"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="RegionManager" numFmtId="0">
+      <sharedItems count="5">
+        <s v="Eric"/>
+        <s v="Sophie"/>
+        <s v="Ryan"/>
+        <s v="Cameron"/>
+        <s v="Wendy"/>
+      </sharedItems>
+    </cacheField>
+    <cacheField name="Total sales" numFmtId="0">
+      <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" minValue="101.73" maxValue="28000"/>
+    </cacheField>
+  </cacheFields>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{725AE2AE-9491-48be-B2B4-4EB974FC3084}">
+      <x14:pivotCacheDefinition pivotCacheId="648737833"/>
+    </ext>
+  </extLst>
+</pivotCacheDefinition>
+</file>
+
+<file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="49">
+  <r>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="2000"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <d v="2023-02-23T00:00:00"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="28000"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="544.01"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <d v="2024-12-19T00:00:00"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="544.01"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="346.18"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0.1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <d v="2023-05-10T00:00:00"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="4846.5200000000004"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="2"/>
+    <n v="384.82"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0.15"/>
+    <x v="2"/>
+    <x v="1"/>
+    <d v="2025-02-26T00:00:00"/>
+    <x v="3"/>
+    <x v="3"/>
+    <n v="6926.76"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <n v="237.76"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <d v="2023-06-24T00:00:00"/>
+    <x v="4"/>
+    <x v="0"/>
+    <n v="4279.68"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="4"/>
+    <x v="3"/>
+    <n v="385.09"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0.15"/>
+    <x v="4"/>
+    <x v="2"/>
+    <d v="2024-02-20T00:00:00"/>
+    <x v="5"/>
+    <x v="3"/>
+    <n v="770.18"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="17.5"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0.1"/>
+    <x v="1"/>
+    <x v="3"/>
+    <d v="2023-01-11T00:00:00"/>
+    <x v="6"/>
+    <x v="1"/>
+    <n v="122.5"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="330.22"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0.15"/>
+    <x v="3"/>
+    <x v="4"/>
+    <d v="2023-01-09T00:00:00"/>
+    <x v="7"/>
+    <x v="3"/>
+    <n v="990.66000000000008"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="5"/>
+    <n v="432.04"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0.05"/>
+    <x v="5"/>
+    <x v="3"/>
+    <d v="2024-10-16T00:00:00"/>
+    <x v="8"/>
+    <x v="1"/>
+    <n v="1296.1200000000001"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="323.27999999999997"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <d v="2025-03-05T00:00:00"/>
+    <x v="9"/>
+    <x v="4"/>
+    <n v="1616.3999999999999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="523.29"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="0.15"/>
+    <x v="0"/>
+    <x v="3"/>
+    <d v="2024-04-10T00:00:00"/>
+    <x v="10"/>
+    <x v="2"/>
+    <n v="7849.3499999999995"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="8"/>
+    <n v="207.35"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <d v="2024-07-12T00:00:00"/>
+    <x v="11"/>
+    <x v="0"/>
+    <n v="3939.65"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="120.53"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0.05"/>
+    <x v="4"/>
+    <x v="4"/>
+    <d v="2023-07-21T00:00:00"/>
+    <x v="12"/>
+    <x v="3"/>
+    <n v="120.53"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="157.83000000000001"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0.15"/>
+    <x v="3"/>
+    <x v="3"/>
+    <d v="2025-01-18T00:00:00"/>
+    <x v="13"/>
+    <x v="4"/>
+    <n v="157.83000000000001"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="7"/>
+    <n v="220.3"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="4"/>
+    <x v="3"/>
+    <d v="2024-12-08T00:00:00"/>
+    <x v="14"/>
+    <x v="2"/>
+    <n v="3304.5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="9"/>
+    <n v="162.96"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <x v="1"/>
+    <d v="2025-05-11T00:00:00"/>
+    <x v="15"/>
+    <x v="4"/>
+    <n v="2770.32"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="0"/>
+    <x v="8"/>
+    <n v="236.11"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="5"/>
+    <x v="0"/>
+    <d v="2023-02-26T00:00:00"/>
+    <x v="16"/>
+    <x v="4"/>
+    <n v="4486.09"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="10"/>
+    <n v="573.14"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.05"/>
+    <x v="4"/>
+    <x v="4"/>
+    <d v="2024-05-28T00:00:00"/>
+    <x v="17"/>
+    <x v="3"/>
+    <n v="6304.54"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="11"/>
+    <n v="519.04"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="3"/>
+    <x v="1"/>
+    <d v="2023-11-30T00:00:00"/>
+    <x v="18"/>
+    <x v="0"/>
+    <n v="10380.799999999999"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="30.83"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="3"/>
+    <x v="0"/>
+    <d v="2023-06-22T00:00:00"/>
+    <x v="19"/>
+    <x v="4"/>
+    <n v="431.62"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="12"/>
+    <n v="319.05"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="4"/>
+    <x v="0"/>
+    <d v="2025-06-05T00:00:00"/>
+    <x v="20"/>
+    <x v="4"/>
+    <n v="3190.5"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="312.79000000000002"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.05"/>
+    <x v="5"/>
+    <x v="0"/>
+    <d v="2023-03-03T00:00:00"/>
+    <x v="21"/>
+    <x v="3"/>
+    <n v="4379.0600000000004"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="0"/>
+    <n v="395.45"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="3"/>
+    <x v="4"/>
+    <d v="2024-02-18T00:00:00"/>
+    <x v="22"/>
+    <x v="2"/>
+    <n v="5536.3"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="13"/>
+    <n v="472.72"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="4"/>
+    <x v="2"/>
+    <d v="2023-08-06T00:00:00"/>
+    <x v="23"/>
+    <x v="3"/>
+    <n v="5672.64"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="288.01"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0"/>
+    <x v="0"/>
+    <x v="2"/>
+    <d v="2024-05-23T00:00:00"/>
+    <x v="24"/>
+    <x v="2"/>
+    <n v="1440.05"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <x v="14"/>
+    <n v="562.29"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <d v="2023-10-23T00:00:00"/>
+    <x v="25"/>
+    <x v="0"/>
+    <n v="7309.7699999999995"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="4"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="101.73"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <d v="2025-06-16T00:00:00"/>
+    <x v="26"/>
+    <x v="4"/>
+    <n v="101.73"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="15"/>
+    <n v="279.49"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="4"/>
+    <x v="2"/>
+    <d v="2023-03-03T00:00:00"/>
+    <x v="21"/>
+    <x v="2"/>
+    <n v="1117.96"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="178.55"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="3"/>
+    <x v="3"/>
+    <d v="2024-11-18T00:00:00"/>
+    <x v="27"/>
+    <x v="1"/>
+    <n v="178.55"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="5"/>
+    <x v="1"/>
+    <n v="472.07"/>
+    <x v="1"/>
+    <x v="0"/>
+    <n v="0.1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <d v="2023-05-09T00:00:00"/>
+    <x v="28"/>
+    <x v="3"/>
+    <n v="472.07"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="13"/>
+    <n v="306.29000000000002"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="2"/>
+    <x v="3"/>
+    <d v="2024-12-07T00:00:00"/>
+    <x v="29"/>
+    <x v="2"/>
+    <n v="3675.4800000000005"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="4"/>
+    <n v="434.77"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="2"/>
+    <x v="0"/>
+    <d v="2024-02-13T00:00:00"/>
+    <x v="30"/>
+    <x v="2"/>
+    <n v="3043.39"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="16"/>
+    <n v="64.98"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="3"/>
+    <x v="3"/>
+    <d v="2025-03-09T00:00:00"/>
+    <x v="31"/>
+    <x v="1"/>
+    <n v="389.88"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="2"/>
+    <x v="9"/>
+    <n v="476.49"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="1"/>
+    <d v="2023-04-05T00:00:00"/>
+    <x v="32"/>
+    <x v="3"/>
+    <n v="8100.33"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="15"/>
+    <n v="559.72"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="4"/>
+    <x v="0"/>
+    <d v="2025-05-08T00:00:00"/>
+    <x v="33"/>
+    <x v="2"/>
+    <n v="2238.88"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="5"/>
+    <x v="0"/>
+    <n v="82.14"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="2"/>
+    <d v="2023-09-03T00:00:00"/>
+    <x v="34"/>
+    <x v="2"/>
+    <n v="1149.96"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="3"/>
+    <x v="17"/>
+    <n v="343.21"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.05"/>
+    <x v="3"/>
+    <x v="3"/>
+    <d v="2025-03-21T00:00:00"/>
+    <x v="35"/>
+    <x v="3"/>
+    <n v="3088.89"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="4"/>
+    <n v="301.01"/>
+    <x v="0"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="4"/>
+    <x v="4"/>
+    <d v="2025-06-20T00:00:00"/>
+    <x v="36"/>
+    <x v="1"/>
+    <n v="2107.0699999999997"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="0"/>
+    <n v="428.13"/>
+    <x v="2"/>
+    <x v="1"/>
+    <n v="0.1"/>
+    <x v="5"/>
+    <x v="4"/>
+    <d v="2024-02-15T00:00:00"/>
+    <x v="37"/>
+    <x v="3"/>
+    <n v="5993.82"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="3"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="503.28"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <d v="2023-06-09T00:00:00"/>
+    <x v="38"/>
+    <x v="3"/>
+    <n v="1006.56"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="6"/>
+    <x v="6"/>
+    <n v="470.32"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <d v="2023-08-10T00:00:00"/>
+    <x v="23"/>
+    <x v="1"/>
+    <n v="2351.6"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="11"/>
+    <n v="65.17"/>
+    <x v="2"/>
+    <x v="0"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <x v="1"/>
+    <d v="2024-06-16T00:00:00"/>
+    <x v="39"/>
+    <x v="3"/>
+    <n v="1303.4000000000001"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="13"/>
+    <n v="36.17"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="0"/>
+    <x v="0"/>
+    <d v="2023-07-23T00:00:00"/>
+    <x v="40"/>
+    <x v="1"/>
+    <n v="434.04"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="3"/>
+    <x v="6"/>
+    <x v="15"/>
+    <n v="459.31"/>
+    <x v="3"/>
+    <x v="0"/>
+    <n v="0.15"/>
+    <x v="3"/>
+    <x v="1"/>
+    <d v="2023-05-20T00:00:00"/>
+    <x v="41"/>
+    <x v="3"/>
+    <n v="1837.24"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="0"/>
+    <x v="3"/>
+    <n v="416.06"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.05"/>
+    <x v="0"/>
+    <x v="3"/>
+    <d v="2023-06-30T00:00:00"/>
+    <x v="42"/>
+    <x v="1"/>
+    <n v="832.12"/>
+  </r>
+  <r>
+    <x v="1"/>
+    <x v="1"/>
+    <x v="5"/>
+    <x v="18"/>
+    <n v="302.58"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0"/>
+    <x v="1"/>
+    <x v="0"/>
+    <d v="2024-06-04T00:00:00"/>
+    <x v="43"/>
+    <x v="1"/>
+    <n v="4841.28"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="4"/>
+    <x v="3"/>
+    <x v="10"/>
+    <n v="33.130000000000003"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="2"/>
+    <x v="0"/>
+    <d v="2025-02-03T00:00:00"/>
+    <x v="44"/>
+    <x v="4"/>
+    <n v="364.43"/>
+  </r>
+  <r>
+    <x v="2"/>
+    <x v="0"/>
+    <x v="5"/>
+    <x v="19"/>
+    <n v="582.52"/>
+    <x v="3"/>
+    <x v="1"/>
+    <n v="0.15"/>
+    <x v="2"/>
+    <x v="1"/>
+    <d v="2024-01-09T00:00:00"/>
+    <x v="45"/>
+    <x v="0"/>
+    <n v="4660.16"/>
+  </r>
+  <r>
+    <x v="0"/>
+    <x v="2"/>
+    <x v="2"/>
+    <x v="6"/>
+    <n v="165.15"/>
+    <x v="1"/>
+    <x v="1"/>
+    <n v="0.1"/>
+    <x v="0"/>
+    <x v="1"/>
+    <d v="2024-03-14T00:00:00"/>
+    <x v="46"/>
+    <x v="2"/>
+    <n v="825.75"/>
+  </r>
+</pivotCacheRecords>
+</file>
+
+<file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{650CDF22-2470-4854-A070-33B83F70C778}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+  <location ref="A6:D9" firstHeaderRow="0" firstDataRow="1" firstDataCol="1" rowPageCount="3" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="6">
+        <item h="1" x="3"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item x="1"/>
+        <item h="1" x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="21">
+        <item x="1"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="15"/>
+        <item x="6"/>
+        <item x="16"/>
+        <item x="4"/>
+        <item x="19"/>
+        <item x="17"/>
+        <item x="12"/>
+        <item x="10"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="0"/>
+        <item x="7"/>
+        <item x="18"/>
+        <item x="9"/>
+        <item x="2"/>
+        <item x="8"/>
+        <item x="11"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0">
+      <items count="5">
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item h="1" x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item h="1" x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="7">
+        <item h="1" x="1"/>
+        <item h="1" x="5"/>
+        <item x="3"/>
+        <item h="1" x="4"/>
+        <item h="1" x="0"/>
+        <item h="1" x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="6">
+        <item x="4"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField axis="axisPage" numFmtId="164" showAll="0">
+      <items count="48">
+        <item x="7"/>
+        <item x="6"/>
+        <item x="0"/>
+        <item x="16"/>
+        <item x="21"/>
+        <item x="32"/>
+        <item x="28"/>
+        <item x="2"/>
+        <item x="41"/>
+        <item x="38"/>
+        <item x="4"/>
+        <item x="19"/>
+        <item x="42"/>
+        <item x="40"/>
+        <item x="12"/>
+        <item x="23"/>
+        <item x="34"/>
+        <item x="25"/>
+        <item x="18"/>
+        <item x="45"/>
+        <item x="30"/>
+        <item x="22"/>
+        <item x="37"/>
+        <item x="5"/>
+        <item x="46"/>
+        <item x="10"/>
+        <item x="24"/>
+        <item x="17"/>
+        <item x="43"/>
+        <item x="39"/>
+        <item x="11"/>
+        <item x="8"/>
+        <item x="27"/>
+        <item x="29"/>
+        <item x="14"/>
+        <item x="1"/>
+        <item x="13"/>
+        <item x="44"/>
+        <item x="3"/>
+        <item x="9"/>
+        <item x="31"/>
+        <item x="35"/>
+        <item x="33"/>
+        <item x="15"/>
+        <item x="20"/>
+        <item x="26"/>
+        <item x="36"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="2">
+    <field x="8"/>
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="3">
+    <i>
+      <x v="2"/>
+    </i>
+    <i r="1">
+      <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="-2"/>
+  </colFields>
+  <colItems count="3">
+    <i>
+      <x/>
+    </i>
+    <i i="1">
+      <x v="1"/>
+    </i>
+    <i i="2">
+      <x v="2"/>
+    </i>
+  </colItems>
+  <pageFields count="3">
+    <pageField fld="2" item="2" hier="-1"/>
+    <pageField fld="11" hier="-1"/>
+    <pageField fld="9" item="2" hier="-1"/>
+  </pageFields>
+  <dataFields count="3">
+    <dataField name="Sum of UnitPrice" fld="4" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Total sales" fld="13" baseField="0" baseItem="0"/>
+    <dataField name="Sum of Discount" fld="7" baseField="0" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{CC3F38A3-D497-48DC-A1A6-44FCCD54D412}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="6">
+  <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="14">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisPage" showAll="0">
+      <items count="6">
+        <item x="3"/>
+        <item x="0"/>
+        <item x="2"/>
+        <item x="1"/>
+        <item x="4"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="8">
+        <item x="3"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="6"/>
+        <item x="5"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField numFmtId="164" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField dataField="1" showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="7">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i>
+      <x v="4"/>
+    </i>
+    <i>
+      <x v="5"/>
+    </i>
+    <i>
+      <x v="6"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="1" item="3" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Sum of Total sales" fld="13" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="7">
+    <chartFormat chart="0" format="1" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="2">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="3">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="4">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="5">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="4"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="6">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="5"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="0" format="7">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="6"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Region" xr10:uid="{4AF2D1A6-2A3F-46F6-886F-EDACA6F3E01E}" sourceName="Region">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="648737833">
+      <items count="5">
+        <i x="1" s="1"/>
+        <i x="3" nd="1"/>
+        <i x="0" nd="1"/>
+        <i x="2" nd="1"/>
+        <i x="4" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache2.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Product" xr10:uid="{5191909C-C586-42A6-A54F-C9AC0223CD38}" sourceName="Product">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="648737833">
+      <items count="7">
+        <i x="0" s="1"/>
+        <i x="3" nd="1"/>
+        <i x="2" nd="1"/>
+        <i x="4" nd="1"/>
+        <i x="1" nd="1"/>
+        <i x="6" nd="1"/>
+        <i x="5" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache3.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_StoreLocation" xr10:uid="{A7D16FF6-3702-42E2-89EE-B563D04EE4AB}" sourceName="StoreLocation">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="648737833">
+      <items count="4">
+        <i x="1" s="1"/>
+        <i x="0" nd="1"/>
+        <i x="2" nd="1"/>
+        <i x="3" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache4.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_CustomerType" xr10:uid="{A3AD732E-412C-40F7-AC87-3B26A3F3E3EB}" sourceName="CustomerType">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="648737833">
+      <items count="2">
+        <i x="1" s="1"/>
+        <i x="0" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache5.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_Salesperson" xr10:uid="{8C11B39A-E5E4-48A9-8968-5791143D0044}" sourceName="Salesperson">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="648737833">
+      <items count="6">
+        <i x="3" s="1"/>
+        <i x="1" nd="1"/>
+        <i x="5" nd="1"/>
+        <i x="4" nd="1"/>
+        <i x="0" nd="1"/>
+        <i x="2" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicerCaches/slicerCache6.xml><?xml version="1.0" encoding="utf-8"?>
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="Slicer_PaymentMethod" xr10:uid="{1D26A900-6923-4759-ADFC-33AA7737FD34}" sourceName="PaymentMethod">
+  <pivotTables>
+    <pivotTable tabId="5" name="PivotTable1"/>
+  </pivotTables>
+  <data>
+    <tabular pivotCacheId="648737833">
+      <items count="5">
+        <i x="3" s="1"/>
+        <i x="4" nd="1"/>
+        <i x="2" nd="1"/>
+        <i x="1" nd="1"/>
+        <i x="0" nd="1"/>
+      </items>
+    </tabular>
+  </data>
+</slicerCacheDefinition>
+</file>
+
+<file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
+  <slicer name="Region" xr10:uid="{9708A51F-1228-46E5-B227-CC004C0DA786}" cache="Slicer_Region" caption="Region" rowHeight="298450"/>
+  <slicer name="Product" xr10:uid="{467547B2-E886-437F-892C-1564FB7173B7}" cache="Slicer_Product" caption="Product" rowHeight="298450"/>
+  <slicer name="StoreLocation" xr10:uid="{46247D15-43C4-4ACB-8600-76F55E3AD12B}" cache="Slicer_StoreLocation" caption="StoreLocation" rowHeight="298450"/>
+  <slicer name="CustomerType" xr10:uid="{29B89459-B567-474B-8543-75AA0CE40ADD}" cache="Slicer_CustomerType" caption="CustomerType" rowHeight="298450"/>
+  <slicer name="Salesperson" xr10:uid="{A1566DFE-FDB0-4C68-88EB-6BB4BDDB0EE3}" cache="Slicer_Salesperson" caption="Salesperson" rowHeight="298450"/>
+  <slicer name="PaymentMethod" xr10:uid="{13CB6984-4D40-4645-8D69-B726176FAE49}" cache="Slicer_PaymentMethod" caption="PaymentMethod" rowHeight="298450"/>
+</slicers>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3458,54 +6485,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="35.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="38" t="s">
         <v>18</v>
       </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="9"/>
-      <c r="E1" s="9"/>
-      <c r="F1" s="9"/>
-      <c r="G1" s="9"/>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="9"/>
-      <c r="K1" s="9"/>
-      <c r="L1" s="9"/>
+      <c r="B1" s="38"/>
+      <c r="C1" s="38"/>
+      <c r="D1" s="38"/>
+      <c r="E1" s="38"/>
+      <c r="F1" s="38"/>
+      <c r="G1" s="38"/>
+      <c r="H1" s="38"/>
+      <c r="I1" s="38"/>
+      <c r="J1" s="38"/>
+      <c r="K1" s="38"/>
+      <c r="L1" s="38"/>
     </row>
     <row r="2" spans="1:12" ht="28.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="8" t="s">
+      <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="8" t="s">
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="37" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="J2" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="L2" s="37" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="26.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="8"/>
-      <c r="B3" s="8"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="37"/>
       <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
@@ -3521,11 +6548,11 @@
       <c r="G3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="8"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-      <c r="L3" s="8"/>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+      <c r="K3" s="37"/>
+      <c r="L3" s="37"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
@@ -3760,8 +6787,203 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2ECEBBF-AF0D-454E-AADB-6DF00E7846E7}">
+  <dimension ref="A2:D9"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.9140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="6" width="13.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="6.4140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.25" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.58203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.25" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="B3" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="29" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7">
+        <v>178.55</v>
+      </c>
+      <c r="C7">
+        <v>178.55</v>
+      </c>
+      <c r="D7">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="B8">
+        <v>178.55</v>
+      </c>
+      <c r="C8">
+        <v>178.55</v>
+      </c>
+      <c r="D8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B9">
+        <v>178.55</v>
+      </c>
+      <c r="C9">
+        <v>178.55</v>
+      </c>
+      <c r="D9">
+        <v>0.15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId3"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D954C92-FCF0-4D8D-A29C-7A9EEB7CBDEB}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.08203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="28" t="s">
+        <v>101</v>
+      </c>
+      <c r="B3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="29" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4">
+        <v>3525.6899999999996</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="29" t="s">
+        <v>72</v>
+      </c>
+      <c r="B5">
+        <v>389.88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="B6">
+        <v>1444.71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="29" t="s">
+        <v>65</v>
+      </c>
+      <c r="B7">
+        <v>544.01</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="29" t="s">
+        <v>90</v>
+      </c>
+      <c r="B8">
+        <v>2351.6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="29" t="s">
+        <v>89</v>
+      </c>
+      <c r="B9">
+        <v>4841.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10">
+        <v>13097.169999999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BD969E-335E-4BAE-AA07-B8473F045CD1}">
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:N109"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="3" width="13.4140625" bestFit="1" customWidth="1"/>
@@ -3770,2758 +6992,2508 @@
     <col min="6" max="7" width="13.75" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="13.4140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.75" customWidth="1"/>
-    <col min="11" max="11" width="18.9140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A1" s="11" t="s">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="11" t="s">
+      <c r="C1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="D1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="11" t="s">
+      <c r="G1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="11" t="s">
+      <c r="H1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="I1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="11" t="s">
+      <c r="J1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="11" t="s">
+      <c r="K1" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="L1" s="11" t="s">
+      <c r="L1" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="M1" s="11" t="s">
+      <c r="M1" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="N1" s="11" t="s">
+      <c r="N1" s="10" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="7">
+        <v>2024</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="O1" s="13" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A2" s="14">
-        <v>2024</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="C2" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="D2" s="7">
+        <v>14</v>
+      </c>
+      <c r="E2" s="7">
+        <v>2000</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="D2" s="10">
-        <v>14</v>
-      </c>
-      <c r="E2" s="10">
-        <v>2000</v>
-      </c>
-      <c r="F2" s="10" t="s">
+      <c r="G2" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="G2" s="10" t="s">
+      <c r="H2" s="7">
+        <v>0</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H2" s="10">
-        <v>0</v>
-      </c>
-      <c r="I2" s="10" t="s">
+      <c r="J2" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J2" s="10" t="s">
+      <c r="K2" s="9">
+        <v>44980</v>
+      </c>
+      <c r="L2" s="9">
+        <v>44984</v>
+      </c>
+      <c r="M2" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K2" s="10">
-        <v>0</v>
-      </c>
-      <c r="L2" s="12">
-        <v>44980</v>
-      </c>
-      <c r="M2" s="12">
-        <v>44984</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O2">
+      <c r="N2">
         <f>PRODUCT(D2,E2)</f>
         <v>28000</v>
       </c>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A3" s="14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A3" s="7">
         <v>2024</v>
       </c>
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="D3" s="7">
+        <v>1</v>
+      </c>
+      <c r="E3" s="7">
+        <v>544.01</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="D3" s="10">
-        <v>1</v>
-      </c>
-      <c r="E3" s="10">
+      <c r="G3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H3" s="7">
+        <v>0</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K3" s="9">
+        <v>45645</v>
+      </c>
+      <c r="L3" s="9">
+        <v>45654</v>
+      </c>
+      <c r="M3" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N3">
+        <f t="shared" ref="N3:N50" si="0">PRODUCT(D3,E3)</f>
         <v>544.01</v>
       </c>
-      <c r="F3" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G3" s="10" t="s">
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A4" s="7">
+        <v>2023</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D4" s="7">
+        <v>14</v>
+      </c>
+      <c r="E4" s="7">
+        <v>346.18</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H3" s="10">
-        <v>0</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K3" s="10">
-        <v>0</v>
-      </c>
-      <c r="L3" s="12">
-        <v>45645</v>
-      </c>
-      <c r="M3" s="12">
-        <v>45654</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O3">
-        <f t="shared" ref="O3:O50" si="0">PRODUCT(D3,E3)</f>
-        <v>544.01</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A4" s="14">
-        <v>2023</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="J4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="9">
+        <v>45056</v>
+      </c>
+      <c r="L4" s="9">
+        <v>45065</v>
+      </c>
+      <c r="M4" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D4" s="10">
-        <v>14</v>
-      </c>
-      <c r="E4" s="10">
-        <v>346.18</v>
-      </c>
-      <c r="F4" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H4" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="I4" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J4" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K4" s="10">
-        <v>0</v>
-      </c>
-      <c r="L4" s="12">
-        <v>45056</v>
-      </c>
-      <c r="M4" s="12">
-        <v>45065</v>
-      </c>
-      <c r="N4" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O4">
+      <c r="N4">
         <f t="shared" si="0"/>
         <v>4846.5200000000004</v>
       </c>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A5" s="14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A5" s="7">
         <v>2025</v>
       </c>
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="D5" s="7">
+        <v>18</v>
+      </c>
+      <c r="E5" s="7">
+        <v>384.82</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="D5" s="10">
-        <v>18</v>
-      </c>
-      <c r="E5" s="10">
-        <v>384.82</v>
-      </c>
-      <c r="F5" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H5" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I5" s="10" t="s">
+      <c r="J5" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K5" s="9">
+        <v>45714</v>
+      </c>
+      <c r="L5" s="9">
+        <v>45718</v>
+      </c>
+      <c r="M5" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="J5" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K5" s="10">
-        <v>0</v>
-      </c>
-      <c r="L5" s="12">
-        <v>45714</v>
-      </c>
-      <c r="M5" s="12">
-        <v>45718</v>
-      </c>
-      <c r="N5" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O5">
+      <c r="N5">
         <f t="shared" si="0"/>
         <v>6926.76</v>
       </c>
     </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A6" s="14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A6" s="7">
         <v>2025</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C6" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" s="10">
+      <c r="B6" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="7">
         <v>18</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="7">
         <v>237.76</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="7">
+        <v>0</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H6" s="10">
-        <v>0</v>
-      </c>
-      <c r="I6" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6" s="10" t="s">
+      <c r="J6" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K6" s="9">
+        <v>45101</v>
+      </c>
+      <c r="L6" s="9">
+        <v>45104</v>
+      </c>
+      <c r="M6" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="K6" s="10">
-        <v>0</v>
-      </c>
-      <c r="L6" s="12">
-        <v>45101</v>
-      </c>
-      <c r="M6" s="12">
-        <v>45104</v>
-      </c>
-      <c r="N6" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O6">
+      <c r="N6">
         <f t="shared" si="0"/>
         <v>4279.68</v>
       </c>
     </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A7" s="14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A7" s="7">
         <v>2025</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D7" s="7">
+        <v>2</v>
+      </c>
+      <c r="E7" s="7">
+        <v>385.09</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D7" s="10">
-        <v>2</v>
-      </c>
-      <c r="E7" s="10">
-        <v>385.09</v>
-      </c>
-      <c r="F7" s="10" t="s">
+      <c r="G7" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H7" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G7" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I7" s="10" t="s">
+      <c r="J7" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J7" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K7" s="10">
-        <v>0</v>
-      </c>
-      <c r="L7" s="12">
+      <c r="K7" s="9">
         <v>45342</v>
       </c>
-      <c r="M7" s="12">
+      <c r="L7" s="9">
         <v>45352</v>
       </c>
-      <c r="N7" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O7">
+      <c r="M7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N7">
         <f t="shared" si="0"/>
         <v>770.18</v>
       </c>
     </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A8" s="14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A8" s="7">
         <v>2025</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D8" s="10">
+      <c r="B8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D8" s="7">
         <v>7</v>
       </c>
-      <c r="E8" s="10">
+      <c r="E8" s="7">
         <v>17.5</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="10" t="s">
+      <c r="F8" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H8" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I8" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H8" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J8" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K8" s="10">
-        <v>0</v>
-      </c>
-      <c r="L8" s="12">
+      <c r="J8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K8" s="9">
         <v>44937</v>
       </c>
-      <c r="M8" s="12">
+      <c r="L8" s="9">
         <v>44940</v>
       </c>
-      <c r="N8" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O8">
+      <c r="M8" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N8">
         <f t="shared" si="0"/>
         <v>122.5</v>
       </c>
     </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A9" s="14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A9" s="7">
         <v>2025</v>
       </c>
-      <c r="B9" s="10" t="s">
+      <c r="B9" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C9" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D9" s="10">
+      <c r="D9" s="7">
         <v>3</v>
       </c>
-      <c r="E9" s="10">
+      <c r="E9" s="7">
         <v>330.22</v>
       </c>
-      <c r="F9" s="10" t="s">
+      <c r="F9" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H9" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G9" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H9" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I9" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K9" s="10">
-        <v>0</v>
-      </c>
-      <c r="L9" s="12">
+      <c r="J9" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K9" s="9">
         <v>44935</v>
       </c>
-      <c r="M9" s="12">
+      <c r="L9" s="9">
         <v>44937</v>
       </c>
-      <c r="N9" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O9">
+      <c r="M9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N9">
         <f t="shared" si="0"/>
         <v>990.66000000000008</v>
       </c>
     </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A10" s="14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A10" s="7">
         <v>2025</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C10" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" s="10">
+      <c r="B10" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D10" s="7">
         <v>3</v>
       </c>
-      <c r="E10" s="10">
+      <c r="E10" s="7">
         <v>432.04</v>
       </c>
-      <c r="F10" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G10" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="10">
+      <c r="F10" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H10" s="7">
         <v>0.05</v>
       </c>
-      <c r="I10" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="J10" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="10">
-        <v>1</v>
-      </c>
-      <c r="L10" s="12">
+      <c r="I10" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J10" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K10" s="9">
         <v>45581</v>
       </c>
-      <c r="M10" s="12">
+      <c r="L10" s="9">
         <v>45583</v>
       </c>
-      <c r="N10" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O10">
+      <c r="M10" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N10">
         <f t="shared" si="0"/>
         <v>1296.1200000000001</v>
       </c>
     </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A11" s="7">
         <v>2025</v>
       </c>
-      <c r="B11" s="10" t="s">
+      <c r="B11" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="7">
+        <v>5</v>
+      </c>
+      <c r="E11" s="7">
+        <v>323.27999999999997</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H11" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J11" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K11" s="9">
+        <v>45721</v>
+      </c>
+      <c r="L11" s="9">
+        <v>45729</v>
+      </c>
+      <c r="M11" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C11" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D11" s="10">
-        <v>5</v>
-      </c>
-      <c r="E11" s="10">
-        <v>323.27999999999997</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G11" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H11" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" s="10">
-        <v>0</v>
-      </c>
-      <c r="L11" s="12">
-        <v>45721</v>
-      </c>
-      <c r="M11" s="12">
-        <v>45729</v>
-      </c>
-      <c r="N11" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O11">
+      <c r="N11">
         <f t="shared" si="0"/>
         <v>1616.3999999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A12" s="7">
         <v>2024</v>
       </c>
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C12" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C12" s="10" t="s">
+      <c r="D12" s="7">
+        <v>15</v>
+      </c>
+      <c r="E12" s="7">
+        <v>523.29</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H12" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J12" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K12" s="9">
+        <v>45392</v>
+      </c>
+      <c r="L12" s="9">
+        <v>45399</v>
+      </c>
+      <c r="M12" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D12" s="10">
-        <v>15</v>
-      </c>
-      <c r="E12" s="10">
-        <v>523.29</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G12" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H12" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I12" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J12" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K12" s="10">
-        <v>0</v>
-      </c>
-      <c r="L12" s="12">
-        <v>45392</v>
-      </c>
-      <c r="M12" s="12">
-        <v>45399</v>
-      </c>
-      <c r="N12" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O12">
+      <c r="N12">
         <f t="shared" si="0"/>
         <v>7849.3499999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A13" s="14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A13" s="7">
         <v>2023</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C13" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D13" s="10">
+      <c r="B13" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D13" s="7">
         <v>19</v>
       </c>
-      <c r="E13" s="10">
+      <c r="E13" s="7">
         <v>207.35</v>
       </c>
-      <c r="F13" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G13" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H13" s="10">
+      <c r="F13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H13" s="7">
         <v>0.1</v>
       </c>
-      <c r="I13" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" s="10">
-        <v>1</v>
-      </c>
-      <c r="L13" s="12">
+      <c r="I13" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K13" s="9">
         <v>45485</v>
       </c>
-      <c r="M13" s="12">
+      <c r="L13" s="9">
         <v>45491</v>
       </c>
-      <c r="N13" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O13">
+      <c r="M13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13">
         <f t="shared" si="0"/>
         <v>3939.65</v>
       </c>
     </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A14" s="14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A14" s="7">
         <v>2024</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C14" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="10">
+      <c r="B14" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="7">
         <v>1</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="7">
         <v>120.53</v>
       </c>
-      <c r="F14" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G14" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H14" s="10">
+      <c r="F14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H14" s="7">
         <v>0.05</v>
       </c>
-      <c r="I14" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J14" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K14" s="10">
-        <v>0</v>
-      </c>
-      <c r="L14" s="12">
+      <c r="I14" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J14" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K14" s="9">
         <v>45128</v>
       </c>
-      <c r="M14" s="12">
+      <c r="L14" s="9">
         <v>45138</v>
       </c>
-      <c r="N14" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O14">
+      <c r="M14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N14">
         <f t="shared" si="0"/>
         <v>120.53</v>
       </c>
     </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A15" s="14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A15" s="7">
         <v>2025</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D15" s="7">
+        <v>1</v>
+      </c>
+      <c r="E15" s="7">
+        <v>157.83000000000001</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H15" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J15" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K15" s="9">
+        <v>45675</v>
+      </c>
+      <c r="L15" s="9">
+        <v>45679</v>
+      </c>
+      <c r="M15" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C15" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="10">
-        <v>1</v>
-      </c>
-      <c r="E15" s="10">
-        <v>157.83000000000001</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G15" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H15" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I15" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K15" s="10">
-        <v>0</v>
-      </c>
-      <c r="L15" s="12">
-        <v>45675</v>
-      </c>
-      <c r="M15" s="12">
-        <v>45679</v>
-      </c>
-      <c r="N15" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O15">
+      <c r="N15">
         <f t="shared" si="0"/>
         <v>157.83000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A16" s="14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A16" s="7">
         <v>2024</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C16" s="10" t="s">
+      <c r="D16" s="7">
+        <v>15</v>
+      </c>
+      <c r="E16" s="7">
+        <v>220.3</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H16" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J16" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K16" s="9">
+        <v>45634</v>
+      </c>
+      <c r="L16" s="9">
+        <v>45641</v>
+      </c>
+      <c r="M16" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="10">
-        <v>15</v>
-      </c>
-      <c r="E16" s="10">
-        <v>220.3</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J16" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K16" s="10">
-        <v>0</v>
-      </c>
-      <c r="L16" s="12">
-        <v>45634</v>
-      </c>
-      <c r="M16" s="12">
-        <v>45641</v>
-      </c>
-      <c r="N16" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O16">
+      <c r="N16">
         <f t="shared" si="0"/>
         <v>3304.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A17" s="14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A17" s="7">
         <v>2024</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B17" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D17" s="7">
+        <v>17</v>
+      </c>
+      <c r="E17" s="7">
+        <v>162.96</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J17" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K17" s="9">
+        <v>45788</v>
+      </c>
+      <c r="L17" s="9">
+        <v>45794</v>
+      </c>
+      <c r="M17" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C17" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D17" s="10">
-        <v>17</v>
-      </c>
-      <c r="E17" s="10">
-        <v>162.96</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K17" s="10">
-        <v>0</v>
-      </c>
-      <c r="L17" s="12">
-        <v>45788</v>
-      </c>
-      <c r="M17" s="12">
-        <v>45794</v>
-      </c>
-      <c r="N17" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O17">
+      <c r="N17">
         <f t="shared" si="0"/>
         <v>2770.32</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A18" s="14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A18" s="7">
         <v>2025</v>
       </c>
-      <c r="B18" s="10" t="s">
+      <c r="B18" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="7">
+        <v>19</v>
+      </c>
+      <c r="E18" s="7">
+        <v>236.11</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H18" s="7">
+        <v>0</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J18" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K18" s="9">
+        <v>44983</v>
+      </c>
+      <c r="L18" s="9">
+        <v>44989</v>
+      </c>
+      <c r="M18" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C18" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D18" s="10">
-        <v>19</v>
-      </c>
-      <c r="E18" s="10">
-        <v>236.11</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G18" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H18" s="10">
-        <v>0</v>
-      </c>
-      <c r="I18" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="J18" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K18" s="10">
-        <v>0</v>
-      </c>
-      <c r="L18" s="12">
-        <v>44983</v>
-      </c>
-      <c r="M18" s="12">
-        <v>44989</v>
-      </c>
-      <c r="N18" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O18">
+      <c r="N18">
         <f t="shared" si="0"/>
         <v>4486.09</v>
       </c>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A19" s="14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A19" s="7">
         <v>2023</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C19" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D19" s="10">
+      <c r="B19" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="7">
         <v>11</v>
       </c>
-      <c r="E19" s="10">
+      <c r="E19" s="7">
         <v>573.14</v>
       </c>
-      <c r="F19" s="10" t="s">
+      <c r="F19" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H19" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="I19" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G19" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H19" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="I19" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J19" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K19" s="10">
-        <v>0</v>
-      </c>
-      <c r="L19" s="12">
+      <c r="J19" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K19" s="9">
         <v>45440</v>
       </c>
-      <c r="M19" s="12">
+      <c r="L19" s="9">
         <v>45444</v>
       </c>
-      <c r="N19" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O19">
+      <c r="M19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N19">
         <f t="shared" si="0"/>
         <v>6304.54</v>
       </c>
     </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A20" s="14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A20" s="7">
         <v>2023</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D20" s="10">
+      <c r="B20" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D20" s="7">
         <v>20</v>
       </c>
-      <c r="E20" s="10">
+      <c r="E20" s="7">
         <v>519.04</v>
       </c>
-      <c r="F20" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G20" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="10">
+      <c r="F20" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G20" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H20" s="7">
         <v>0.15</v>
       </c>
-      <c r="I20" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K20" s="10">
-        <v>0</v>
-      </c>
-      <c r="L20" s="12">
+      <c r="I20" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K20" s="9">
         <v>45260</v>
       </c>
-      <c r="M20" s="12">
+      <c r="L20" s="9">
         <v>45268</v>
       </c>
-      <c r="N20" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O20">
+      <c r="M20" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20">
         <f t="shared" si="0"/>
         <v>10380.799999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A21" s="14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A21" s="7">
         <v>2024</v>
       </c>
-      <c r="B21" s="10" t="s">
+      <c r="B21" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="7">
+        <v>14</v>
+      </c>
+      <c r="E21" s="7">
+        <v>30.83</v>
+      </c>
+      <c r="F21" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H21" s="7">
+        <v>0</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K21" s="9">
+        <v>45099</v>
+      </c>
+      <c r="L21" s="9">
+        <v>45109</v>
+      </c>
+      <c r="M21" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C21" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D21" s="10">
-        <v>14</v>
-      </c>
-      <c r="E21" s="10">
-        <v>30.83</v>
-      </c>
-      <c r="F21" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H21" s="10">
-        <v>0</v>
-      </c>
-      <c r="I21" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J21" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K21" s="10">
-        <v>1</v>
-      </c>
-      <c r="L21" s="12">
-        <v>45099</v>
-      </c>
-      <c r="M21" s="12">
-        <v>45109</v>
-      </c>
-      <c r="N21" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O21">
+      <c r="N21">
         <f t="shared" si="0"/>
         <v>431.62</v>
       </c>
     </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A22" s="14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A22" s="7">
         <v>2025</v>
       </c>
-      <c r="B22" s="10" t="s">
+      <c r="B22" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" s="7">
+        <v>10</v>
+      </c>
+      <c r="E22" s="7">
+        <v>319.05</v>
+      </c>
+      <c r="F22" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G22" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H22" s="7">
+        <v>0</v>
+      </c>
+      <c r="I22" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J22" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K22" s="9">
+        <v>45813</v>
+      </c>
+      <c r="L22" s="9">
+        <v>45816</v>
+      </c>
+      <c r="M22" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C22" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D22" s="10">
-        <v>10</v>
-      </c>
-      <c r="E22" s="10">
-        <v>319.05</v>
-      </c>
-      <c r="F22" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G22" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H22" s="10">
-        <v>0</v>
-      </c>
-      <c r="I22" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K22" s="10">
-        <v>0</v>
-      </c>
-      <c r="L22" s="12">
-        <v>45813</v>
-      </c>
-      <c r="M22" s="12">
-        <v>45816</v>
-      </c>
-      <c r="N22" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O22">
+      <c r="N22">
         <f t="shared" si="0"/>
         <v>3190.5</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A23" s="14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A23" s="7">
         <v>2024</v>
       </c>
-      <c r="B23" s="10" t="s">
+      <c r="B23" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C23" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D23" s="10">
+      <c r="D23" s="7">
         <v>14</v>
       </c>
-      <c r="E23" s="10">
+      <c r="E23" s="7">
         <v>312.79000000000002</v>
       </c>
-      <c r="F23" s="10" t="s">
+      <c r="F23" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G23" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G23" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H23" s="10">
+      <c r="H23" s="7">
         <v>0.05</v>
       </c>
-      <c r="I23" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="J23" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K23" s="10">
-        <v>1</v>
-      </c>
-      <c r="L23" s="12">
+      <c r="I23" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="J23" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K23" s="9">
         <v>44988</v>
       </c>
-      <c r="M23" s="12">
+      <c r="L23" s="9">
         <v>44993</v>
       </c>
-      <c r="N23" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O23">
+      <c r="M23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N23">
         <f t="shared" si="0"/>
         <v>4379.0600000000004</v>
       </c>
     </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A24" s="14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A24" s="7">
         <v>2024</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C24" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="10">
+      <c r="B24" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C24" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D24" s="7">
         <v>14</v>
       </c>
-      <c r="E24" s="10">
+      <c r="E24" s="7">
         <v>395.45</v>
       </c>
-      <c r="F24" s="10" t="s">
+      <c r="F24" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H24" s="7">
+        <v>0</v>
+      </c>
+      <c r="I24" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="10">
-        <v>0</v>
-      </c>
-      <c r="I24" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J24" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K24" s="10">
-        <v>1</v>
-      </c>
-      <c r="L24" s="12">
+      <c r="J24" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K24" s="9">
         <v>45340</v>
       </c>
-      <c r="M24" s="12">
+      <c r="L24" s="9">
         <v>45344</v>
       </c>
-      <c r="N24" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O24">
+      <c r="M24" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N24">
         <f t="shared" si="0"/>
         <v>5536.3</v>
       </c>
     </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A25" s="14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A25" s="7">
         <v>2025</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C25" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="10">
+      <c r="B25" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D25" s="7">
         <v>12</v>
       </c>
-      <c r="E25" s="10">
+      <c r="E25" s="7">
         <v>472.72</v>
       </c>
-      <c r="F25" s="10" t="s">
+      <c r="F25" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H25" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I25" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G25" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H25" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I25" s="10" t="s">
+      <c r="J25" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J25" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K25" s="10">
-        <v>0</v>
-      </c>
-      <c r="L25" s="12">
+      <c r="K25" s="9">
         <v>45144</v>
       </c>
-      <c r="M25" s="12">
+      <c r="L25" s="9">
         <v>45152</v>
       </c>
-      <c r="N25" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O25">
+      <c r="M25" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N25">
         <f t="shared" si="0"/>
         <v>5672.64</v>
       </c>
     </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A26" s="14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A26" s="7">
         <v>2023</v>
       </c>
-      <c r="B26" s="10" t="s">
+      <c r="B26" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C26" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="10" t="s">
+      <c r="D26" s="7">
+        <v>5</v>
+      </c>
+      <c r="E26" s="7">
+        <v>288.01</v>
+      </c>
+      <c r="F26" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G26" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H26" s="7">
+        <v>0</v>
+      </c>
+      <c r="I26" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J26" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K26" s="9">
+        <v>45435</v>
+      </c>
+      <c r="L26" s="9">
+        <v>45442</v>
+      </c>
+      <c r="M26" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D26" s="10">
-        <v>5</v>
-      </c>
-      <c r="E26" s="10">
-        <v>288.01</v>
-      </c>
-      <c r="F26" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G26" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H26" s="10">
-        <v>0</v>
-      </c>
-      <c r="I26" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J26" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K26" s="10">
-        <v>0</v>
-      </c>
-      <c r="L26" s="12">
-        <v>45435</v>
-      </c>
-      <c r="M26" s="12">
-        <v>45442</v>
-      </c>
-      <c r="N26" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O26">
+      <c r="N26">
         <f t="shared" si="0"/>
         <v>1440.05</v>
       </c>
     </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A27" s="14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A27" s="7">
         <v>2023</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D27" s="10">
+      <c r="B27" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="7">
         <v>13</v>
       </c>
-      <c r="E27" s="10">
+      <c r="E27" s="7">
         <v>562.29</v>
       </c>
-      <c r="F27" s="10" t="s">
+      <c r="F27" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H27" s="7">
+        <v>0</v>
+      </c>
+      <c r="I27" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G27" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H27" s="10">
-        <v>0</v>
-      </c>
-      <c r="I27" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J27" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K27" s="10">
-        <v>0</v>
-      </c>
-      <c r="L27" s="12">
+      <c r="J27" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K27" s="9">
         <v>45222</v>
       </c>
-      <c r="M27" s="12">
+      <c r="L27" s="9">
         <v>45227</v>
       </c>
-      <c r="N27" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O27">
+      <c r="M27" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27">
         <f t="shared" si="0"/>
         <v>7309.7699999999995</v>
       </c>
     </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A28" s="14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A28" s="7">
         <v>2024</v>
       </c>
-      <c r="B28" s="10" t="s">
+      <c r="B28" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="7">
+        <v>1</v>
+      </c>
+      <c r="E28" s="7">
+        <v>101.73</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G28" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H28" s="7">
+        <v>0</v>
+      </c>
+      <c r="I28" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J28" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K28" s="9">
+        <v>45824</v>
+      </c>
+      <c r="L28" s="9">
+        <v>45833</v>
+      </c>
+      <c r="M28" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C28" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D28" s="10">
-        <v>1</v>
-      </c>
-      <c r="E28" s="10">
-        <v>101.73</v>
-      </c>
-      <c r="F28" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H28" s="10">
-        <v>0</v>
-      </c>
-      <c r="I28" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J28" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K28" s="10">
-        <v>0</v>
-      </c>
-      <c r="L28" s="12">
-        <v>45824</v>
-      </c>
-      <c r="M28" s="12">
-        <v>45833</v>
-      </c>
-      <c r="N28" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O28">
+      <c r="N28">
         <f t="shared" si="0"/>
         <v>101.73</v>
       </c>
     </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A29" s="14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A29" s="7">
         <v>2025</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C29" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D29" s="10">
+      <c r="B29" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="7">
         <v>4</v>
       </c>
-      <c r="E29" s="10">
+      <c r="E29" s="7">
         <v>279.49</v>
       </c>
-      <c r="F29" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G29" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H29" s="10">
+      <c r="F29" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G29" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H29" s="7">
         <v>0</v>
       </c>
-      <c r="I29" s="10" t="s">
+      <c r="I29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J29" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="J29" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K29" s="10">
-        <v>0</v>
-      </c>
-      <c r="L29" s="12">
+      <c r="K29" s="9">
         <v>44988</v>
       </c>
-      <c r="M29" s="12">
+      <c r="L29" s="9">
         <v>44993</v>
       </c>
-      <c r="N29" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O29">
+      <c r="M29" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N29">
         <f t="shared" si="0"/>
         <v>1117.96</v>
       </c>
     </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A30" s="14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A30" s="7">
         <v>2025</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C30" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D30" s="10">
+      <c r="B30" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D30" s="7">
         <v>1</v>
       </c>
-      <c r="E30" s="10">
+      <c r="E30" s="7">
         <v>178.55</v>
       </c>
-      <c r="F30" s="10" t="s">
+      <c r="F30" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G30" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H30" s="10">
+      <c r="H30" s="7">
         <v>0.15</v>
       </c>
-      <c r="I30" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J30" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K30" s="10">
-        <v>1</v>
-      </c>
-      <c r="L30" s="12">
+      <c r="I30" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J30" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K30" s="9">
         <v>45614</v>
       </c>
-      <c r="M30" s="12">
+      <c r="L30" s="9">
         <v>45617</v>
       </c>
-      <c r="N30" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O30">
+      <c r="M30" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N30">
         <f t="shared" si="0"/>
         <v>178.55</v>
       </c>
     </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A31" s="14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A31" s="7">
         <v>2024</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D31" s="10">
+      <c r="B31" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D31" s="7">
         <v>1</v>
       </c>
-      <c r="E31" s="10">
+      <c r="E31" s="7">
         <v>472.07</v>
       </c>
-      <c r="F31" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H31" s="10">
+      <c r="F31" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G31" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H31" s="7">
         <v>0.1</v>
       </c>
-      <c r="I31" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J31" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K31" s="10">
-        <v>0</v>
-      </c>
-      <c r="L31" s="12">
+      <c r="I31" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J31" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K31" s="9">
         <v>45055</v>
       </c>
-      <c r="M31" s="12">
+      <c r="L31" s="9">
         <v>45063</v>
       </c>
-      <c r="N31" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O31">
+      <c r="M31" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N31">
         <f t="shared" si="0"/>
         <v>472.07</v>
       </c>
     </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A32" s="14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A32" s="7">
         <v>2025</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C32" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D32" s="10">
+      <c r="B32" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D32" s="7">
         <v>12</v>
       </c>
-      <c r="E32" s="10">
+      <c r="E32" s="7">
         <v>306.29000000000002</v>
       </c>
-      <c r="F32" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G32" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H32" s="10">
+      <c r="F32" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H32" s="7">
         <v>0</v>
       </c>
-      <c r="I32" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J32" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K32" s="10">
-        <v>0</v>
-      </c>
-      <c r="L32" s="12">
+      <c r="I32" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J32" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K32" s="9">
         <v>45633</v>
       </c>
-      <c r="M32" s="12">
+      <c r="L32" s="9">
         <v>45640</v>
       </c>
-      <c r="N32" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O32">
+      <c r="M32" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N32">
         <f t="shared" si="0"/>
         <v>3675.4800000000005</v>
       </c>
     </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A33" s="14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A33" s="7">
         <v>2023</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C33" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="D33" s="10">
+      <c r="B33" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="D33" s="7">
         <v>7</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="7">
         <v>434.77</v>
       </c>
-      <c r="F33" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G33" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H33" s="10">
+      <c r="F33" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G33" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="7">
         <v>0.15</v>
       </c>
-      <c r="I33" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J33" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K33" s="10">
-        <v>0</v>
-      </c>
-      <c r="L33" s="12">
+      <c r="I33" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J33" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K33" s="9">
         <v>45335</v>
       </c>
-      <c r="M33" s="12">
+      <c r="L33" s="9">
         <v>45337</v>
       </c>
-      <c r="N33" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O33">
+      <c r="M33" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N33">
         <f t="shared" si="0"/>
         <v>3043.39</v>
       </c>
     </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A34" s="14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A34" s="7">
         <v>2025</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D34" s="10">
+      <c r="B34" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="7">
         <v>6</v>
       </c>
-      <c r="E34" s="10">
+      <c r="E34" s="7">
         <v>64.98</v>
       </c>
-      <c r="F34" s="10" t="s">
+      <c r="F34" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H34" s="7">
+        <v>0</v>
+      </c>
+      <c r="I34" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="G34" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H34" s="10">
-        <v>0</v>
-      </c>
-      <c r="I34" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J34" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K34" s="10">
-        <v>0</v>
-      </c>
-      <c r="L34" s="12">
+      <c r="J34" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K34" s="9">
         <v>45725</v>
       </c>
-      <c r="M34" s="12">
+      <c r="L34" s="9">
         <v>45731</v>
       </c>
-      <c r="N34" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O34">
+      <c r="M34" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N34">
         <f t="shared" si="0"/>
         <v>389.88</v>
       </c>
     </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A35" s="14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A35" s="7">
         <v>2025</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C35" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="D35" s="10">
+      <c r="B35" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="7">
         <v>17</v>
       </c>
-      <c r="E35" s="10">
+      <c r="E35" s="7">
         <v>476.49</v>
       </c>
-      <c r="F35" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G35" s="10" t="s">
+      <c r="F35" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G35" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H35" s="7">
+        <v>0</v>
+      </c>
+      <c r="I35" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H35" s="10">
-        <v>0</v>
-      </c>
-      <c r="I35" s="10" t="s">
+      <c r="J35" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J35" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K35" s="10">
-        <v>0</v>
-      </c>
-      <c r="L35" s="12">
+      <c r="K35" s="9">
         <v>45021</v>
       </c>
-      <c r="M35" s="12">
+      <c r="L35" s="9">
         <v>45027</v>
       </c>
-      <c r="N35" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O35">
+      <c r="M35" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N35">
         <f t="shared" si="0"/>
         <v>8100.33</v>
       </c>
     </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A36" s="14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A36" s="7">
         <v>2023</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C36" s="10" t="s">
+      <c r="B36" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="D36" s="7">
+        <v>4</v>
+      </c>
+      <c r="E36" s="7">
+        <v>559.72</v>
+      </c>
+      <c r="F36" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="D36" s="10">
-        <v>4</v>
-      </c>
-      <c r="E36" s="10">
-        <v>559.72</v>
-      </c>
-      <c r="F36" s="10" t="s">
+      <c r="G36" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I36" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="G36" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H36" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I36" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J36" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K36" s="10">
-        <v>0</v>
-      </c>
-      <c r="L36" s="12">
+      <c r="J36" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K36" s="9">
         <v>45785</v>
       </c>
-      <c r="M36" s="12">
+      <c r="L36" s="9">
         <v>45789</v>
       </c>
-      <c r="N36" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O36">
+      <c r="M36" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N36">
         <f t="shared" si="0"/>
         <v>2238.88</v>
       </c>
     </row>
-    <row r="37" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A37" s="14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A37" s="7">
         <v>2024</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D37" s="10">
+      <c r="B37" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D37" s="7">
         <v>14</v>
       </c>
-      <c r="E37" s="10">
+      <c r="E37" s="7">
         <v>82.14</v>
       </c>
-      <c r="F37" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G37" s="10" t="s">
+      <c r="F37" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G37" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H37" s="7">
+        <v>0</v>
+      </c>
+      <c r="I37" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H37" s="10">
-        <v>0</v>
-      </c>
-      <c r="I37" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J37" s="10" t="s">
-        <v>84</v>
-      </c>
-      <c r="K37" s="10">
-        <v>0</v>
-      </c>
-      <c r="L37" s="12">
+      <c r="J37" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K37" s="9">
         <v>45172</v>
       </c>
-      <c r="M37" s="12">
+      <c r="L37" s="9">
         <v>45180</v>
       </c>
-      <c r="N37" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O37">
+      <c r="M37" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="N37">
         <f t="shared" si="0"/>
         <v>1149.96</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A38" s="14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A38" s="7">
         <v>2025</v>
       </c>
-      <c r="B38" s="10" t="s">
+      <c r="B38" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C38" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C38" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="10">
+      <c r="D38" s="7">
         <v>9</v>
       </c>
-      <c r="E38" s="10">
+      <c r="E38" s="7">
         <v>343.21</v>
       </c>
-      <c r="F38" s="10" t="s">
+      <c r="F38" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G38" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H38" s="10">
+      <c r="H38" s="7">
         <v>0.05</v>
       </c>
-      <c r="I38" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J38" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K38" s="10">
-        <v>0</v>
-      </c>
-      <c r="L38" s="12">
+      <c r="I38" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J38" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K38" s="9">
         <v>45737</v>
       </c>
-      <c r="M38" s="12">
+      <c r="L38" s="9">
         <v>45744</v>
       </c>
-      <c r="N38" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O38">
+      <c r="M38" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N38">
         <f t="shared" si="0"/>
         <v>3088.89</v>
       </c>
     </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A39" s="14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A39" s="7">
         <v>2025</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" s="10">
+      <c r="B39" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D39" s="7">
         <v>7</v>
       </c>
-      <c r="E39" s="10">
+      <c r="E39" s="7">
         <v>301.01</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>60</v>
-      </c>
-      <c r="G39" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H39" s="10">
+      <c r="F39" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G39" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H39" s="7">
         <v>0.15</v>
       </c>
-      <c r="I39" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="J39" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="K39" s="10">
-        <v>1</v>
-      </c>
-      <c r="L39" s="12">
+      <c r="I39" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="J39" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K39" s="9">
         <v>45828</v>
       </c>
-      <c r="M39" s="12">
+      <c r="L39" s="9">
         <v>45838</v>
       </c>
-      <c r="N39" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O39">
+      <c r="M39" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N39">
         <f t="shared" si="0"/>
         <v>2107.0699999999997</v>
       </c>
     </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A40" s="14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A40" s="7">
         <v>2025</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="10">
+      <c r="B40" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D40" s="7">
         <v>14</v>
       </c>
-      <c r="E40" s="10">
+      <c r="E40" s="7">
         <v>428.13</v>
       </c>
-      <c r="F40" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G40" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H40" s="10">
+      <c r="F40" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G40" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H40" s="7">
         <v>0.1</v>
       </c>
-      <c r="I40" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="J40" s="10" t="s">
+      <c r="I40" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="K40" s="10">
-        <v>1</v>
-      </c>
-      <c r="L40" s="12">
+      <c r="J40" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="K40" s="9">
         <v>45337</v>
       </c>
-      <c r="M40" s="12">
+      <c r="L40" s="9">
         <v>45347</v>
       </c>
-      <c r="N40" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O40">
+      <c r="M40" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N40">
         <f t="shared" si="0"/>
         <v>5993.82</v>
       </c>
     </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A41" s="14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A41" s="7">
         <v>2023</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="10">
+      <c r="B41" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D41" s="7">
         <v>2</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="7">
         <v>503.28</v>
       </c>
-      <c r="F41" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G41" s="10" t="s">
+      <c r="F41" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G41" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H41" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I41" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H41" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I41" s="10" t="s">
+      <c r="J41" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J41" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K41" s="10">
-        <v>0</v>
-      </c>
-      <c r="L41" s="12">
+      <c r="K41" s="9">
         <v>45086</v>
       </c>
-      <c r="M41" s="12">
+      <c r="L41" s="9">
         <v>45094</v>
       </c>
-      <c r="N41" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O41">
+      <c r="M41" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N41">
         <f t="shared" si="0"/>
         <v>1006.56</v>
       </c>
     </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A42" s="14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A42" s="7">
         <v>2023</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" s="10">
+      <c r="B42" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D42" s="7">
         <v>5</v>
       </c>
-      <c r="E42" s="10">
+      <c r="E42" s="7">
         <v>470.32</v>
       </c>
-      <c r="F42" s="10" t="s">
+      <c r="F42" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G42" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G42" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H42" s="10">
+      <c r="H42" s="7">
         <v>0.1</v>
       </c>
-      <c r="I42" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J42" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K42" s="10">
-        <v>0</v>
-      </c>
-      <c r="L42" s="12">
+      <c r="I42" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J42" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K42" s="9">
         <v>45148</v>
       </c>
-      <c r="M42" s="12">
+      <c r="L42" s="9">
         <v>45152</v>
       </c>
-      <c r="N42" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O42">
+      <c r="M42" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N42">
         <f t="shared" si="0"/>
         <v>2351.6</v>
       </c>
     </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A43" s="14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A43" s="7">
         <v>2024</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C43" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" s="10">
+      <c r="B43" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="7">
         <v>20</v>
       </c>
-      <c r="E43" s="10">
+      <c r="E43" s="7">
         <v>65.17</v>
       </c>
-      <c r="F43" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="G43" s="10" t="s">
+      <c r="F43" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H43" s="7">
+        <v>0.05</v>
+      </c>
+      <c r="I43" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="H43" s="10">
-        <v>0.05</v>
-      </c>
-      <c r="I43" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J43" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K43" s="10">
-        <v>0</v>
-      </c>
-      <c r="L43" s="12">
+      <c r="J43" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K43" s="9">
         <v>45459</v>
       </c>
-      <c r="M43" s="12">
+      <c r="L43" s="9">
         <v>45468</v>
       </c>
-      <c r="N43" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O43">
+      <c r="M43" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N43">
         <f t="shared" si="0"/>
         <v>1303.4000000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A44" s="14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A44" s="7">
         <v>2025</v>
       </c>
-      <c r="B44" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C44" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D44" s="10">
+      <c r="B44" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D44" s="7">
         <v>12</v>
       </c>
-      <c r="E44" s="10">
+      <c r="E44" s="7">
         <v>36.17</v>
       </c>
-      <c r="F44" s="10" t="s">
+      <c r="F44" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G44" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="G44" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H44" s="10">
+      <c r="H44" s="7">
         <v>0</v>
       </c>
-      <c r="I44" s="10" t="s">
+      <c r="I44" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J44" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="J44" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K44" s="10">
-        <v>0</v>
-      </c>
-      <c r="L44" s="12">
+      <c r="K44" s="9">
         <v>45130</v>
       </c>
-      <c r="M44" s="12">
+      <c r="L44" s="9">
         <v>45133</v>
       </c>
-      <c r="N44" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O44">
+      <c r="M44" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N44">
         <f t="shared" si="0"/>
         <v>434.04</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A45" s="14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A45" s="7">
         <v>2025</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="C45" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D45" s="10">
+      <c r="B45" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D45" s="7">
         <v>4</v>
       </c>
-      <c r="E45" s="10">
+      <c r="E45" s="7">
         <v>459.31</v>
       </c>
-      <c r="F45" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G45" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="H45" s="10">
+      <c r="F45" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G45" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="H45" s="7">
         <v>0.15</v>
       </c>
-      <c r="I45" s="10" t="s">
-        <v>80</v>
-      </c>
-      <c r="J45" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K45" s="10">
-        <v>1</v>
-      </c>
-      <c r="L45" s="12">
+      <c r="I45" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J45" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K45" s="9">
         <v>45066</v>
       </c>
-      <c r="M45" s="12">
+      <c r="L45" s="9">
         <v>45073</v>
       </c>
-      <c r="N45" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="O45">
+      <c r="M45" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="N45">
         <f t="shared" si="0"/>
         <v>1837.24</v>
       </c>
     </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A46" s="14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A46" s="7">
         <v>2023</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C46" s="10" t="s">
-        <v>59</v>
-      </c>
-      <c r="D46" s="10">
+      <c r="B46" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="D46" s="7">
         <v>2</v>
       </c>
-      <c r="E46" s="10">
+      <c r="E46" s="7">
         <v>416.06</v>
       </c>
-      <c r="F46" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G46" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H46" s="10">
+      <c r="F46" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G46" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H46" s="7">
         <v>0.05</v>
       </c>
-      <c r="I46" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J46" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="K46" s="10">
-        <v>0</v>
-      </c>
-      <c r="L46" s="12">
+      <c r="I46" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J46" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="K46" s="9">
         <v>45107</v>
       </c>
-      <c r="M46" s="12">
+      <c r="L46" s="9">
         <v>45111</v>
       </c>
-      <c r="N46" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O46">
+      <c r="M46" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N46">
         <f t="shared" si="0"/>
         <v>832.12</v>
       </c>
     </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A47" s="14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A47" s="7">
         <v>2023</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C47" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D47" s="10">
+      <c r="B47" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D47" s="7">
         <v>16</v>
       </c>
-      <c r="E47" s="10">
+      <c r="E47" s="7">
         <v>302.58</v>
       </c>
-      <c r="F47" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G47" s="10" t="s">
+      <c r="F47" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G47" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H47" s="7">
+        <v>0</v>
+      </c>
+      <c r="I47" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="H47" s="10">
-        <v>0</v>
-      </c>
-      <c r="I47" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="J47" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K47" s="10">
-        <v>1</v>
-      </c>
-      <c r="L47" s="12">
+      <c r="J47" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K47" s="9">
         <v>45447</v>
       </c>
-      <c r="M47" s="12">
+      <c r="L47" s="9">
         <v>45457</v>
       </c>
-      <c r="N47" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="O47">
+      <c r="M47" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="N47">
         <f t="shared" si="0"/>
         <v>4841.28</v>
       </c>
     </row>
-    <row r="48" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A48" s="14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A48" s="7">
         <v>2025</v>
       </c>
-      <c r="B48" s="10" t="s">
+      <c r="B48" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="D48" s="7">
+        <v>11</v>
+      </c>
+      <c r="E48" s="7">
+        <v>33.130000000000003</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G48" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H48" s="7">
+        <v>0.15</v>
+      </c>
+      <c r="I48" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J48" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="K48" s="9">
+        <v>45691</v>
+      </c>
+      <c r="L48" s="9">
+        <v>45693</v>
+      </c>
+      <c r="M48" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D48" s="10">
-        <v>11</v>
-      </c>
-      <c r="E48" s="10">
-        <v>33.130000000000003</v>
-      </c>
-      <c r="F48" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G48" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H48" s="10">
-        <v>0.15</v>
-      </c>
-      <c r="I48" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J48" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="K48" s="10">
-        <v>0</v>
-      </c>
-      <c r="L48" s="12">
-        <v>45691</v>
-      </c>
-      <c r="M48" s="12">
-        <v>45693</v>
-      </c>
-      <c r="N48" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="O48">
+      <c r="N48">
         <f t="shared" si="0"/>
         <v>364.43</v>
       </c>
     </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A49" s="14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A49" s="7">
         <v>2025</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C49" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="D49" s="10">
+      <c r="B49" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="D49" s="7">
         <v>8</v>
       </c>
-      <c r="E49" s="10">
+      <c r="E49" s="7">
         <v>582.52</v>
       </c>
-      <c r="F49" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="G49" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H49" s="10">
+      <c r="F49" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="G49" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H49" s="7">
         <v>0.15</v>
       </c>
-      <c r="I49" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="J49" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K49" s="10">
-        <v>0</v>
-      </c>
-      <c r="L49" s="12">
+      <c r="I49" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="J49" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K49" s="9">
         <v>45300</v>
       </c>
-      <c r="M49" s="12">
+      <c r="L49" s="9">
         <v>45304</v>
       </c>
-      <c r="N49" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="O49">
+      <c r="M49" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="N49">
         <f t="shared" si="0"/>
         <v>4660.16</v>
       </c>
     </row>
-    <row r="50" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A50" s="14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A50" s="7">
         <v>2024</v>
       </c>
-      <c r="B50" s="10" t="s">
+      <c r="B50" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C50" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C50" s="10" t="s">
+      <c r="D50" s="7">
+        <v>5</v>
+      </c>
+      <c r="E50" s="7">
+        <v>165.15</v>
+      </c>
+      <c r="F50" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="G50" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="H50" s="7">
+        <v>0.1</v>
+      </c>
+      <c r="I50" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="J50" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="K50" s="9">
+        <v>45365</v>
+      </c>
+      <c r="L50" s="9">
+        <v>45367</v>
+      </c>
+      <c r="M50" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D50" s="10">
-        <v>5</v>
-      </c>
-      <c r="E50" s="10">
-        <v>165.15</v>
-      </c>
-      <c r="F50" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="G50" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="H50" s="10">
-        <v>0.1</v>
-      </c>
-      <c r="I50" s="10" t="s">
-        <v>62</v>
-      </c>
-      <c r="J50" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="K50" s="10">
-        <v>0</v>
-      </c>
-      <c r="L50" s="12">
-        <v>45365</v>
-      </c>
-      <c r="M50" s="12">
-        <v>45367</v>
-      </c>
-      <c r="N50" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="O50">
+      <c r="N50">
         <f t="shared" si="0"/>
         <v>825.75</v>
       </c>
     </row>
-    <row r="54" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
+    <row r="69" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A69" s="31" t="s">
         <v>92</v>
       </c>
-      <c r="B54" s="15">
+      <c r="B69" s="31"/>
+      <c r="C69" s="31"/>
+      <c r="D69" s="31"/>
+      <c r="E69" s="32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F69" s="32"/>
+      <c r="G69" s="32"/>
+      <c r="H69" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="I69" s="33"/>
+      <c r="J69" s="33"/>
+    </row>
+    <row r="70" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B70" s="11">
+        <v>2023</v>
+      </c>
+      <c r="C70" s="11">
         <v>2024</v>
       </c>
-      <c r="C54" s="15"/>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>30</v>
-      </c>
-      <c r="B55">
-        <f>SUMIF(A2:A50,B54,O2:O50)</f>
-        <v>56788.600000000006</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>92</v>
-      </c>
-      <c r="B57">
+      <c r="D70" s="11">
+        <v>2025</v>
+      </c>
+      <c r="E70" s="13">
         <v>2023</v>
       </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>45</v>
-      </c>
-      <c r="B58" t="s">
+      <c r="F70" s="13">
+        <v>2024</v>
+      </c>
+      <c r="G70" s="13">
+        <v>2025</v>
+      </c>
+      <c r="H70" s="13">
+        <v>2023</v>
+      </c>
+      <c r="I70" s="13">
+        <v>2024</v>
+      </c>
+      <c r="J70" s="13">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A71" s="16" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>94</v>
-      </c>
-      <c r="B59">
-        <f>SUMIFS(O2:O50,A2:A50,B57,B2:B50,B58)</f>
-        <v>21630.219999999998</v>
-      </c>
-    </row>
-    <row r="61" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A61" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
-      <c r="D61" s="16"/>
-      <c r="E61">
-        <v>2023</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A62" t="s">
-        <v>96</v>
-      </c>
-      <c r="B62">
-        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM(A62),$A$2:$A$50,$E$61)</f>
+      <c r="B71" s="22">
+        <f t="shared" ref="B71:D75" si="1">SUMIFS($N$2:$N$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
         <v>1838.6799999999998</v>
       </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
-        <v>91</v>
-      </c>
-      <c r="B63">
-        <f t="shared" ref="B63:B66" si="1">SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM(A63),$A$2:$A$50,$E$61)</f>
+      <c r="C71" s="22">
+        <f t="shared" si="1"/>
+        <v>33536.300000000003</v>
+      </c>
+      <c r="D71" s="22">
+        <f t="shared" si="1"/>
+        <v>10771.32</v>
+      </c>
+      <c r="E71" s="19">
+        <f>COUNTIFS($C$2:$C$50,TRIM($A71),$A$2:$A$50,E$70)</f>
+        <v>2</v>
+      </c>
+      <c r="F71" s="19">
+        <f t="shared" ref="F71:G71" si="2">COUNTIFS($C$2:$C$50,TRIM($A71),$A$2:$A$50,F$70)</f>
+        <v>2</v>
+      </c>
+      <c r="G71" s="19">
+        <f t="shared" si="2"/>
+        <v>4</v>
+      </c>
+      <c r="H71" s="20">
+        <f>E71/SUM(E$71:E$75)</f>
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I71" s="20">
+        <f t="shared" ref="I71:J75" si="3">F71/SUM(F$71:F$75)</f>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="J71" s="20">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A72" s="16" t="s">
+        <v>90</v>
+      </c>
+      <c r="B72" s="22">
+        <f t="shared" si="1"/>
         <v>2351.6</v>
       </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
-        <v>76</v>
-      </c>
-      <c r="B64">
+      <c r="C72" s="22">
+        <f t="shared" si="1"/>
+        <v>1303.4000000000001</v>
+      </c>
+      <c r="D72" s="22">
+        <f t="shared" si="1"/>
+        <v>7831.0599999999995</v>
+      </c>
+      <c r="E72" s="19">
+        <f t="shared" ref="E72:G75" si="4">COUNTIFS($C$2:$C$50,TRIM($A72),$A$2:$A$50,E$70)</f>
+        <v>1</v>
+      </c>
+      <c r="F72" s="19">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="G72" s="19">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="H72" s="20">
+        <f t="shared" ref="H72:H75" si="5">E72/SUM(E$71:E$75)</f>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I72" s="20">
+        <f t="shared" si="3"/>
+        <v>9.0909090909090912E-2</v>
+      </c>
+      <c r="J72" s="20">
+        <f t="shared" si="3"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A73" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73" s="22">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65">
+      <c r="C73" s="22">
+        <f t="shared" si="1"/>
+        <v>7149.380000000001</v>
+      </c>
+      <c r="D73" s="22">
+        <f t="shared" si="1"/>
+        <v>14896.43</v>
+      </c>
+      <c r="E73" s="19">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="F73" s="19">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="G73" s="19">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="H73" s="20">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I73" s="20">
+        <f t="shared" si="3"/>
+        <v>0.18181818181818182</v>
+      </c>
+      <c r="J73" s="20">
+        <f t="shared" si="3"/>
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A74" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="B74" s="22">
         <f t="shared" si="1"/>
         <v>12591.11</v>
       </c>
-    </row>
-    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
-        <v>90</v>
-      </c>
-      <c r="B66">
+      <c r="C74" s="22">
+        <f t="shared" si="1"/>
+        <v>12411.22</v>
+      </c>
+      <c r="D74" s="22">
+        <f t="shared" si="1"/>
+        <v>14386.29</v>
+      </c>
+      <c r="E74" s="19">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="F74" s="19">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="G74" s="19">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="H74" s="20">
+        <f t="shared" si="5"/>
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="I74" s="20">
+        <f t="shared" si="3"/>
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="J74" s="20">
+        <f t="shared" si="3"/>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A75" s="16" t="s">
+        <v>89</v>
+      </c>
+      <c r="B75" s="22">
         <f t="shared" si="1"/>
         <v>4841.28</v>
       </c>
-    </row>
-    <row r="69" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="17" t="s">
-        <v>97</v>
-      </c>
-      <c r="B69" s="17"/>
-      <c r="C69" s="17"/>
-      <c r="D69" s="17"/>
-      <c r="E69" s="20" t="s">
-        <v>102</v>
-      </c>
-      <c r="F69" s="20"/>
-      <c r="G69" s="20"/>
-      <c r="H69" s="28" t="s">
-        <v>103</v>
-      </c>
-      <c r="I69" s="28"/>
-      <c r="J69" s="28"/>
-    </row>
-    <row r="70" spans="1:10" ht="24.6" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B70" s="18">
-        <v>2023</v>
-      </c>
-      <c r="C70" s="18">
-        <v>2024</v>
-      </c>
-      <c r="D70" s="18">
-        <v>2025</v>
-      </c>
-      <c r="E70" s="21">
-        <v>2023</v>
-      </c>
-      <c r="F70" s="21">
-        <v>2024</v>
-      </c>
-      <c r="G70" s="21">
-        <v>2025</v>
-      </c>
-      <c r="H70" s="21">
-        <v>2023</v>
-      </c>
-      <c r="I70" s="21">
-        <v>2024</v>
-      </c>
-      <c r="J70" s="21">
-        <v>2025</v>
-      </c>
-    </row>
-    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A71" s="24" t="s">
-        <v>59</v>
-      </c>
-      <c r="B71" s="31">
-        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
-        <v>1838.6799999999998</v>
-      </c>
-      <c r="C71" s="31">
-        <f t="shared" ref="C71:D75" si="2">SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,C$70)</f>
-        <v>33536.300000000003</v>
-      </c>
-      <c r="D71" s="31">
-        <f t="shared" si="2"/>
-        <v>10771.32</v>
-      </c>
-      <c r="E71" s="27">
-        <f>COUNTIFS($C$2:$C$50,TRIM($A71),$A$2:$A$50,E$70)</f>
+      <c r="C75" s="22">
+        <f t="shared" si="1"/>
+        <v>1622.03</v>
+      </c>
+      <c r="D75" s="22">
+        <f t="shared" si="1"/>
+        <v>8493.4700000000012</v>
+      </c>
+      <c r="E75" s="19">
+        <f t="shared" si="4"/>
+        <v>1</v>
+      </c>
+      <c r="F75" s="19">
+        <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="F71" s="27">
-        <f t="shared" ref="F71:G71" si="3">COUNTIFS($C$2:$C$50,TRIM($A71),$A$2:$A$50,F$70)</f>
-        <v>2</v>
-      </c>
-      <c r="G71" s="27">
+      <c r="G75" s="19">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="H75" s="20">
+        <f t="shared" si="5"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="I75" s="20">
         <f t="shared" si="3"/>
-        <v>4</v>
-      </c>
-      <c r="H71" s="29">
-        <f>E71/SUM(E$71:E$75)</f>
-        <v>0.2857142857142857</v>
-      </c>
-      <c r="I71" s="29">
-        <f t="shared" ref="I71:J75" si="4">F71/SUM(F$71:F$75)</f>
         <v>0.18181818181818182</v>
       </c>
-      <c r="J71" s="29">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A72" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="B72" s="31">
-        <f t="shared" ref="B72:B75" si="5">SUMIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,B$70)</f>
-        <v>2351.6</v>
-      </c>
-      <c r="C72" s="31">
-        <f t="shared" si="2"/>
-        <v>1303.4000000000001</v>
-      </c>
-      <c r="D72" s="31">
-        <f t="shared" si="2"/>
-        <v>7831.0599999999995</v>
-      </c>
-      <c r="E72" s="27">
-        <f t="shared" ref="D72:G75" si="6">COUNTIFS($C$2:$C$50,TRIM($A72),$A$2:$A$50,E$70)</f>
-        <v>1</v>
-      </c>
-      <c r="F72" s="27">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="G72" s="27">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="H72" s="29">
-        <f t="shared" ref="H72:H75" si="7">E72/SUM(E$71:E$75)</f>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="I72" s="29">
-        <f t="shared" si="4"/>
-        <v>9.0909090909090912E-2</v>
-      </c>
-      <c r="J72" s="29">
-        <f t="shared" si="4"/>
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A73" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="B73" s="31">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="C73" s="31">
-        <f t="shared" si="2"/>
-        <v>7149.380000000001</v>
-      </c>
-      <c r="D73" s="31">
-        <f t="shared" si="2"/>
-        <v>14896.43</v>
-      </c>
-      <c r="E73" s="27">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="F73" s="27">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="G73" s="27">
-        <f t="shared" si="6"/>
-        <v>7</v>
-      </c>
-      <c r="H73" s="29">
-        <f t="shared" si="7"/>
-        <v>0</v>
-      </c>
-      <c r="I73" s="29">
-        <f t="shared" si="4"/>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="J73" s="29">
-        <f t="shared" si="4"/>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A74" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="B74" s="31">
-        <f t="shared" si="5"/>
-        <v>12591.11</v>
-      </c>
-      <c r="C74" s="31">
-        <f t="shared" si="2"/>
-        <v>12411.22</v>
-      </c>
-      <c r="D74" s="31">
-        <f t="shared" si="2"/>
-        <v>14386.29</v>
-      </c>
-      <c r="E74" s="27">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="F74" s="27">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="G74" s="27">
-        <f t="shared" si="6"/>
-        <v>4</v>
-      </c>
-      <c r="H74" s="29">
-        <f t="shared" si="7"/>
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="I74" s="29">
-        <f t="shared" si="4"/>
-        <v>0.36363636363636365</v>
-      </c>
-      <c r="J74" s="29">
-        <f t="shared" si="4"/>
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A75" s="24" t="s">
-        <v>90</v>
-      </c>
-      <c r="B75" s="31">
-        <f t="shared" si="5"/>
-        <v>4841.28</v>
-      </c>
-      <c r="C75" s="31">
-        <f t="shared" si="2"/>
-        <v>1622.03</v>
-      </c>
-      <c r="D75" s="31">
-        <f t="shared" si="2"/>
-        <v>8493.4700000000012</v>
-      </c>
-      <c r="E75" s="27">
-        <f t="shared" si="6"/>
-        <v>1</v>
-      </c>
-      <c r="F75" s="27">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="G75" s="27">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="H75" s="29">
-        <f t="shared" si="7"/>
-        <v>0.14285714285714285</v>
-      </c>
-      <c r="I75" s="29">
-        <f t="shared" si="4"/>
-        <v>0.18181818181818182</v>
-      </c>
-      <c r="J75" s="29">
-        <f t="shared" si="4"/>
+      <c r="J75" s="20">
+        <f t="shared" si="3"/>
         <v>0.15</v>
       </c>
     </row>
@@ -6534,134 +9506,134 @@
       <c r="J76" s="1"/>
     </row>
     <row r="77" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="D77" s="30" t="s">
+      <c r="D77" s="21" t="s">
         <v>8</v>
       </c>
-      <c r="E77" s="25">
+      <c r="E77" s="17">
         <f>SUM(E71:E75)</f>
         <v>7</v>
       </c>
-      <c r="F77" s="25">
+      <c r="F77" s="17">
         <f>SUM(F71:F75)</f>
         <v>11</v>
       </c>
-      <c r="G77" s="25">
+      <c r="G77" s="17">
         <f>SUM(G71:G75)</f>
         <v>20</v>
       </c>
-      <c r="H77" s="26">
+      <c r="H77" s="18">
         <f>SUM(H71:H75)</f>
         <v>1</v>
       </c>
-      <c r="I77" s="26">
-        <f t="shared" ref="I77:J77" si="8">SUM(I71:I75)</f>
+      <c r="I77" s="18">
+        <f t="shared" ref="I77:J77" si="6">SUM(I71:I75)</f>
         <v>1</v>
       </c>
-      <c r="J77" s="26">
-        <f t="shared" si="8"/>
+      <c r="J77" s="18">
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A80" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="B80" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="C80" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E80" s="23" t="s">
-        <v>101</v>
+      <c r="A80" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="E80" s="15" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A81" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
+      <c r="A81" s="14">
+        <f t="shared" ref="A81:C85" si="7">AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
         <v>919.33999999999992</v>
       </c>
-      <c r="B81" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,C$70)</f>
+      <c r="B81" s="14">
+        <f t="shared" si="7"/>
         <v>16768.150000000001</v>
       </c>
-      <c r="C81" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,D$70)</f>
+      <c r="C81" s="14">
+        <f t="shared" si="7"/>
         <v>2692.83</v>
       </c>
-      <c r="E81" s="22">
+      <c r="E81" s="14">
         <f>IFERROR(A81,"Something went wrong")</f>
         <v>919.33999999999992</v>
       </c>
     </row>
     <row r="82" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A82" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,B$70)</f>
+      <c r="A82" s="14">
+        <f t="shared" si="7"/>
         <v>2351.6</v>
       </c>
-      <c r="B82" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,C$70)</f>
+      <c r="B82" s="14">
+        <f t="shared" si="7"/>
         <v>1303.4000000000001</v>
       </c>
-      <c r="C82" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A72),$A$2:$A$50,D$70)</f>
+      <c r="C82" s="14">
+        <f t="shared" si="7"/>
         <v>3915.5299999999997</v>
       </c>
-      <c r="E82" s="22">
+      <c r="E82" s="14">
         <f>IFERROR(A82,"Something went wrong")</f>
         <v>2351.6</v>
       </c>
     </row>
     <row r="83" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A83" s="22" t="e">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A73),$A$2:$A$50,B$70)</f>
+      <c r="A83" s="14" t="e">
+        <f t="shared" si="7"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="B83" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A73),$A$2:$A$50,C$70)</f>
+      <c r="B83" s="14">
+        <f t="shared" si="7"/>
         <v>3574.6900000000005</v>
       </c>
-      <c r="C83" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A73),$A$2:$A$50,D$70)</f>
+      <c r="C83" s="14">
+        <f t="shared" si="7"/>
         <v>2128.0614285714287</v>
       </c>
-      <c r="E83" s="22" t="str">
+      <c r="E83" s="14" t="str">
         <f>IFERROR(A83,"Something went wrong")</f>
         <v>Something went wrong</v>
       </c>
     </row>
     <row r="84" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A84" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A74),$A$2:$A$50,B$70)</f>
+      <c r="A84" s="14">
+        <f t="shared" si="7"/>
         <v>4197.0366666666669</v>
       </c>
-      <c r="B84" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A74),$A$2:$A$50,C$70)</f>
+      <c r="B84" s="14">
+        <f t="shared" si="7"/>
         <v>3102.8049999999998</v>
       </c>
-      <c r="C84" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A74),$A$2:$A$50,D$70)</f>
+      <c r="C84" s="14">
+        <f t="shared" si="7"/>
         <v>3596.5725000000002</v>
       </c>
-      <c r="E84" s="22">
+      <c r="E84" s="14">
         <f>IFERROR(A84,"Something went wrong")</f>
         <v>4197.0366666666669</v>
       </c>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A85" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A75),$A$2:$A$50,B$70)</f>
+      <c r="A85" s="14">
+        <f t="shared" si="7"/>
         <v>4841.28</v>
       </c>
-      <c r="B85" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A75),$A$2:$A$50,C$70)</f>
+      <c r="B85" s="14">
+        <f t="shared" si="7"/>
         <v>811.01499999999999</v>
       </c>
-      <c r="C85" s="22">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM($A75),$A$2:$A$50,D$70)</f>
+      <c r="C85" s="14">
+        <f t="shared" si="7"/>
         <v>2831.1566666666672</v>
       </c>
-      <c r="E85" s="22">
+      <c r="E85" s="14">
         <f>IFERROR(A85,"Something went wrong")</f>
         <v>4841.28</v>
       </c>
@@ -6680,178 +9652,205 @@
     </row>
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
-      <c r="B88" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C88" s="35"/>
-      <c r="D88" s="35"/>
-      <c r="E88" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="F88" s="36"/>
-      <c r="G88" s="36"/>
-      <c r="H88" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="I88" s="37"/>
-      <c r="J88" s="37"/>
+      <c r="B88" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C88" s="34"/>
+      <c r="D88" s="34"/>
+      <c r="E88" s="35" t="s">
+        <v>75</v>
+      </c>
+      <c r="F88" s="35"/>
+      <c r="G88" s="35"/>
+      <c r="H88" s="36" t="s">
+        <v>90</v>
+      </c>
+      <c r="I88" s="36"/>
+      <c r="J88" s="36"/>
     </row>
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
-      <c r="B89" s="38" t="s">
-        <v>102</v>
-      </c>
-      <c r="C89" s="38" t="s">
-        <v>104</v>
-      </c>
-      <c r="D89" s="38" t="s">
-        <v>105</v>
-      </c>
-      <c r="E89" s="33" t="s">
-        <v>102</v>
-      </c>
-      <c r="F89" s="33" t="s">
-        <v>104</v>
-      </c>
-      <c r="G89" s="33" t="s">
-        <v>105</v>
-      </c>
-      <c r="H89" s="39" t="s">
-        <v>102</v>
-      </c>
-      <c r="I89" s="39" t="s">
-        <v>104</v>
-      </c>
-      <c r="J89" s="39" t="s">
-        <v>105</v>
+      <c r="B89" s="26" t="s">
+        <v>97</v>
+      </c>
+      <c r="C89" s="26" t="s">
+        <v>99</v>
+      </c>
+      <c r="D89" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="E89" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G89" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="H89" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="I89" s="27" t="s">
+        <v>99</v>
+      </c>
+      <c r="J89" s="27" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A90" s="32">
+      <c r="A90" s="23">
         <v>2023</v>
       </c>
-      <c r="B90" s="34">
+      <c r="B90" s="25">
         <f>COUNTIFS($C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A90)</f>
         <v>2</v>
       </c>
-      <c r="C90" s="34">
-        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,B$88,$A$2:$A$50,$A90)</f>
+      <c r="C90" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,B$88,$A$2:$A$50,$A90)</f>
         <v>1838.6799999999998</v>
       </c>
-      <c r="D90" s="34">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A90)</f>
+      <c r="D90" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A90)</f>
         <v>919.33999999999992</v>
       </c>
-      <c r="E90" s="34">
+      <c r="E90" s="25">
         <f>COUNTIFS($C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A90)</f>
         <v>0</v>
       </c>
-      <c r="F90" s="34">
-        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,E$88,$A$2:$A$50,$A90)</f>
+      <c r="F90" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,E$88,$A$2:$A$50,$A90)</f>
         <v>0</v>
       </c>
-      <c r="G90" s="34" t="e">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A90)</f>
+      <c r="G90" s="25" t="e">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A90)</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H90" s="34">
+      <c r="H90" s="25">
         <f>COUNTIFS($C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A90)</f>
         <v>1</v>
       </c>
-      <c r="I90" s="34">
-        <f>SUMIFS($O$2:$O$50,$C$2:$C$50,H$88,$A$2:$A$50,$A90)</f>
+      <c r="I90" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,H$88,$A$2:$A$50,$A90)</f>
         <v>2351.6</v>
       </c>
-      <c r="J90" s="34">
-        <f>AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A90)</f>
+      <c r="J90" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A90)</f>
         <v>2351.6</v>
       </c>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A91" s="32">
+      <c r="A91" s="23">
         <v>2024</v>
       </c>
-      <c r="B91" s="34">
-        <f t="shared" ref="B91:B92" si="9">COUNTIFS($C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A91)</f>
+      <c r="B91" s="25">
+        <f t="shared" ref="B91:B92" si="8">COUNTIFS($C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A91)</f>
         <v>2</v>
       </c>
-      <c r="C91" s="34">
-        <f t="shared" ref="C91:C92" si="10">SUMIFS($O$2:$O$50,$C$2:$C$50,B$88,$A$2:$A$50,$A91)</f>
+      <c r="C91" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,B$88,$A$2:$A$50,$A91)</f>
         <v>33536.300000000003</v>
       </c>
-      <c r="D91" s="34">
-        <f t="shared" ref="D91:D92" si="11">AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A91)</f>
+      <c r="D91" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A91)</f>
         <v>16768.150000000001</v>
       </c>
-      <c r="E91" s="34">
-        <f t="shared" ref="E91:E92" si="12">COUNTIFS($C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A91)</f>
+      <c r="E91" s="25">
+        <f t="shared" ref="E91:E92" si="9">COUNTIFS($C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A91)</f>
         <v>2</v>
       </c>
-      <c r="F91" s="34">
-        <f t="shared" ref="F91:F92" si="13">SUMIFS($O$2:$O$50,$C$2:$C$50,E$88,$A$2:$A$50,$A91)</f>
+      <c r="F91" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,E$88,$A$2:$A$50,$A91)</f>
         <v>7149.380000000001</v>
       </c>
-      <c r="G91" s="34">
-        <f t="shared" ref="G91:G92" si="14">AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A91)</f>
+      <c r="G91" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A91)</f>
         <v>3574.6900000000005</v>
       </c>
-      <c r="H91" s="34">
-        <f t="shared" ref="H91:H92" si="15">COUNTIFS($C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A91)</f>
+      <c r="H91" s="25">
+        <f t="shared" ref="H91:H92" si="10">COUNTIFS($C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A91)</f>
         <v>1</v>
       </c>
-      <c r="I91" s="34">
-        <f t="shared" ref="I91:I92" si="16">SUMIFS($O$2:$O$50,$C$2:$C$50,H$88,$A$2:$A$50,$A91)</f>
+      <c r="I91" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,H$88,$A$2:$A$50,$A91)</f>
         <v>1303.4000000000001</v>
       </c>
-      <c r="J91" s="34">
-        <f t="shared" ref="J91:J92" si="17">AVERAGEIFS($O$2:$O$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A91)</f>
+      <c r="J91" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A91)</f>
         <v>1303.4000000000001</v>
       </c>
     </row>
     <row r="92" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A92" s="32">
+      <c r="A92" s="23">
         <v>2025</v>
       </c>
-      <c r="B92" s="34">
+      <c r="B92" s="25">
+        <f t="shared" si="8"/>
+        <v>4</v>
+      </c>
+      <c r="C92" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,B$88,$A$2:$A$50,$A92)</f>
+        <v>10771.32</v>
+      </c>
+      <c r="D92" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(B$88),$A$2:$A$50,$A92)</f>
+        <v>2692.83</v>
+      </c>
+      <c r="E92" s="25">
         <f t="shared" si="9"/>
-        <v>4</v>
-      </c>
-      <c r="C92" s="34">
+        <v>7</v>
+      </c>
+      <c r="F92" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,E$88,$A$2:$A$50,$A92)</f>
+        <v>14896.43</v>
+      </c>
+      <c r="G92" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(E$88),$A$2:$A$50,$A92)</f>
+        <v>2128.0614285714287</v>
+      </c>
+      <c r="H92" s="25">
         <f t="shared" si="10"/>
-        <v>10771.32</v>
-      </c>
-      <c r="D92" s="34">
-        <f t="shared" si="11"/>
-        <v>2692.83</v>
-      </c>
-      <c r="E92" s="34">
-        <f t="shared" si="12"/>
-        <v>7</v>
-      </c>
-      <c r="F92" s="34">
-        <f t="shared" si="13"/>
-        <v>14896.43</v>
-      </c>
-      <c r="G92" s="34">
-        <f t="shared" si="14"/>
-        <v>2128.0614285714287</v>
-      </c>
-      <c r="H92" s="34">
-        <f t="shared" si="15"/>
         <v>2</v>
       </c>
-      <c r="I92" s="34">
-        <f t="shared" si="16"/>
+      <c r="I92" s="25">
+        <f>SUMIFS($N$2:$N$50,$C$2:$C$50,H$88,$A$2:$A$50,$A92)</f>
         <v>7831.0599999999995</v>
       </c>
-      <c r="J92" s="34">
-        <f t="shared" si="17"/>
+      <c r="J92" s="25">
+        <f>AVERAGEIFS($N$2:$N$50,$C$2:$C$50,TRIM(H$88),$A$2:$A$50,$A92)</f>
         <v>3915.5299999999997</v>
       </c>
     </row>
+    <row r="106" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E106">
+        <v>1</v>
+      </c>
+      <c r="G106" cm="1">
+        <f t="array" ref="G106">_xlfn.IFS(E106 = 1, 10, E106= 2, 20)</f>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="107" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E107">
+        <v>2</v>
+      </c>
+      <c r="G107" cm="1">
+        <f t="array" ref="G107">_xlfn.IFS(E107 = 1, 10, E107= 2, 20)</f>
+        <v>20</v>
+      </c>
+    </row>
+    <row r="108" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E109">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A61:D61"/>
+  <mergeCells count="6">
     <mergeCell ref="A69:D69"/>
     <mergeCell ref="E69:G69"/>
     <mergeCell ref="H69:J69"/>
@@ -6859,42 +9858,47 @@
     <mergeCell ref="E88:G88"/>
     <mergeCell ref="H88:J88"/>
   </mergeCells>
-  <conditionalFormatting sqref="E81:E85">
-    <cfRule type="expression" dxfId="5" priority="11">
-      <formula>ISERROR(A81)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="H71:J75">
-    <cfRule type="expression" dxfId="4" priority="5">
-      <formula>H71=MAX(H$71:H$75)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E71:G75">
-    <cfRule type="expression" dxfId="3" priority="4">
-      <formula>E71=MAX(E$71:E$75)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B71:D75">
-    <cfRule type="expression" dxfId="2" priority="3">
-      <formula>B71=MAX(B$71:B$75)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <conditionalFormatting sqref="A81:A85">
-    <cfRule type="expression" dxfId="1" priority="2">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>A81=MAX(A$81:A$85)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81:C85">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="4" priority="1">
       <formula>B81=MAX(B$81:B$85)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="B71:D75">
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>B71=MAX(B$71:B$75)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E81:E85">
+    <cfRule type="expression" dxfId="2" priority="11">
+      <formula>ISERROR(A81)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E71:G75">
+    <cfRule type="expression" dxfId="1" priority="4">
+      <formula>E71=MAX(E$71:E$75)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H71:J75">
+    <cfRule type="expression" dxfId="0" priority="5">
+      <formula>H71=MAX(H$71:H$75)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C55" xr:uid="{7A1D44A2-8035-4DFE-8A51-7825B299FC79}">
+      <formula1>"Laptop, Tablet, Chair, Desk, Printer, Monitor, Phone, "</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC1EC01-3558-4CAF-8FA5-3C02BC76403B}">
   <dimension ref="C1:L72"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
@@ -6904,17 +9908,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12" x14ac:dyDescent="0.35">
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="E1" s="39"/>
+      <c r="F1" s="39"/>
+      <c r="G1" s="39"/>
+      <c r="H1" s="39"/>
+      <c r="I1" s="39"/>
+      <c r="J1" s="39"/>
+      <c r="K1" s="39"/>
+      <c r="L1" s="39"/>
     </row>
     <row r="2" spans="4:12" x14ac:dyDescent="0.35">
       <c r="D2" t="s">
@@ -7507,7 +10511,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08F756C-290F-404E-81ED-2B88E96B5E6A}">
   <dimension ref="B2:F7"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>

--- a/Excel_practice/practice_excel.xlsx
+++ b/Excel_practice/practice_excel.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Fiiit\Excel_practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7148AC2B-C614-4BFC-9B4E-B61E5696B324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC02C69-F425-47B3-A60A-779ED322FC5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{9582A52E-1B81-4984-BBE7-A03F4D74D0D3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{9582A52E-1B81-4984-BBE7-A03F4D74D0D3}"/>
   </bookViews>
   <sheets>
     <sheet name="Task 1" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,13 @@
     <sheet name="pivot chart" sheetId="6" r:id="rId3"/>
     <sheet name="Task 3" sheetId="4" r:id="rId4"/>
     <sheet name="Sheet1" sheetId="3" r:id="rId5"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId6"/>
+    <sheet name="Attendance" sheetId="7" r:id="rId6"/>
+    <sheet name="utils" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="months">utils!$D$2:$D$13</definedName>
+    <definedName name="no_of_holidays">Holidays[Holiday]</definedName>
+    <definedName name="no_of_years">Year[Years]</definedName>
     <definedName name="Slicer_CustomerType">#N/A</definedName>
     <definedName name="Slicer_PaymentMethod">#N/A</definedName>
     <definedName name="Slicer_Product">#N/A</definedName>
@@ -30,17 +34,17 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="0" r:id="rId7"/>
+    <pivotCache cacheId="0" r:id="rId8"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId8"/>
         <x14:slicerCache r:id="rId9"/>
         <x14:slicerCache r:id="rId10"/>
         <x14:slicerCache r:id="rId11"/>
         <x14:slicerCache r:id="rId12"/>
         <x14:slicerCache r:id="rId13"/>
+        <x14:slicerCache r:id="rId14"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -85,7 +89,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="474" uniqueCount="126">
   <si>
     <t>S.No</t>
   </si>
@@ -181,15 +185,6 @@
   </si>
   <si>
     <t>mixed reference</t>
-  </si>
-  <si>
-    <t>HTML</t>
-  </si>
-  <si>
-    <t>JS</t>
-  </si>
-  <si>
-    <t>Java</t>
   </si>
   <si>
     <t>cell reference</t>
@@ -407,16 +402,84 @@
   <si>
     <t>Sum of UnitPrice</t>
   </si>
+  <si>
+    <t>Years</t>
+  </si>
+  <si>
+    <t>Months</t>
+  </si>
+  <si>
+    <t>January</t>
+  </si>
+  <si>
+    <t>February</t>
+  </si>
+  <si>
+    <t>March</t>
+  </si>
+  <si>
+    <t>April</t>
+  </si>
+  <si>
+    <t>May</t>
+  </si>
+  <si>
+    <t>June</t>
+  </si>
+  <si>
+    <t>July</t>
+  </si>
+  <si>
+    <t>August</t>
+  </si>
+  <si>
+    <t>September</t>
+  </si>
+  <si>
+    <t>October</t>
+  </si>
+  <si>
+    <t>November</t>
+  </si>
+  <si>
+    <t>December</t>
+  </si>
+  <si>
+    <t>ATTENDANCE TRACKING SYSTEM</t>
+  </si>
+  <si>
+    <t>MONTH</t>
+  </si>
+  <si>
+    <t>YEAR</t>
+  </si>
+  <si>
+    <t>S.NO</t>
+  </si>
+  <si>
+    <t>Holiday</t>
+  </si>
+  <si>
+    <t>P COUNT</t>
+  </si>
+  <si>
+    <t>A COUNT</t>
+  </si>
+  <si>
+    <t>Percentage</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="165" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="167" formatCode="ddd"/>
+    <numFmt numFmtId="168" formatCode="dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -469,8 +532,22 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="23">
+  <fills count="24">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -603,8 +680,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -638,12 +721,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -748,12 +840,81 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{838E1F74-091B-422A-8F25-11DC4903382E}"/>
   </cellStyles>
-  <dxfs count="6">
+  <dxfs count="14">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="darkDown">
+          <fgColor auto="1"/>
+          <bgColor rgb="FF00B0F0"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
     <dxf>
       <fill>
         <gradientFill degree="90">
@@ -825,6 +986,9 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFCE3232"/>
+      <color rgb="FFDE4A22"/>
+      <color rgb="FFD85228"/>
       <color rgb="FF10A872"/>
     </mruColors>
   </colors>
@@ -837,6 +1001,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/activeX/activeX1.xml><?xml version="1.0" encoding="utf-8"?>
+<ax:ocx xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ax:classid="{D7053240-CE69-11CD-A777-00DD01143C57}" ax:persistence="persistStreamInit" r:id="rId1"/>
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4712,6 +4880,69 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+      <xdr:twoCellAnchor editAs="oneCell">
+        <xdr:from>
+          <xdr:col>3</xdr:col>
+          <xdr:colOff>106680</xdr:colOff>
+          <xdr:row>1</xdr:row>
+          <xdr:rowOff>106680</xdr:rowOff>
+        </xdr:from>
+        <xdr:to>
+          <xdr:col>6</xdr:col>
+          <xdr:colOff>220980</xdr:colOff>
+          <xdr:row>2</xdr:row>
+          <xdr:rowOff>205740</xdr:rowOff>
+        </xdr:to>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="6151" name="CommandButton1" hidden="1">
+              <a:extLst>
+                <a:ext uri="{63B3BB69-23CF-44E3-9099-C40C66FF867C}">
+                  <a14:compatExt spid="_x0000_s6151"/>
+                </a:ext>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000007180000}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvSpPr/>
+          </xdr:nvSpPr>
+          <xdr:spPr bwMode="auto">
+            <a:xfrm>
+              <a:off x="0" y="0"/>
+              <a:ext cx="0" cy="0"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:extLst>
+              <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
+                <a14:hiddenLine w="9525">
+                  <a:noFill/>
+                  <a:miter lim="800000"/>
+                  <a:headEnd/>
+                  <a:tailEnd/>
+                </a14:hiddenLine>
+              </a:ext>
+            </a:extLst>
+          </xdr:spPr>
+        </xdr:sp>
+        <xdr:clientData/>
+      </xdr:twoCellAnchor>
+    </mc:Choice>
+    <mc:Fallback/>
+  </mc:AlternateContent>
+</xdr:wsDr>
+</file>
+
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
 <pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Raj kumar" refreshedDate="46290.967947569443" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="49" xr:uid="{2FDE50FE-7957-47EE-B383-986769CD9CBB}">
   <cacheSource type="worksheet">
@@ -6179,6 +6410,26 @@
 </slicers>
 </file>
 
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2EBCA347-4C43-4782-B587-5DA1368DD27E}" name="Year" displayName="Year" ref="A1:A13" totalsRowShown="0" headerRowDxfId="5" dataDxfId="6">
+  <autoFilter ref="A1:A13" xr:uid="{2EBCA347-4C43-4782-B587-5DA1368DD27E}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{7EA50A58-FEC8-408A-9435-4CFA3928B564}" name="Years" dataDxfId="7"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{16D98FE3-64AB-430B-939F-A3710C3D56D7}" name="Holidays" displayName="Holidays" ref="G1:G19" totalsRowShown="0">
+  <autoFilter ref="G1:G19" xr:uid="{16D98FE3-64AB-430B-939F-A3710C3D56D7}"/>
+  <tableColumns count="1">
+    <tableColumn id="1" xr3:uid="{3748BBEA-7D06-43F3-A6C3-F81EE1CDDF83}" name="Holiday" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
@@ -6476,6 +6727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1C0E12B-972A-40A9-953C-C64BA2031B55}">
+  <sheetPr codeName="Sheet2"/>
   <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6788,6 +7040,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2ECEBBF-AF0D-454E-AADB-6DF00E7846E7}">
+  <sheetPr codeName="Sheet3"/>
   <dimension ref="A2:D9"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6803,45 +7056,45 @@
   <sheetData>
     <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="28" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="B3" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="28" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C6" t="s">
         <v>101</v>
       </c>
-      <c r="B6" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" t="s">
-        <v>104</v>
-      </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="B7">
         <v>178.55</v>
@@ -6855,7 +7108,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="30" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B8">
         <v>178.55</v>
@@ -6869,7 +7122,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B9">
         <v>178.55</v>
@@ -6896,6 +7149,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D954C92-FCF0-4D8D-A29C-7A9EEB7CBDEB}">
+  <sheetPr codeName="Sheet4"/>
   <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6905,23 +7159,23 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="28" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
         <v>101</v>
-      </c>
-      <c r="B3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="29" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B4">
         <v>3525.6899999999996</v>
@@ -6929,7 +7183,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="29" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B5">
         <v>389.88</v>
@@ -6937,7 +7191,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="29" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B6">
         <v>1444.71</v>
@@ -6945,7 +7199,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B7">
         <v>544.01</v>
@@ -6953,7 +7207,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="29" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B8">
         <v>2351.6</v>
@@ -6961,7 +7215,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B9">
         <v>4841.28</v>
@@ -6969,7 +7223,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="29" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B10">
         <v>13097.169999999998</v>
@@ -6983,6 +7237,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48BD969E-335E-4BAE-AA07-B8473F045CD1}">
+  <sheetPr codeName="Sheet5"/>
   <dimension ref="A1:N109"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -6998,46 +7253,46 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="J1" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="K1" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="J1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="K1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="8" t="s">
-        <v>56</v>
-      </c>
       <c r="N1" s="10" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -7045,10 +7300,10 @@
         <v>2024</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D2" s="7">
         <v>14</v>
@@ -7057,19 +7312,19 @@
         <v>2000</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H2" s="7">
         <v>0</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J2" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K2" s="9">
         <v>44980</v>
@@ -7078,7 +7333,7 @@
         <v>44984</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N2">
         <f>PRODUCT(D2,E2)</f>
@@ -7090,10 +7345,10 @@
         <v>2024</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D3" s="7">
         <v>1</v>
@@ -7102,19 +7357,19 @@
         <v>544.01</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H3" s="7">
         <v>0</v>
       </c>
       <c r="I3" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J3" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K3" s="9">
         <v>45645</v>
@@ -7123,7 +7378,7 @@
         <v>45654</v>
       </c>
       <c r="M3" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N3">
         <f t="shared" ref="N3:N50" si="0">PRODUCT(D3,E3)</f>
@@ -7135,10 +7390,10 @@
         <v>2023</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D4" s="7">
         <v>14</v>
@@ -7147,19 +7402,19 @@
         <v>346.18</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H4" s="7">
         <v>0.1</v>
       </c>
       <c r="I4" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J4" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K4" s="9">
         <v>45056</v>
@@ -7168,7 +7423,7 @@
         <v>45065</v>
       </c>
       <c r="M4" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N4">
         <f t="shared" si="0"/>
@@ -7180,10 +7435,10 @@
         <v>2025</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7">
         <v>18</v>
@@ -7192,19 +7447,19 @@
         <v>384.82</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H5" s="7">
         <v>0.15</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K5" s="9">
         <v>45714</v>
@@ -7213,7 +7468,7 @@
         <v>45718</v>
       </c>
       <c r="M5" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N5">
         <f t="shared" si="0"/>
@@ -7225,10 +7480,10 @@
         <v>2025</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D6" s="7">
         <v>18</v>
@@ -7237,19 +7492,19 @@
         <v>237.76</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H6" s="7">
         <v>0</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J6" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K6" s="9">
         <v>45101</v>
@@ -7258,7 +7513,7 @@
         <v>45104</v>
       </c>
       <c r="M6" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N6">
         <f t="shared" si="0"/>
@@ -7270,10 +7525,10 @@
         <v>2025</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D7" s="7">
         <v>2</v>
@@ -7282,19 +7537,19 @@
         <v>385.09</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H7" s="7">
         <v>0.15</v>
       </c>
       <c r="I7" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J7" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K7" s="9">
         <v>45342</v>
@@ -7303,7 +7558,7 @@
         <v>45352</v>
       </c>
       <c r="M7" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N7">
         <f t="shared" si="0"/>
@@ -7315,10 +7570,10 @@
         <v>2025</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D8" s="7">
         <v>7</v>
@@ -7327,19 +7582,19 @@
         <v>17.5</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H8" s="7">
         <v>0.1</v>
       </c>
       <c r="I8" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J8" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K8" s="9">
         <v>44937</v>
@@ -7348,7 +7603,7 @@
         <v>44940</v>
       </c>
       <c r="M8" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N8">
         <f t="shared" si="0"/>
@@ -7360,10 +7615,10 @@
         <v>2025</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D9" s="7">
         <v>3</v>
@@ -7372,19 +7627,19 @@
         <v>330.22</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H9" s="7">
         <v>0.15</v>
       </c>
       <c r="I9" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J9" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K9" s="9">
         <v>44935</v>
@@ -7393,7 +7648,7 @@
         <v>44937</v>
       </c>
       <c r="M9" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N9">
         <f t="shared" si="0"/>
@@ -7405,10 +7660,10 @@
         <v>2025</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D10" s="7">
         <v>3</v>
@@ -7417,19 +7672,19 @@
         <v>432.04</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H10" s="7">
         <v>0.05</v>
       </c>
       <c r="I10" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J10" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K10" s="9">
         <v>45581</v>
@@ -7438,7 +7693,7 @@
         <v>45583</v>
       </c>
       <c r="M10" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N10">
         <f t="shared" si="0"/>
@@ -7450,10 +7705,10 @@
         <v>2025</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D11" s="7">
         <v>5</v>
@@ -7462,19 +7717,19 @@
         <v>323.27999999999997</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H11" s="7">
         <v>0.1</v>
       </c>
       <c r="I11" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J11" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K11" s="9">
         <v>45721</v>
@@ -7483,7 +7738,7 @@
         <v>45729</v>
       </c>
       <c r="M11" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N11">
         <f t="shared" si="0"/>
@@ -7495,10 +7750,10 @@
         <v>2024</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D12" s="7">
         <v>15</v>
@@ -7507,19 +7762,19 @@
         <v>523.29</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H12" s="7">
         <v>0.15</v>
       </c>
       <c r="I12" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J12" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K12" s="9">
         <v>45392</v>
@@ -7528,7 +7783,7 @@
         <v>45399</v>
       </c>
       <c r="M12" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N12">
         <f t="shared" si="0"/>
@@ -7540,10 +7795,10 @@
         <v>2023</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D13" s="7">
         <v>19</v>
@@ -7552,19 +7807,19 @@
         <v>207.35</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H13" s="7">
         <v>0.1</v>
       </c>
       <c r="I13" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J13" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K13" s="9">
         <v>45485</v>
@@ -7573,7 +7828,7 @@
         <v>45491</v>
       </c>
       <c r="M13" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N13">
         <f t="shared" si="0"/>
@@ -7585,10 +7840,10 @@
         <v>2024</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D14" s="7">
         <v>1</v>
@@ -7597,19 +7852,19 @@
         <v>120.53</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H14" s="7">
         <v>0.05</v>
       </c>
       <c r="I14" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J14" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="J14" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="K14" s="9">
         <v>45128</v>
@@ -7618,7 +7873,7 @@
         <v>45138</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N14">
         <f t="shared" si="0"/>
@@ -7630,10 +7885,10 @@
         <v>2025</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D15" s="7">
         <v>1</v>
@@ -7642,19 +7897,19 @@
         <v>157.83000000000001</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H15" s="7">
         <v>0.15</v>
       </c>
       <c r="I15" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K15" s="9">
         <v>45675</v>
@@ -7663,7 +7918,7 @@
         <v>45679</v>
       </c>
       <c r="M15" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N15">
         <f t="shared" si="0"/>
@@ -7675,10 +7930,10 @@
         <v>2024</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D16" s="7">
         <v>15</v>
@@ -7687,19 +7942,19 @@
         <v>220.3</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G16" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H16" s="7">
         <v>0.15</v>
       </c>
       <c r="I16" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J16" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K16" s="9">
         <v>45634</v>
@@ -7708,7 +7963,7 @@
         <v>45641</v>
       </c>
       <c r="M16" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N16">
         <f t="shared" si="0"/>
@@ -7720,10 +7975,10 @@
         <v>2024</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D17" s="7">
         <v>17</v>
@@ -7732,19 +7987,19 @@
         <v>162.96</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G17" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H17" s="7">
         <v>0.05</v>
       </c>
       <c r="I17" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J17" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K17" s="9">
         <v>45788</v>
@@ -7753,7 +8008,7 @@
         <v>45794</v>
       </c>
       <c r="M17" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N17">
         <f t="shared" si="0"/>
@@ -7765,10 +8020,10 @@
         <v>2025</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D18" s="7">
         <v>19</v>
@@ -7777,19 +8032,19 @@
         <v>236.11</v>
       </c>
       <c r="F18" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G18" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H18" s="7">
         <v>0</v>
       </c>
       <c r="I18" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J18" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K18" s="9">
         <v>44983</v>
@@ -7798,7 +8053,7 @@
         <v>44989</v>
       </c>
       <c r="M18" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N18">
         <f t="shared" si="0"/>
@@ -7810,10 +8065,10 @@
         <v>2023</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D19" s="7">
         <v>11</v>
@@ -7822,19 +8077,19 @@
         <v>573.14</v>
       </c>
       <c r="F19" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G19" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H19" s="7">
         <v>0.05</v>
       </c>
       <c r="I19" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J19" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="J19" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="K19" s="9">
         <v>45440</v>
@@ -7843,7 +8098,7 @@
         <v>45444</v>
       </c>
       <c r="M19" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N19">
         <f t="shared" si="0"/>
@@ -7855,10 +8110,10 @@
         <v>2023</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D20" s="7">
         <v>20</v>
@@ -7867,19 +8122,19 @@
         <v>519.04</v>
       </c>
       <c r="F20" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G20" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H20" s="7">
         <v>0.15</v>
       </c>
       <c r="I20" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J20" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K20" s="9">
         <v>45260</v>
@@ -7888,7 +8143,7 @@
         <v>45268</v>
       </c>
       <c r="M20" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N20">
         <f t="shared" si="0"/>
@@ -7900,10 +8155,10 @@
         <v>2024</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D21" s="7">
         <v>14</v>
@@ -7912,19 +8167,19 @@
         <v>30.83</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G21" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H21" s="7">
         <v>0</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J21" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K21" s="9">
         <v>45099</v>
@@ -7933,7 +8188,7 @@
         <v>45109</v>
       </c>
       <c r="M21" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N21">
         <f t="shared" si="0"/>
@@ -7945,10 +8200,10 @@
         <v>2025</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D22" s="7">
         <v>10</v>
@@ -7957,19 +8212,19 @@
         <v>319.05</v>
       </c>
       <c r="F22" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G22" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H22" s="7">
         <v>0</v>
       </c>
       <c r="I22" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J22" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K22" s="9">
         <v>45813</v>
@@ -7978,7 +8233,7 @@
         <v>45816</v>
       </c>
       <c r="M22" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N22">
         <f t="shared" si="0"/>
@@ -7990,10 +8245,10 @@
         <v>2024</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D23" s="7">
         <v>14</v>
@@ -8002,19 +8257,19 @@
         <v>312.79000000000002</v>
       </c>
       <c r="F23" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G23" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H23" s="7">
         <v>0.05</v>
       </c>
       <c r="I23" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J23" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K23" s="9">
         <v>44988</v>
@@ -8023,7 +8278,7 @@
         <v>44993</v>
       </c>
       <c r="M23" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N23">
         <f t="shared" si="0"/>
@@ -8035,10 +8290,10 @@
         <v>2024</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D24" s="7">
         <v>14</v>
@@ -8047,19 +8302,19 @@
         <v>395.45</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G24" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H24" s="7">
         <v>0</v>
       </c>
       <c r="I24" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J24" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K24" s="9">
         <v>45340</v>
@@ -8068,7 +8323,7 @@
         <v>45344</v>
       </c>
       <c r="M24" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N24">
         <f t="shared" si="0"/>
@@ -8080,10 +8335,10 @@
         <v>2025</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D25" s="7">
         <v>12</v>
@@ -8092,19 +8347,19 @@
         <v>472.72</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H25" s="7">
         <v>0.15</v>
       </c>
       <c r="I25" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J25" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K25" s="9">
         <v>45144</v>
@@ -8113,7 +8368,7 @@
         <v>45152</v>
       </c>
       <c r="M25" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N25">
         <f t="shared" si="0"/>
@@ -8125,10 +8380,10 @@
         <v>2023</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D26" s="7">
         <v>5</v>
@@ -8137,19 +8392,19 @@
         <v>288.01</v>
       </c>
       <c r="F26" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G26" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H26" s="7">
         <v>0</v>
       </c>
       <c r="I26" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J26" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K26" s="9">
         <v>45435</v>
@@ -8158,7 +8413,7 @@
         <v>45442</v>
       </c>
       <c r="M26" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N26">
         <f t="shared" si="0"/>
@@ -8170,10 +8425,10 @@
         <v>2023</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D27" s="7">
         <v>13</v>
@@ -8182,19 +8437,19 @@
         <v>562.29</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H27" s="7">
         <v>0</v>
       </c>
       <c r="I27" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J27" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K27" s="9">
         <v>45222</v>
@@ -8203,7 +8458,7 @@
         <v>45227</v>
       </c>
       <c r="M27" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N27">
         <f t="shared" si="0"/>
@@ -8215,10 +8470,10 @@
         <v>2024</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D28" s="7">
         <v>1</v>
@@ -8227,19 +8482,19 @@
         <v>101.73</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G28" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H28" s="7">
         <v>0</v>
       </c>
       <c r="I28" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J28" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K28" s="9">
         <v>45824</v>
@@ -8248,7 +8503,7 @@
         <v>45833</v>
       </c>
       <c r="M28" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N28">
         <f t="shared" si="0"/>
@@ -8260,10 +8515,10 @@
         <v>2025</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D29" s="7">
         <v>4</v>
@@ -8272,19 +8527,19 @@
         <v>279.49</v>
       </c>
       <c r="F29" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G29" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H29" s="7">
         <v>0</v>
       </c>
       <c r="I29" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J29" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K29" s="9">
         <v>44988</v>
@@ -8293,7 +8548,7 @@
         <v>44993</v>
       </c>
       <c r="M29" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N29">
         <f t="shared" si="0"/>
@@ -8305,10 +8560,10 @@
         <v>2025</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D30" s="7">
         <v>1</v>
@@ -8317,19 +8572,19 @@
         <v>178.55</v>
       </c>
       <c r="F30" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G30" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H30" s="7">
         <v>0.15</v>
       </c>
       <c r="I30" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J30" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K30" s="9">
         <v>45614</v>
@@ -8338,7 +8593,7 @@
         <v>45617</v>
       </c>
       <c r="M30" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N30">
         <f t="shared" si="0"/>
@@ -8350,10 +8605,10 @@
         <v>2024</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D31" s="7">
         <v>1</v>
@@ -8362,19 +8617,19 @@
         <v>472.07</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H31" s="7">
         <v>0.1</v>
       </c>
       <c r="I31" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J31" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K31" s="9">
         <v>45055</v>
@@ -8383,7 +8638,7 @@
         <v>45063</v>
       </c>
       <c r="M31" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N31">
         <f t="shared" si="0"/>
@@ -8395,10 +8650,10 @@
         <v>2025</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D32" s="7">
         <v>12</v>
@@ -8407,19 +8662,19 @@
         <v>306.29000000000002</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G32" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H32" s="7">
         <v>0</v>
       </c>
       <c r="I32" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J32" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K32" s="9">
         <v>45633</v>
@@ -8428,7 +8683,7 @@
         <v>45640</v>
       </c>
       <c r="M32" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N32">
         <f t="shared" si="0"/>
@@ -8440,10 +8695,10 @@
         <v>2023</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D33" s="7">
         <v>7</v>
@@ -8452,19 +8707,19 @@
         <v>434.77</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G33" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H33" s="7">
         <v>0.15</v>
       </c>
       <c r="I33" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J33" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K33" s="9">
         <v>45335</v>
@@ -8473,7 +8728,7 @@
         <v>45337</v>
       </c>
       <c r="M33" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N33">
         <f t="shared" si="0"/>
@@ -8485,10 +8740,10 @@
         <v>2025</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D34" s="7">
         <v>6</v>
@@ -8497,19 +8752,19 @@
         <v>64.98</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G34" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H34" s="7">
         <v>0</v>
       </c>
       <c r="I34" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J34" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K34" s="9">
         <v>45725</v>
@@ -8518,7 +8773,7 @@
         <v>45731</v>
       </c>
       <c r="M34" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N34">
         <f t="shared" si="0"/>
@@ -8530,10 +8785,10 @@
         <v>2025</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D35" s="7">
         <v>17</v>
@@ -8542,19 +8797,19 @@
         <v>476.49</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H35" s="7">
         <v>0</v>
       </c>
       <c r="I35" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J35" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K35" s="9">
         <v>45021</v>
@@ -8563,7 +8818,7 @@
         <v>45027</v>
       </c>
       <c r="M35" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N35">
         <f t="shared" si="0"/>
@@ -8575,10 +8830,10 @@
         <v>2023</v>
       </c>
       <c r="B36" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="D36" s="7">
         <v>4</v>
@@ -8587,19 +8842,19 @@
         <v>559.72</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G36" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H36" s="7">
         <v>0.15</v>
       </c>
       <c r="I36" s="7" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="J36" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K36" s="9">
         <v>45785</v>
@@ -8608,7 +8863,7 @@
         <v>45789</v>
       </c>
       <c r="M36" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N36">
         <f t="shared" si="0"/>
@@ -8620,10 +8875,10 @@
         <v>2024</v>
       </c>
       <c r="B37" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D37" s="7">
         <v>14</v>
@@ -8632,19 +8887,19 @@
         <v>82.14</v>
       </c>
       <c r="F37" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G37" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H37" s="7">
         <v>0</v>
       </c>
       <c r="I37" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J37" s="7" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K37" s="9">
         <v>45172</v>
@@ -8653,7 +8908,7 @@
         <v>45180</v>
       </c>
       <c r="M37" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N37">
         <f t="shared" si="0"/>
@@ -8665,10 +8920,10 @@
         <v>2025</v>
       </c>
       <c r="B38" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D38" s="7">
         <v>9</v>
@@ -8677,19 +8932,19 @@
         <v>343.21</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G38" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H38" s="7">
         <v>0.05</v>
       </c>
       <c r="I38" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J38" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K38" s="9">
         <v>45737</v>
@@ -8698,7 +8953,7 @@
         <v>45744</v>
       </c>
       <c r="M38" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N38">
         <f t="shared" si="0"/>
@@ -8710,10 +8965,10 @@
         <v>2025</v>
       </c>
       <c r="B39" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D39" s="7">
         <v>7</v>
@@ -8722,19 +8977,19 @@
         <v>301.01</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G39" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H39" s="7">
         <v>0.15</v>
       </c>
       <c r="I39" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="J39" s="7" t="s">
         <v>82</v>
-      </c>
-      <c r="J39" s="7" t="s">
-        <v>85</v>
       </c>
       <c r="K39" s="9">
         <v>45828</v>
@@ -8743,7 +8998,7 @@
         <v>45838</v>
       </c>
       <c r="M39" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N39">
         <f t="shared" si="0"/>
@@ -8755,10 +9010,10 @@
         <v>2025</v>
       </c>
       <c r="B40" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D40" s="7">
         <v>14</v>
@@ -8767,19 +9022,19 @@
         <v>428.13</v>
       </c>
       <c r="F40" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G40" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H40" s="7">
         <v>0.1</v>
       </c>
       <c r="I40" s="7" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="J40" s="7" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K40" s="9">
         <v>45337</v>
@@ -8788,7 +9043,7 @@
         <v>45347</v>
       </c>
       <c r="M40" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N40">
         <f t="shared" si="0"/>
@@ -8800,10 +9055,10 @@
         <v>2023</v>
       </c>
       <c r="B41" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D41" s="7">
         <v>2</v>
@@ -8812,19 +9067,19 @@
         <v>503.28</v>
       </c>
       <c r="F41" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G41" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H41" s="7">
         <v>0.15</v>
       </c>
       <c r="I41" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J41" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K41" s="9">
         <v>45086</v>
@@ -8833,7 +9088,7 @@
         <v>45094</v>
       </c>
       <c r="M41" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N41">
         <f t="shared" si="0"/>
@@ -8845,10 +9100,10 @@
         <v>2023</v>
       </c>
       <c r="B42" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D42" s="7">
         <v>5</v>
@@ -8857,19 +9112,19 @@
         <v>470.32</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G42" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H42" s="7">
         <v>0.1</v>
       </c>
       <c r="I42" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J42" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K42" s="9">
         <v>45148</v>
@@ -8878,7 +9133,7 @@
         <v>45152</v>
       </c>
       <c r="M42" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N42">
         <f t="shared" si="0"/>
@@ -8890,10 +9145,10 @@
         <v>2024</v>
       </c>
       <c r="B43" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D43" s="7">
         <v>20</v>
@@ -8902,19 +9157,19 @@
         <v>65.17</v>
       </c>
       <c r="F43" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="G43" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H43" s="7">
         <v>0.05</v>
       </c>
       <c r="I43" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J43" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K43" s="9">
         <v>45459</v>
@@ -8923,7 +9178,7 @@
         <v>45468</v>
       </c>
       <c r="M43" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N43">
         <f t="shared" si="0"/>
@@ -8935,10 +9190,10 @@
         <v>2025</v>
       </c>
       <c r="B44" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D44" s="7">
         <v>12</v>
@@ -8947,19 +9202,19 @@
         <v>36.17</v>
       </c>
       <c r="F44" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G44" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H44" s="7">
         <v>0</v>
       </c>
       <c r="I44" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J44" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K44" s="9">
         <v>45130</v>
@@ -8968,7 +9223,7 @@
         <v>45133</v>
       </c>
       <c r="M44" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N44">
         <f t="shared" si="0"/>
@@ -8980,10 +9235,10 @@
         <v>2025</v>
       </c>
       <c r="B45" s="7" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D45" s="7">
         <v>4</v>
@@ -8992,19 +9247,19 @@
         <v>459.31</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G45" s="7" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="H45" s="7">
         <v>0.15</v>
       </c>
       <c r="I45" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="J45" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K45" s="9">
         <v>45066</v>
@@ -9013,7 +9268,7 @@
         <v>45073</v>
       </c>
       <c r="M45" s="7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="N45">
         <f t="shared" si="0"/>
@@ -9025,10 +9280,10 @@
         <v>2023</v>
       </c>
       <c r="B46" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="D46" s="7">
         <v>2</v>
@@ -9037,19 +9292,19 @@
         <v>416.06</v>
       </c>
       <c r="F46" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G46" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H46" s="7">
         <v>0.05</v>
       </c>
       <c r="I46" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J46" s="7" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K46" s="9">
         <v>45107</v>
@@ -9058,7 +9313,7 @@
         <v>45111</v>
       </c>
       <c r="M46" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N46">
         <f t="shared" si="0"/>
@@ -9070,10 +9325,10 @@
         <v>2023</v>
       </c>
       <c r="B47" s="7" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D47" s="7">
         <v>16</v>
@@ -9082,19 +9337,19 @@
         <v>302.58</v>
       </c>
       <c r="F47" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G47" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H47" s="7">
         <v>0</v>
       </c>
       <c r="I47" s="7" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="J47" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K47" s="9">
         <v>45447</v>
@@ -9103,7 +9358,7 @@
         <v>45457</v>
       </c>
       <c r="M47" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="N47">
         <f t="shared" si="0"/>
@@ -9115,10 +9370,10 @@
         <v>2025</v>
       </c>
       <c r="B48" s="7" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="D48" s="7">
         <v>11</v>
@@ -9127,19 +9382,19 @@
         <v>33.130000000000003</v>
       </c>
       <c r="F48" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G48" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H48" s="7">
         <v>0.15</v>
       </c>
       <c r="I48" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J48" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="K48" s="9">
         <v>45691</v>
@@ -9148,7 +9403,7 @@
         <v>45693</v>
       </c>
       <c r="M48" s="7" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="N48">
         <f t="shared" si="0"/>
@@ -9160,10 +9415,10 @@
         <v>2025</v>
       </c>
       <c r="B49" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="D49" s="7">
         <v>8</v>
@@ -9172,19 +9427,19 @@
         <v>582.52</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="G49" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H49" s="7">
         <v>0.15</v>
       </c>
       <c r="I49" s="7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J49" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K49" s="9">
         <v>45300</v>
@@ -9193,7 +9448,7 @@
         <v>45304</v>
       </c>
       <c r="M49" s="7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="N49">
         <f t="shared" si="0"/>
@@ -9205,10 +9460,10 @@
         <v>2024</v>
       </c>
       <c r="B50" s="7" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D50" s="7">
         <v>5</v>
@@ -9217,19 +9472,19 @@
         <v>165.15</v>
       </c>
       <c r="F50" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="G50" s="7" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="H50" s="7">
         <v>0.1</v>
       </c>
       <c r="I50" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="J50" s="7" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="K50" s="9">
         <v>45365</v>
@@ -9238,7 +9493,7 @@
         <v>45367</v>
       </c>
       <c r="M50" s="7" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="N50">
         <f t="shared" si="0"/>
@@ -9247,18 +9502,18 @@
     </row>
     <row r="69" spans="1:10" ht="31.2" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="31" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B69" s="31"/>
       <c r="C69" s="31"/>
       <c r="D69" s="31"/>
       <c r="E69" s="32" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F69" s="32"/>
       <c r="G69" s="32"/>
       <c r="H69" s="33" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="I69" s="33"/>
       <c r="J69" s="33"/>
@@ -9294,7 +9549,7 @@
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="16" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="B71" s="22">
         <f t="shared" ref="B71:D75" si="1">SUMIFS($N$2:$N$50,$C$2:$C$50,TRIM($A71),$A$2:$A$50,B$70)</f>
@@ -9335,7 +9590,7 @@
     </row>
     <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="16" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B72" s="22">
         <f t="shared" si="1"/>
@@ -9376,7 +9631,7 @@
     </row>
     <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="16" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="B73" s="22">
         <f t="shared" si="1"/>
@@ -9417,7 +9672,7 @@
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="16" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="B74" s="22">
         <f t="shared" si="1"/>
@@ -9458,7 +9713,7 @@
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="16" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B75" s="22">
         <f t="shared" si="1"/>
@@ -9536,16 +9791,16 @@
     </row>
     <row r="80" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A80" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="B80" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C80" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="E80" s="15" t="s">
         <v>93</v>
-      </c>
-      <c r="B80" s="12" t="s">
-        <v>94</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E80" s="15" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.35">
@@ -9653,17 +9908,17 @@
     <row r="88" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A88" s="1"/>
       <c r="B88" s="34" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="C88" s="34"/>
       <c r="D88" s="34"/>
       <c r="E88" s="35" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F88" s="35"/>
       <c r="G88" s="35"/>
       <c r="H88" s="36" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="I88" s="36"/>
       <c r="J88" s="36"/>
@@ -9671,31 +9926,31 @@
     <row r="89" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A89" s="1"/>
       <c r="B89" s="26" t="s">
+        <v>94</v>
+      </c>
+      <c r="C89" s="26" t="s">
+        <v>96</v>
+      </c>
+      <c r="D89" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="C89" s="26" t="s">
-        <v>99</v>
-      </c>
-      <c r="D89" s="26" t="s">
-        <v>100</v>
-      </c>
       <c r="E89" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="G89" s="24" t="s">
         <v>97</v>
       </c>
-      <c r="F89" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="G89" s="24" t="s">
-        <v>100</v>
-      </c>
       <c r="H89" s="27" t="s">
+        <v>94</v>
+      </c>
+      <c r="I89" s="27" t="s">
+        <v>96</v>
+      </c>
+      <c r="J89" s="27" t="s">
         <v>97</v>
-      </c>
-      <c r="I89" s="27" t="s">
-        <v>99</v>
-      </c>
-      <c r="J89" s="27" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="90" spans="1:10" x14ac:dyDescent="0.35">
@@ -9859,32 +10114,32 @@
     <mergeCell ref="H88:J88"/>
   </mergeCells>
   <conditionalFormatting sqref="A81:A85">
-    <cfRule type="expression" dxfId="5" priority="2">
+    <cfRule type="expression" dxfId="13" priority="2">
       <formula>A81=MAX(A$81:A$85)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B81:C85">
-    <cfRule type="expression" dxfId="4" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>B81=MAX(B$81:B$85)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B71:D75">
-    <cfRule type="expression" dxfId="3" priority="3">
+    <cfRule type="expression" dxfId="11" priority="3">
       <formula>B71=MAX(B$71:B$75)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E81:E85">
-    <cfRule type="expression" dxfId="2" priority="11">
+    <cfRule type="expression" dxfId="10" priority="11">
       <formula>ISERROR(A81)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E71:G75">
-    <cfRule type="expression" dxfId="1" priority="4">
+    <cfRule type="expression" dxfId="9" priority="4">
       <formula>E71=MAX(E$71:E$75)</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H71:J75">
-    <cfRule type="expression" dxfId="0" priority="5">
+    <cfRule type="expression" dxfId="8" priority="5">
       <formula>H71=MAX(H$71:H$75)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -9900,6 +10155,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6AC1EC01-3558-4CAF-8FA5-3C02BC76403B}">
+  <sheetPr codeName="Sheet6"/>
   <dimension ref="C1:L72"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
@@ -10207,25 +10463,25 @@
     </row>
     <row r="37" spans="4:7" x14ac:dyDescent="0.35">
       <c r="E37" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="38" spans="4:7" x14ac:dyDescent="0.35">
       <c r="F38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
     </row>
     <row r="39" spans="4:7" x14ac:dyDescent="0.35">
       <c r="F39" t="s">
+        <v>34</v>
+      </c>
+      <c r="G39" t="s">
         <v>37</v>
-      </c>
-      <c r="G39" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="40" spans="4:7" x14ac:dyDescent="0.35">
       <c r="F40" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="43" spans="4:7" x14ac:dyDescent="0.35">
@@ -10236,7 +10492,7 @@
         <v>21</v>
       </c>
       <c r="G43" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="44" spans="4:7" x14ac:dyDescent="0.35">
@@ -10361,10 +10617,10 @@
     </row>
     <row r="58" spans="4:11" x14ac:dyDescent="0.35">
       <c r="E58" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="F58" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="J58" t="s">
         <v>25</v>
@@ -10402,7 +10658,7 @@
     </row>
     <row r="66" spans="4:8" x14ac:dyDescent="0.35">
       <c r="E66" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="68" spans="4:8" x14ac:dyDescent="0.35">
@@ -10512,44 +10768,1774 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A08F756C-290F-404E-81ED-2B88E96B5E6A}">
-  <dimension ref="B2:F7"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04930B2B-A5A9-4CE8-B122-3EDC90EC5A42}">
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:AJ29"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.1640625" customWidth="1"/>
-    <col min="6" max="6" width="16.1640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.5" style="1" customWidth="1"/>
+    <col min="3" max="32" width="9.9140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="8.6640625" style="1"/>
+    <col min="36" max="36" width="9.9140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="2:6" ht="23.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="F4" s="6">
-        <v>46288.717997337961</v>
-      </c>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F5" s="6">
+    <row r="1" spans="1:36" ht="40.200000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
+      <c r="K1" s="40"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="B3" s="1">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A5" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>26</v>
+      </c>
+      <c r="C5" s="43">
+        <f>DATE(B3,MONTH(B2&amp;0),1)</f>
+        <v>46266</v>
+      </c>
+      <c r="D5" s="43">
+        <f>IF(C5&gt;= EOMONTH(DATE($B$3,MONTH($B$2&amp;0),1),0), "", C5+1)</f>
+        <v>46267</v>
+      </c>
+      <c r="E5" s="43">
+        <f>IF(D5&gt;= EOMONTH(DATE($B$3,MONTH($B$2&amp;0),1),0), "", D5+1)</f>
+        <v>46268</v>
+      </c>
+      <c r="F5" s="43">
+        <f t="shared" ref="F5:AG5" si="0">IF(E5&gt;= EOMONTH(DATE($B$3,MONTH($B$2&amp;0),1),0), "", E5+1)</f>
+        <v>46269</v>
+      </c>
+      <c r="G5" s="43">
+        <f t="shared" si="0"/>
+        <v>46270</v>
+      </c>
+      <c r="H5" s="43">
+        <f t="shared" si="0"/>
+        <v>46271</v>
+      </c>
+      <c r="I5" s="43">
+        <f t="shared" si="0"/>
+        <v>46272</v>
+      </c>
+      <c r="J5" s="43">
+        <f t="shared" si="0"/>
+        <v>46273</v>
+      </c>
+      <c r="K5" s="43">
+        <f t="shared" si="0"/>
+        <v>46274</v>
+      </c>
+      <c r="L5" s="43">
+        <f t="shared" si="0"/>
+        <v>46275</v>
+      </c>
+      <c r="M5" s="43">
+        <f t="shared" si="0"/>
+        <v>46276</v>
+      </c>
+      <c r="N5" s="43">
+        <f t="shared" si="0"/>
+        <v>46277</v>
+      </c>
+      <c r="O5" s="43">
+        <f t="shared" si="0"/>
+        <v>46278</v>
+      </c>
+      <c r="P5" s="43">
+        <f t="shared" si="0"/>
+        <v>46279</v>
+      </c>
+      <c r="Q5" s="43">
+        <f t="shared" si="0"/>
+        <v>46280</v>
+      </c>
+      <c r="R5" s="43">
+        <f t="shared" si="0"/>
+        <v>46281</v>
+      </c>
+      <c r="S5" s="43">
+        <f t="shared" si="0"/>
+        <v>46282</v>
+      </c>
+      <c r="T5" s="43">
+        <f t="shared" si="0"/>
+        <v>46283</v>
+      </c>
+      <c r="U5" s="43">
+        <f t="shared" si="0"/>
+        <v>46284</v>
+      </c>
+      <c r="V5" s="43">
+        <f t="shared" si="0"/>
+        <v>46285</v>
+      </c>
+      <c r="W5" s="43">
+        <f t="shared" si="0"/>
+        <v>46286</v>
+      </c>
+      <c r="X5" s="43">
+        <f t="shared" si="0"/>
+        <v>46287</v>
+      </c>
+      <c r="Y5" s="43">
+        <f t="shared" si="0"/>
+        <v>46288</v>
+      </c>
+      <c r="Z5" s="43">
+        <f t="shared" si="0"/>
         <v>46289</v>
       </c>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B7" t="s">
-        <v>33</v>
+      <c r="AA5" s="43">
+        <f t="shared" si="0"/>
+        <v>46290</v>
+      </c>
+      <c r="AB5" s="43">
+        <f t="shared" si="0"/>
+        <v>46291</v>
+      </c>
+      <c r="AC5" s="43">
+        <f t="shared" si="0"/>
+        <v>46292</v>
+      </c>
+      <c r="AD5" s="43">
+        <f t="shared" si="0"/>
+        <v>46293</v>
+      </c>
+      <c r="AE5" s="43">
+        <f t="shared" si="0"/>
+        <v>46294</v>
+      </c>
+      <c r="AF5" s="43">
+        <f t="shared" si="0"/>
+        <v>46295</v>
+      </c>
+      <c r="AG5" s="43" t="str">
+        <f t="shared" si="0"/>
+        <v/>
+      </c>
+      <c r="AH5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A6" s="42"/>
+      <c r="B6" s="42"/>
+      <c r="C6" s="44">
+        <f>C5</f>
+        <v>46266</v>
+      </c>
+      <c r="D6" s="44">
+        <f t="shared" ref="D6:AH6" si="1">D5</f>
+        <v>46267</v>
+      </c>
+      <c r="E6" s="44">
+        <f t="shared" si="1"/>
+        <v>46268</v>
+      </c>
+      <c r="F6" s="44">
+        <f t="shared" si="1"/>
+        <v>46269</v>
+      </c>
+      <c r="G6" s="44">
+        <f t="shared" si="1"/>
+        <v>46270</v>
+      </c>
+      <c r="H6" s="44">
+        <f t="shared" si="1"/>
+        <v>46271</v>
+      </c>
+      <c r="I6" s="44">
+        <f t="shared" si="1"/>
+        <v>46272</v>
+      </c>
+      <c r="J6" s="44">
+        <f t="shared" si="1"/>
+        <v>46273</v>
+      </c>
+      <c r="K6" s="44">
+        <f t="shared" si="1"/>
+        <v>46274</v>
+      </c>
+      <c r="L6" s="44">
+        <f t="shared" si="1"/>
+        <v>46275</v>
+      </c>
+      <c r="M6" s="44">
+        <f t="shared" si="1"/>
+        <v>46276</v>
+      </c>
+      <c r="N6" s="44">
+        <f t="shared" si="1"/>
+        <v>46277</v>
+      </c>
+      <c r="O6" s="44">
+        <f t="shared" si="1"/>
+        <v>46278</v>
+      </c>
+      <c r="P6" s="44">
+        <f t="shared" si="1"/>
+        <v>46279</v>
+      </c>
+      <c r="Q6" s="44">
+        <f t="shared" si="1"/>
+        <v>46280</v>
+      </c>
+      <c r="R6" s="44">
+        <f t="shared" si="1"/>
+        <v>46281</v>
+      </c>
+      <c r="S6" s="44">
+        <f t="shared" si="1"/>
+        <v>46282</v>
+      </c>
+      <c r="T6" s="44">
+        <f t="shared" si="1"/>
+        <v>46283</v>
+      </c>
+      <c r="U6" s="44">
+        <f t="shared" si="1"/>
+        <v>46284</v>
+      </c>
+      <c r="V6" s="44">
+        <f t="shared" si="1"/>
+        <v>46285</v>
+      </c>
+      <c r="W6" s="44">
+        <f t="shared" si="1"/>
+        <v>46286</v>
+      </c>
+      <c r="X6" s="44">
+        <f t="shared" si="1"/>
+        <v>46287</v>
+      </c>
+      <c r="Y6" s="44">
+        <f t="shared" si="1"/>
+        <v>46288</v>
+      </c>
+      <c r="Z6" s="44">
+        <f t="shared" si="1"/>
+        <v>46289</v>
+      </c>
+      <c r="AA6" s="44">
+        <f t="shared" si="1"/>
+        <v>46290</v>
+      </c>
+      <c r="AB6" s="44">
+        <f t="shared" si="1"/>
+        <v>46291</v>
+      </c>
+      <c r="AC6" s="44">
+        <f t="shared" si="1"/>
+        <v>46292</v>
+      </c>
+      <c r="AD6" s="44">
+        <f t="shared" si="1"/>
+        <v>46293</v>
+      </c>
+      <c r="AE6" s="44">
+        <f t="shared" si="1"/>
+        <v>46294</v>
+      </c>
+      <c r="AF6" s="44">
+        <f t="shared" si="1"/>
+        <v>46295</v>
+      </c>
+      <c r="AG6" s="44" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+      <c r="AH6" s="41"/>
+      <c r="AI6" s="45"/>
+      <c r="AJ6" s="46"/>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A7" s="25">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25" t="str">
+        <f>"Text_user_" &amp; TEXT(ROW(A1),"000")</f>
+        <v>Text_user_001</v>
+      </c>
+      <c r="C7" s="25"/>
+      <c r="D7" s="25"/>
+      <c r="E7" s="25"/>
+      <c r="F7" s="25"/>
+      <c r="G7" s="25"/>
+      <c r="H7" s="25"/>
+      <c r="I7" s="25"/>
+      <c r="J7" s="25"/>
+      <c r="K7" s="25"/>
+      <c r="L7" s="25"/>
+      <c r="M7" s="25"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="25"/>
+      <c r="Q7" s="25"/>
+      <c r="R7" s="25"/>
+      <c r="S7" s="25"/>
+      <c r="T7" s="25"/>
+      <c r="U7" s="25"/>
+      <c r="V7" s="25"/>
+      <c r="W7" s="25"/>
+      <c r="X7" s="25"/>
+      <c r="Y7" s="25"/>
+      <c r="Z7" s="25"/>
+      <c r="AA7" s="25"/>
+      <c r="AB7" s="25"/>
+      <c r="AC7" s="25"/>
+      <c r="AD7" s="25"/>
+      <c r="AE7" s="25"/>
+      <c r="AF7" s="25"/>
+      <c r="AG7" s="25"/>
+      <c r="AH7" s="41">
+        <f>COUNTIF(C7:AG7,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AI7" s="45">
+        <f>COUNTIF(C7:AG7,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="46" t="e">
+        <f>COUNTIF(C7:AG7,"P")/COUNTA(C7:AG7)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A8" s="25">
+        <v>2</v>
+      </c>
+      <c r="B8" s="25" t="str">
+        <f t="shared" ref="B8:B29" si="2">"Text_user_" &amp; TEXT(ROW(A2),"000")</f>
+        <v>Text_user_002</v>
+      </c>
+      <c r="C8" s="25"/>
+      <c r="D8" s="25"/>
+      <c r="E8" s="25"/>
+      <c r="F8" s="25"/>
+      <c r="G8" s="25"/>
+      <c r="H8" s="25"/>
+      <c r="I8" s="25"/>
+      <c r="J8" s="25"/>
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="25"/>
+      <c r="Q8" s="25"/>
+      <c r="R8" s="25"/>
+      <c r="S8" s="25"/>
+      <c r="T8" s="25"/>
+      <c r="U8" s="25"/>
+      <c r="V8" s="25"/>
+      <c r="W8" s="25"/>
+      <c r="X8" s="25"/>
+      <c r="Y8" s="25"/>
+      <c r="Z8" s="25"/>
+      <c r="AA8" s="25"/>
+      <c r="AB8" s="25"/>
+      <c r="AC8" s="25"/>
+      <c r="AD8" s="25"/>
+      <c r="AE8" s="25"/>
+      <c r="AF8" s="25"/>
+      <c r="AG8" s="25"/>
+      <c r="AH8" s="41">
+        <f t="shared" ref="AH8:AH29" si="3">COUNTIF(C8:AG8,"P")</f>
+        <v>0</v>
+      </c>
+      <c r="AI8" s="45">
+        <f t="shared" ref="AI8:AI29" si="4">COUNTIF(C8:AG8,"A")</f>
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="46" t="e">
+        <f t="shared" ref="AJ8:AJ29" si="5">COUNTIF(C8:AG8,"P")/COUNTA(C8:AG8)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A9" s="25">
+        <v>3</v>
+      </c>
+      <c r="B9" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_003</v>
+      </c>
+      <c r="C9" s="25"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="25"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+      <c r="M9" s="25"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="25"/>
+      <c r="Q9" s="25"/>
+      <c r="R9" s="25"/>
+      <c r="S9" s="25"/>
+      <c r="T9" s="25"/>
+      <c r="U9" s="25"/>
+      <c r="V9" s="25"/>
+      <c r="W9" s="25"/>
+      <c r="X9" s="25"/>
+      <c r="Y9" s="25"/>
+      <c r="Z9" s="25"/>
+      <c r="AA9" s="25"/>
+      <c r="AB9" s="25"/>
+      <c r="AC9" s="25"/>
+      <c r="AD9" s="25"/>
+      <c r="AE9" s="25"/>
+      <c r="AF9" s="25"/>
+      <c r="AG9" s="25"/>
+      <c r="AH9" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI9" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A10" s="25">
+        <v>4</v>
+      </c>
+      <c r="B10" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_004</v>
+      </c>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="25"/>
+      <c r="K10" s="25"/>
+      <c r="L10" s="25"/>
+      <c r="M10" s="25"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="25"/>
+      <c r="Q10" s="25"/>
+      <c r="R10" s="25"/>
+      <c r="S10" s="25"/>
+      <c r="T10" s="25"/>
+      <c r="U10" s="25"/>
+      <c r="V10" s="25"/>
+      <c r="W10" s="25"/>
+      <c r="X10" s="25"/>
+      <c r="Y10" s="25"/>
+      <c r="Z10" s="25"/>
+      <c r="AA10" s="25"/>
+      <c r="AB10" s="25"/>
+      <c r="AC10" s="25"/>
+      <c r="AD10" s="25"/>
+      <c r="AE10" s="25"/>
+      <c r="AF10" s="25"/>
+      <c r="AG10" s="25"/>
+      <c r="AH10" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI10" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A11" s="25">
+        <v>5</v>
+      </c>
+      <c r="B11" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_005</v>
+      </c>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="25"/>
+      <c r="L11" s="25"/>
+      <c r="M11" s="25"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="25"/>
+      <c r="P11" s="25"/>
+      <c r="Q11" s="25"/>
+      <c r="R11" s="25"/>
+      <c r="S11" s="25"/>
+      <c r="T11" s="25"/>
+      <c r="U11" s="25"/>
+      <c r="V11" s="25"/>
+      <c r="W11" s="25"/>
+      <c r="X11" s="25"/>
+      <c r="Y11" s="25"/>
+      <c r="Z11" s="25"/>
+      <c r="AA11" s="25"/>
+      <c r="AB11" s="25"/>
+      <c r="AC11" s="25"/>
+      <c r="AD11" s="25"/>
+      <c r="AE11" s="25"/>
+      <c r="AF11" s="25"/>
+      <c r="AG11" s="25"/>
+      <c r="AH11" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI11" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A12" s="25">
+        <v>6</v>
+      </c>
+      <c r="B12" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_006</v>
+      </c>
+      <c r="C12" s="25"/>
+      <c r="D12" s="25"/>
+      <c r="E12" s="25"/>
+      <c r="F12" s="25"/>
+      <c r="G12" s="25"/>
+      <c r="H12" s="25"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="25"/>
+      <c r="K12" s="25"/>
+      <c r="L12" s="25"/>
+      <c r="M12" s="25"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="25"/>
+      <c r="P12" s="25"/>
+      <c r="Q12" s="25"/>
+      <c r="R12" s="25"/>
+      <c r="S12" s="25"/>
+      <c r="T12" s="25"/>
+      <c r="U12" s="25"/>
+      <c r="V12" s="25"/>
+      <c r="W12" s="25"/>
+      <c r="X12" s="25"/>
+      <c r="Y12" s="25"/>
+      <c r="Z12" s="25"/>
+      <c r="AA12" s="25"/>
+      <c r="AB12" s="25"/>
+      <c r="AC12" s="25"/>
+      <c r="AD12" s="25"/>
+      <c r="AE12" s="25"/>
+      <c r="AF12" s="25"/>
+      <c r="AG12" s="25"/>
+      <c r="AH12" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI12" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A13" s="25">
+        <v>7</v>
+      </c>
+      <c r="B13" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_007</v>
+      </c>
+      <c r="C13" s="25"/>
+      <c r="D13" s="25"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="25"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="25"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="25"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="25"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="25"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="25"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="25"/>
+      <c r="U13" s="25"/>
+      <c r="V13" s="25"/>
+      <c r="W13" s="25"/>
+      <c r="X13" s="25"/>
+      <c r="Y13" s="25"/>
+      <c r="Z13" s="25"/>
+      <c r="AA13" s="25"/>
+      <c r="AB13" s="25"/>
+      <c r="AC13" s="25"/>
+      <c r="AD13" s="25"/>
+      <c r="AE13" s="25"/>
+      <c r="AF13" s="25"/>
+      <c r="AG13" s="25"/>
+      <c r="AH13" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI13" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="14" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A14" s="25">
+        <v>8</v>
+      </c>
+      <c r="B14" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_008</v>
+      </c>
+      <c r="C14" s="25"/>
+      <c r="D14" s="25"/>
+      <c r="E14" s="25"/>
+      <c r="F14" s="25"/>
+      <c r="G14" s="25"/>
+      <c r="H14" s="25"/>
+      <c r="I14" s="25"/>
+      <c r="J14" s="25"/>
+      <c r="K14" s="25"/>
+      <c r="L14" s="25"/>
+      <c r="M14" s="25"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="25"/>
+      <c r="P14" s="25"/>
+      <c r="Q14" s="25"/>
+      <c r="R14" s="25"/>
+      <c r="S14" s="25"/>
+      <c r="T14" s="25"/>
+      <c r="U14" s="25"/>
+      <c r="V14" s="25"/>
+      <c r="W14" s="25"/>
+      <c r="X14" s="25"/>
+      <c r="Y14" s="25"/>
+      <c r="Z14" s="25"/>
+      <c r="AA14" s="25"/>
+      <c r="AB14" s="25"/>
+      <c r="AC14" s="25"/>
+      <c r="AD14" s="25"/>
+      <c r="AE14" s="25"/>
+      <c r="AF14" s="25"/>
+      <c r="AG14" s="25"/>
+      <c r="AH14" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI14" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="15" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A15" s="25">
+        <v>9</v>
+      </c>
+      <c r="B15" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_009</v>
+      </c>
+      <c r="C15" s="25"/>
+      <c r="D15" s="25"/>
+      <c r="E15" s="25"/>
+      <c r="F15" s="25"/>
+      <c r="G15" s="25"/>
+      <c r="H15" s="25"/>
+      <c r="I15" s="25"/>
+      <c r="J15" s="25"/>
+      <c r="K15" s="25"/>
+      <c r="L15" s="25"/>
+      <c r="M15" s="25"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="25"/>
+      <c r="P15" s="25"/>
+      <c r="Q15" s="25"/>
+      <c r="R15" s="25"/>
+      <c r="S15" s="25"/>
+      <c r="T15" s="25"/>
+      <c r="U15" s="25"/>
+      <c r="V15" s="25"/>
+      <c r="W15" s="25"/>
+      <c r="X15" s="25"/>
+      <c r="Y15" s="25"/>
+      <c r="Z15" s="25"/>
+      <c r="AA15" s="25"/>
+      <c r="AB15" s="25"/>
+      <c r="AC15" s="25"/>
+      <c r="AD15" s="25"/>
+      <c r="AE15" s="25"/>
+      <c r="AF15" s="25"/>
+      <c r="AG15" s="25"/>
+      <c r="AH15" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI15" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="16" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A16" s="25">
+        <v>10</v>
+      </c>
+      <c r="B16" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_010</v>
+      </c>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="25"/>
+      <c r="G16" s="25"/>
+      <c r="H16" s="25"/>
+      <c r="I16" s="25"/>
+      <c r="J16" s="25"/>
+      <c r="K16" s="25"/>
+      <c r="L16" s="25"/>
+      <c r="M16" s="25"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="25"/>
+      <c r="P16" s="25"/>
+      <c r="Q16" s="25"/>
+      <c r="R16" s="25"/>
+      <c r="S16" s="25"/>
+      <c r="T16" s="25"/>
+      <c r="U16" s="25"/>
+      <c r="V16" s="25"/>
+      <c r="W16" s="25"/>
+      <c r="X16" s="25"/>
+      <c r="Y16" s="25"/>
+      <c r="Z16" s="25"/>
+      <c r="AA16" s="25"/>
+      <c r="AB16" s="25"/>
+      <c r="AC16" s="25"/>
+      <c r="AD16" s="25"/>
+      <c r="AE16" s="25"/>
+      <c r="AF16" s="25"/>
+      <c r="AG16" s="25"/>
+      <c r="AH16" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI16" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="17" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A17" s="25">
+        <v>11</v>
+      </c>
+      <c r="B17" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_011</v>
+      </c>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="25"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="25"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="25"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="25"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="25"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="25"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="25"/>
+      <c r="T17" s="25"/>
+      <c r="U17" s="25"/>
+      <c r="V17" s="25"/>
+      <c r="W17" s="25"/>
+      <c r="X17" s="25"/>
+      <c r="Y17" s="25"/>
+      <c r="Z17" s="25"/>
+      <c r="AA17" s="25"/>
+      <c r="AB17" s="25"/>
+      <c r="AC17" s="25"/>
+      <c r="AD17" s="25"/>
+      <c r="AE17" s="25"/>
+      <c r="AF17" s="25"/>
+      <c r="AG17" s="25"/>
+      <c r="AH17" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI17" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="18" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A18" s="25">
+        <v>12</v>
+      </c>
+      <c r="B18" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_012</v>
+      </c>
+      <c r="C18" s="25"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="25"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="25"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="25"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="25"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="25"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="25"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="25"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="25"/>
+      <c r="T18" s="25"/>
+      <c r="U18" s="25"/>
+      <c r="V18" s="25"/>
+      <c r="W18" s="25"/>
+      <c r="X18" s="25"/>
+      <c r="Y18" s="25"/>
+      <c r="Z18" s="25"/>
+      <c r="AA18" s="25"/>
+      <c r="AB18" s="25"/>
+      <c r="AC18" s="25"/>
+      <c r="AD18" s="25"/>
+      <c r="AE18" s="25"/>
+      <c r="AF18" s="25"/>
+      <c r="AG18" s="25"/>
+      <c r="AH18" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI18" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="19" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A19" s="25">
+        <v>13</v>
+      </c>
+      <c r="B19" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_013</v>
+      </c>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="25"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="25"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="25"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="25"/>
+      <c r="T19" s="25"/>
+      <c r="U19" s="25"/>
+      <c r="V19" s="25"/>
+      <c r="W19" s="25"/>
+      <c r="X19" s="25"/>
+      <c r="Y19" s="25"/>
+      <c r="Z19" s="25"/>
+      <c r="AA19" s="25"/>
+      <c r="AB19" s="25"/>
+      <c r="AC19" s="25"/>
+      <c r="AD19" s="25"/>
+      <c r="AE19" s="25"/>
+      <c r="AF19" s="25"/>
+      <c r="AG19" s="25"/>
+      <c r="AH19" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI19" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="20" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A20" s="25">
+        <v>14</v>
+      </c>
+      <c r="B20" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_014</v>
+      </c>
+      <c r="C20" s="25"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="25"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="25"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="25"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="25"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="25"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="25"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="25"/>
+      <c r="T20" s="25"/>
+      <c r="U20" s="25"/>
+      <c r="V20" s="25"/>
+      <c r="W20" s="25"/>
+      <c r="X20" s="25"/>
+      <c r="Y20" s="25"/>
+      <c r="Z20" s="25"/>
+      <c r="AA20" s="25"/>
+      <c r="AB20" s="25"/>
+      <c r="AC20" s="25"/>
+      <c r="AD20" s="25"/>
+      <c r="AE20" s="25"/>
+      <c r="AF20" s="25"/>
+      <c r="AG20" s="25"/>
+      <c r="AH20" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI20" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="21" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A21" s="25">
+        <v>15</v>
+      </c>
+      <c r="B21" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_015</v>
+      </c>
+      <c r="C21" s="25"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="25"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="25"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="25"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="25"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="25"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="25"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="25"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="25"/>
+      <c r="T21" s="25"/>
+      <c r="U21" s="25"/>
+      <c r="V21" s="25"/>
+      <c r="W21" s="25"/>
+      <c r="X21" s="25"/>
+      <c r="Y21" s="25"/>
+      <c r="Z21" s="25"/>
+      <c r="AA21" s="25"/>
+      <c r="AB21" s="25"/>
+      <c r="AC21" s="25"/>
+      <c r="AD21" s="25"/>
+      <c r="AE21" s="25"/>
+      <c r="AF21" s="25"/>
+      <c r="AG21" s="25"/>
+      <c r="AH21" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI21" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="22" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A22" s="25">
+        <v>16</v>
+      </c>
+      <c r="B22" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_016</v>
+      </c>
+      <c r="C22" s="25"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="25"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="25"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="25"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="25"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="25"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="25"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="25"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="25"/>
+      <c r="T22" s="25"/>
+      <c r="U22" s="25"/>
+      <c r="V22" s="25"/>
+      <c r="W22" s="25"/>
+      <c r="X22" s="25"/>
+      <c r="Y22" s="25"/>
+      <c r="Z22" s="25"/>
+      <c r="AA22" s="25"/>
+      <c r="AB22" s="25"/>
+      <c r="AC22" s="25"/>
+      <c r="AD22" s="25"/>
+      <c r="AE22" s="25"/>
+      <c r="AF22" s="25"/>
+      <c r="AG22" s="25"/>
+      <c r="AH22" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI22" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="23" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A23" s="25">
+        <v>17</v>
+      </c>
+      <c r="B23" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_017</v>
+      </c>
+      <c r="C23" s="25"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="25"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="25"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="25"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="25"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="25"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="25"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="25"/>
+      <c r="T23" s="25"/>
+      <c r="U23" s="25"/>
+      <c r="V23" s="25"/>
+      <c r="W23" s="25"/>
+      <c r="X23" s="25"/>
+      <c r="Y23" s="25"/>
+      <c r="Z23" s="25"/>
+      <c r="AA23" s="25"/>
+      <c r="AB23" s="25"/>
+      <c r="AC23" s="25"/>
+      <c r="AD23" s="25"/>
+      <c r="AE23" s="25"/>
+      <c r="AF23" s="25"/>
+      <c r="AG23" s="25"/>
+      <c r="AH23" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI23" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ23" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="24" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A24" s="25">
+        <v>18</v>
+      </c>
+      <c r="B24" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_018</v>
+      </c>
+      <c r="C24" s="25"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="25"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="25"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="25"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="25"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="25"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="25"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="25"/>
+      <c r="T24" s="25"/>
+      <c r="U24" s="25"/>
+      <c r="V24" s="25"/>
+      <c r="W24" s="25"/>
+      <c r="X24" s="25"/>
+      <c r="Y24" s="25"/>
+      <c r="Z24" s="25"/>
+      <c r="AA24" s="25"/>
+      <c r="AB24" s="25"/>
+      <c r="AC24" s="25"/>
+      <c r="AD24" s="25"/>
+      <c r="AE24" s="25"/>
+      <c r="AF24" s="25"/>
+      <c r="AG24" s="25"/>
+      <c r="AH24" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI24" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ24" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="25" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A25" s="25">
+        <v>19</v>
+      </c>
+      <c r="B25" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_019</v>
+      </c>
+      <c r="C25" s="25"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="25"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="25"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="25"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="25"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="25"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="25"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="25"/>
+      <c r="T25" s="25"/>
+      <c r="U25" s="25"/>
+      <c r="V25" s="25"/>
+      <c r="W25" s="25"/>
+      <c r="X25" s="25"/>
+      <c r="Y25" s="25"/>
+      <c r="Z25" s="25"/>
+      <c r="AA25" s="25"/>
+      <c r="AB25" s="25"/>
+      <c r="AC25" s="25"/>
+      <c r="AD25" s="25"/>
+      <c r="AE25" s="25"/>
+      <c r="AF25" s="25"/>
+      <c r="AG25" s="25"/>
+      <c r="AH25" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI25" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ25" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="26" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A26" s="25">
+        <v>20</v>
+      </c>
+      <c r="B26" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_020</v>
+      </c>
+      <c r="C26" s="25"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="25"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="25"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="25"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="25"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="25"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="25"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="25"/>
+      <c r="T26" s="25"/>
+      <c r="U26" s="25"/>
+      <c r="V26" s="25"/>
+      <c r="W26" s="25"/>
+      <c r="X26" s="25"/>
+      <c r="Y26" s="25"/>
+      <c r="Z26" s="25"/>
+      <c r="AA26" s="25"/>
+      <c r="AB26" s="25"/>
+      <c r="AC26" s="25"/>
+      <c r="AD26" s="25"/>
+      <c r="AE26" s="25"/>
+      <c r="AF26" s="25"/>
+      <c r="AG26" s="25"/>
+      <c r="AH26" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI26" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="27" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A27" s="25">
+        <v>21</v>
+      </c>
+      <c r="B27" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_021</v>
+      </c>
+      <c r="C27" s="25"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="25"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="25"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="25"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="25"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="25"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="25"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="25"/>
+      <c r="T27" s="25"/>
+      <c r="U27" s="25"/>
+      <c r="V27" s="25"/>
+      <c r="W27" s="25"/>
+      <c r="X27" s="25"/>
+      <c r="Y27" s="25"/>
+      <c r="Z27" s="25"/>
+      <c r="AA27" s="25"/>
+      <c r="AB27" s="25"/>
+      <c r="AC27" s="25"/>
+      <c r="AD27" s="25"/>
+      <c r="AE27" s="25"/>
+      <c r="AF27" s="25"/>
+      <c r="AG27" s="25"/>
+      <c r="AH27" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI27" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ27" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="28" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A28" s="25">
+        <v>22</v>
+      </c>
+      <c r="B28" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_022</v>
+      </c>
+      <c r="C28" s="25"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="25"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="25"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="25"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="25"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="25"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="25"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="25"/>
+      <c r="T28" s="25"/>
+      <c r="U28" s="25"/>
+      <c r="V28" s="25"/>
+      <c r="W28" s="25"/>
+      <c r="X28" s="25"/>
+      <c r="Y28" s="25"/>
+      <c r="Z28" s="25"/>
+      <c r="AA28" s="25"/>
+      <c r="AB28" s="25"/>
+      <c r="AC28" s="25"/>
+      <c r="AD28" s="25"/>
+      <c r="AE28" s="25"/>
+      <c r="AF28" s="25"/>
+      <c r="AG28" s="25"/>
+      <c r="AH28" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI28" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ28" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+    <row r="29" spans="1:36" x14ac:dyDescent="0.35">
+      <c r="A29" s="25">
+        <v>23</v>
+      </c>
+      <c r="B29" s="25" t="str">
+        <f t="shared" si="2"/>
+        <v>Text_user_023</v>
+      </c>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+      <c r="M29" s="25"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="25"/>
+      <c r="P29" s="25"/>
+      <c r="Q29" s="25"/>
+      <c r="R29" s="25"/>
+      <c r="S29" s="25"/>
+      <c r="T29" s="25"/>
+      <c r="U29" s="25"/>
+      <c r="V29" s="25"/>
+      <c r="W29" s="25"/>
+      <c r="X29" s="25"/>
+      <c r="Y29" s="25"/>
+      <c r="Z29" s="25"/>
+      <c r="AA29" s="25"/>
+      <c r="AB29" s="25"/>
+      <c r="AC29" s="25"/>
+      <c r="AD29" s="25"/>
+      <c r="AE29" s="25"/>
+      <c r="AF29" s="25"/>
+      <c r="AG29" s="25"/>
+      <c r="AH29" s="41">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="AI29" s="45">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="AJ29" s="46" t="e">
+        <f t="shared" si="5"/>
+        <v>#DIV/0!</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B12" xr:uid="{A8223CBD-25D4-4F7C-8804-8566BB798AD8}">
-      <formula1>"Java, Python, HTML, CSS, JS"</formula1>
+  <mergeCells count="3">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A5:A6"/>
+  </mergeCells>
+  <conditionalFormatting sqref="C5:AG29 AI6:AI29">
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>OR(WEEKDAY(C$5,11)=6,WEEKDAY(C$5,11)=7,COUNTIF(no_of_holidays,C$5)=1)</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="3" priority="3">
+      <formula>C$5=""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C7:AG29">
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>C7="P"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>C7="A"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{4290E332-D6BC-41AF-BA8B-ABD42AAAAE76}">
+      <formula1>months</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{4668F209-EFB0-4753-B9FF-74A4F376569C}">
+      <formula1>no_of_years</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C5:AG6" xr:uid="{09023EEF-AE87-470E-AF90-E1C394307DC0}">
+      <formula1>AND(NOT(OR(WEEKDAY(C$5,11)=6,WEEKDAY(C$5,11)=7,COUNTIF(no_of_holidays,C$5)=1)),OR(C7="P",C7="A"))</formula1>
+    </dataValidation>
+    <dataValidation type="custom" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error" error="Please enter only A or P and in Holidays you can't able to update anything" sqref="C7:AG29" xr:uid="{485CD3E9-EEE1-4033-AEBF-D5E5454666B1}">
+      <formula1>AND(NOT(OR(WEEKDAY(C$5,11)=6,WEEKDAY(C$5,11)=7,COUNTIF(no_of_holidays,C$5)=1)),OR(C7="P",C7="A"))</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+  <controls>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice Requires="x14">
+        <control shapeId="6151" r:id="rId3" name="CommandButton1">
+          <controlPr defaultSize="0" autoLine="0" r:id="rId4">
+            <anchor moveWithCells="1">
+              <from>
+                <xdr:col>3</xdr:col>
+                <xdr:colOff>106680</xdr:colOff>
+                <xdr:row>1</xdr:row>
+                <xdr:rowOff>106680</xdr:rowOff>
+              </from>
+              <to>
+                <xdr:col>6</xdr:col>
+                <xdr:colOff>220980</xdr:colOff>
+                <xdr:row>2</xdr:row>
+                <xdr:rowOff>205740</xdr:rowOff>
+              </to>
+            </anchor>
+          </controlPr>
+        </control>
+      </mc:Choice>
+      <mc:Fallback>
+        <control shapeId="6151" r:id="rId3" name="CommandButton1"/>
+      </mc:Fallback>
+    </mc:AlternateContent>
+  </controls>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B8C947B3-DF31-4A72-8ED4-AF725AC17A85}">
+  <sheetPr codeName="Sheet7"/>
+  <dimension ref="A1:G19"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="7" max="7" width="9.9140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" t="s">
+        <v>105</v>
+      </c>
+      <c r="G1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="1">
+        <v>2026</v>
+      </c>
+      <c r="D2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G2" s="6">
+        <v>46048</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="1">
+        <v>2027</v>
+      </c>
+      <c r="D3" t="s">
+        <v>107</v>
+      </c>
+      <c r="G3" s="6">
+        <v>46037</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="1">
+        <v>2028</v>
+      </c>
+      <c r="D4" t="s">
+        <v>108</v>
+      </c>
+      <c r="G4" s="6">
+        <v>46102</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="1">
+        <v>2029</v>
+      </c>
+      <c r="D5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="6">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>2030</v>
+      </c>
+      <c r="D6" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="6">
+        <v>46115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="1">
+        <v>2031</v>
+      </c>
+      <c r="D7" t="s">
+        <v>111</v>
+      </c>
+      <c r="G7" s="6">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="1">
+        <v>2032</v>
+      </c>
+      <c r="D8" t="s">
+        <v>112</v>
+      </c>
+      <c r="G8" s="6">
+        <v>46143</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>2033</v>
+      </c>
+      <c r="D9" t="s">
+        <v>113</v>
+      </c>
+      <c r="G9" s="6">
+        <v>46170</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>2034</v>
+      </c>
+      <c r="D10" t="s">
+        <v>114</v>
+      </c>
+      <c r="G10" s="6">
+        <v>46199</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>2035</v>
+      </c>
+      <c r="D11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G11" s="6">
+        <v>46249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>2036</v>
+      </c>
+      <c r="D12" t="s">
+        <v>116</v>
+      </c>
+      <c r="G12" s="6">
+        <v>46260</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>2037</v>
+      </c>
+      <c r="D13" t="s">
+        <v>117</v>
+      </c>
+      <c r="G13" s="6">
+        <v>46279</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G14" s="6">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G15" s="6">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G16" s="6">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="17" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G17" s="6">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="18" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G18" s="6">
+        <v>46381</v>
+      </c>
+    </row>
+    <row r="19" spans="7:7" x14ac:dyDescent="0.35">
+      <c r="G19" s="6">
+        <v>46023</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>